--- a/_Localizations.xlsx
+++ b/_Localizations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\Anno 1800\mods\[Addon] Return to the Orient\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91113A0-5B70-4C18-A8EB-298DC4779F7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B157060D-A799-4CDA-B19B-79A0BB84F4D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4677" uniqueCount="1995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4707" uniqueCount="2010">
   <si>
     <t>ModFolder</t>
   </si>
@@ -6013,6 +6013,51 @@
   </si>
   <si>
     <t>In dieser riesigen Menschenmenge scheint der Glaube grenzenlos zu sein, und die Welt steht für einen kurzen Moment still.</t>
+  </si>
+  <si>
+    <t>Mandelsaatgut</t>
+  </si>
+  <si>
+    <t>Dattelsaatgut</t>
+  </si>
+  <si>
+    <t>Granatapfelsaatgut</t>
+  </si>
+  <si>
+    <t>Rosensaatgut</t>
+  </si>
+  <si>
+    <t>Seidensaatgut</t>
+  </si>
+  <si>
+    <t>Qualitäts-​Mandelsaatgut</t>
+  </si>
+  <si>
+    <t>Qualitäts-​Dattelsaatgut</t>
+  </si>
+  <si>
+    <t>Qualitäts-​Granatapfelsaatgut</t>
+  </si>
+  <si>
+    <t>Qualitäts-​Rosensaatgut</t>
+  </si>
+  <si>
+    <t>Qualitäts-​Seidensaatgut</t>
+  </si>
+  <si>
+    <t>Gekreuztes Seidensaatgut</t>
+  </si>
+  <si>
+    <t>Gekreuztes Rosensaatgut</t>
+  </si>
+  <si>
+    <t>Gekreuztes Granatapfelsaatgut</t>
+  </si>
+  <si>
+    <t>Gekreuztes Dattelsaatgut</t>
+  </si>
+  <si>
+    <t>Gekreuztes Mandelsaatgut</t>
   </si>
 </sst>
 </file>
@@ -6432,7 +6477,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -6485,7 +6530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -6505,7 +6550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -6519,7 +6564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -6533,7 +6578,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -6547,7 +6592,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -6561,7 +6606,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -6581,7 +6626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -6601,7 +6646,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -6621,7 +6666,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -6635,7 +6680,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -6655,7 +6700,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -6675,7 +6720,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -6695,7 +6740,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -6715,7 +6760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -6735,7 +6780,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -6755,7 +6800,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -6775,7 +6820,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -6795,7 +6840,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -6815,7 +6860,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -6835,7 +6880,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
@@ -6855,7 +6900,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
@@ -6869,7 +6914,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -6883,7 +6928,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -6897,7 +6942,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -6911,7 +6956,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -6925,7 +6970,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -6939,7 +6984,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -6953,7 +6998,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -6967,7 +7012,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -6981,7 +7026,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -6995,7 +7040,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -7009,7 +7054,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -7023,7 +7068,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -7037,7 +7082,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -7051,7 +7096,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -7065,7 +7110,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -7079,7 +7124,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -7093,7 +7138,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -7107,7 +7152,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -7127,7 +7172,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -7147,7 +7192,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -7167,7 +7212,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -7187,7 +7232,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -7207,7 +7252,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -7227,7 +7272,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -7247,7 +7292,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -7267,7 +7312,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -7287,7 +7332,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -7307,7 +7352,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>17</v>
       </c>
@@ -7333,7 +7378,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>17</v>
       </c>
@@ -7359,7 +7404,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>17</v>
       </c>
@@ -7385,7 +7430,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>17</v>
       </c>
@@ -7411,7 +7456,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>17</v>
       </c>
@@ -7437,7 +7482,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -7463,7 +7508,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>17</v>
       </c>
@@ -7489,7 +7534,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>17</v>
       </c>
@@ -7515,7 +7560,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>17</v>
       </c>
@@ -7541,7 +7586,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>17</v>
       </c>
@@ -7567,7 +7612,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>17</v>
       </c>
@@ -7593,7 +7638,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>17</v>
       </c>
@@ -7619,7 +7664,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>17</v>
       </c>
@@ -7645,7 +7690,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>17</v>
       </c>
@@ -7671,7 +7716,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>17</v>
       </c>
@@ -7697,7 +7742,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>17</v>
       </c>
@@ -7723,7 +7768,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>17</v>
       </c>
@@ -7749,7 +7794,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>17</v>
       </c>
@@ -7775,7 +7820,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>17</v>
       </c>
@@ -7801,7 +7846,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>17</v>
       </c>
@@ -7827,7 +7872,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -7853,7 +7898,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>17</v>
       </c>
@@ -7879,7 +7924,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>17</v>
       </c>
@@ -7905,7 +7950,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>17</v>
       </c>
@@ -7931,7 +7976,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -7957,7 +8002,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>17</v>
       </c>
@@ -7983,7 +8028,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -8009,7 +8054,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>17</v>
       </c>
@@ -8035,7 +8080,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>17</v>
       </c>
@@ -8061,7 +8106,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>17</v>
       </c>
@@ -8087,7 +8132,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>17</v>
       </c>
@@ -8113,7 +8158,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>17</v>
       </c>
@@ -8139,7 +8184,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>17</v>
       </c>
@@ -8165,7 +8210,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>17</v>
       </c>
@@ -8191,7 +8236,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -8217,7 +8262,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>17</v>
       </c>
@@ -8243,7 +8288,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>17</v>
       </c>
@@ -8269,7 +8314,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>17</v>
       </c>
@@ -8295,7 +8340,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -8321,7 +8366,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>17</v>
       </c>
@@ -8347,7 +8392,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>17</v>
       </c>
@@ -8373,7 +8418,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>17</v>
       </c>
@@ -8399,7 +8444,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>17</v>
       </c>
@@ -8425,7 +8470,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>17</v>
       </c>
@@ -8451,7 +8496,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>17</v>
       </c>
@@ -8477,7 +8522,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>17</v>
       </c>
@@ -8503,7 +8548,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>17</v>
       </c>
@@ -8529,7 +8574,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>17</v>
       </c>
@@ -8555,7 +8600,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>17</v>
       </c>
@@ -8581,7 +8626,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>17</v>
       </c>
@@ -8607,7 +8652,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>17</v>
       </c>
@@ -8633,7 +8678,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>17</v>
       </c>
@@ -8659,7 +8704,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -8685,7 +8730,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>17</v>
       </c>
@@ -8711,7 +8756,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>17</v>
       </c>
@@ -8737,7 +8782,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>17</v>
       </c>
@@ -8763,7 +8808,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>17</v>
       </c>
@@ -8789,7 +8834,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>17</v>
       </c>
@@ -8815,7 +8860,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>17</v>
       </c>
@@ -8841,7 +8886,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>17</v>
       </c>
@@ -8867,7 +8912,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>17</v>
       </c>
@@ -8893,7 +8938,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>17</v>
       </c>
@@ -8919,7 +8964,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>17</v>
       </c>
@@ -8945,7 +8990,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>17</v>
       </c>
@@ -8971,7 +9016,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>17</v>
       </c>
@@ -8997,7 +9042,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>17</v>
       </c>
@@ -9023,7 +9068,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>17</v>
       </c>
@@ -9049,7 +9094,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>17</v>
       </c>
@@ -9075,7 +9120,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>17</v>
       </c>
@@ -9101,7 +9146,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>17</v>
       </c>
@@ -9127,7 +9172,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>17</v>
       </c>
@@ -9153,7 +9198,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>17</v>
       </c>
@@ -9179,7 +9224,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>17</v>
       </c>
@@ -9205,7 +9250,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>17</v>
       </c>
@@ -9231,7 +9276,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>17</v>
       </c>
@@ -9257,7 +9302,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>17</v>
       </c>
@@ -9283,7 +9328,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>17</v>
       </c>
@@ -9309,7 +9354,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>17</v>
       </c>
@@ -9335,7 +9380,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>17</v>
       </c>
@@ -9361,7 +9406,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>17</v>
       </c>
@@ -9387,7 +9432,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>17</v>
       </c>
@@ -9413,7 +9458,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>17</v>
       </c>
@@ -9439,7 +9484,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>17</v>
       </c>
@@ -9465,7 +9510,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>17</v>
       </c>
@@ -9491,7 +9536,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>17</v>
       </c>
@@ -9517,7 +9562,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>17</v>
       </c>
@@ -9543,7 +9588,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>17</v>
       </c>
@@ -9569,7 +9614,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>17</v>
       </c>
@@ -9595,7 +9640,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>17</v>
       </c>
@@ -9621,7 +9666,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>17</v>
       </c>
@@ -9647,7 +9692,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>17</v>
       </c>
@@ -9667,7 +9712,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>17</v>
       </c>
@@ -9687,7 +9732,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>17</v>
       </c>
@@ -9707,7 +9752,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>17</v>
       </c>
@@ -9727,7 +9772,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>17</v>
       </c>
@@ -9747,7 +9792,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -9761,7 +9806,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>17</v>
       </c>
@@ -9775,7 +9820,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>17</v>
       </c>
@@ -9789,7 +9834,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>17</v>
       </c>
@@ -9803,7 +9848,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>17</v>
       </c>
@@ -9823,7 +9868,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>17</v>
       </c>
@@ -9843,7 +9888,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>17</v>
       </c>
@@ -9863,7 +9908,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>17</v>
       </c>
@@ -9883,7 +9928,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>17</v>
       </c>
@@ -9903,7 +9948,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>17</v>
       </c>
@@ -9923,7 +9968,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>17</v>
       </c>
@@ -9943,7 +9988,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>17</v>
       </c>
@@ -9963,7 +10008,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>17</v>
       </c>
@@ -9983,7 +10028,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>17</v>
       </c>
@@ -10003,7 +10048,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>17</v>
       </c>
@@ -10023,7 +10068,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>17</v>
       </c>
@@ -10043,7 +10088,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>17</v>
       </c>
@@ -10063,7 +10108,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>17</v>
       </c>
@@ -10077,7 +10122,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>17</v>
       </c>
@@ -10097,7 +10142,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>17</v>
       </c>
@@ -10117,7 +10162,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>17</v>
       </c>
@@ -10131,7 +10176,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>17</v>
       </c>
@@ -10145,7 +10190,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>17</v>
       </c>
@@ -10165,7 +10210,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>17</v>
       </c>
@@ -10185,7 +10230,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>17</v>
       </c>
@@ -10205,7 +10250,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>17</v>
       </c>
@@ -10225,7 +10270,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>17</v>
       </c>
@@ -10239,7 +10284,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>17</v>
       </c>
@@ -10253,7 +10298,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>17</v>
       </c>
@@ -10267,7 +10312,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>17</v>
       </c>
@@ -10281,7 +10326,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>17</v>
       </c>
@@ -10295,7 +10340,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>17</v>
       </c>
@@ -10309,7 +10354,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>17</v>
       </c>
@@ -10323,7 +10368,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>17</v>
       </c>
@@ -10337,7 +10382,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>17</v>
       </c>
@@ -10351,7 +10396,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>17</v>
       </c>
@@ -10365,7 +10410,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>17</v>
       </c>
@@ -10379,7 +10424,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>17</v>
       </c>
@@ -10393,7 +10438,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>17</v>
       </c>
@@ -10407,7 +10452,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>17</v>
       </c>
@@ -10427,7 +10472,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>17</v>
       </c>
@@ -10447,7 +10492,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>17</v>
       </c>
@@ -10467,7 +10512,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>17</v>
       </c>
@@ -10487,7 +10532,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>17</v>
       </c>
@@ -10507,7 +10552,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>17</v>
       </c>
@@ -10527,7 +10572,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>17</v>
       </c>
@@ -10547,7 +10592,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>17</v>
       </c>
@@ -10567,7 +10612,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>17</v>
       </c>
@@ -10581,7 +10626,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>17</v>
       </c>
@@ -10595,7 +10640,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>17</v>
       </c>
@@ -10615,7 +10660,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>17</v>
       </c>
@@ -10635,7 +10680,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>17</v>
       </c>
@@ -10655,7 +10700,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>17</v>
       </c>
@@ -10675,7 +10720,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>17</v>
       </c>
@@ -10695,7 +10740,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>17</v>
       </c>
@@ -10709,7 +10754,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>17</v>
       </c>
@@ -10723,7 +10768,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>17</v>
       </c>
@@ -10737,7 +10782,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>17</v>
       </c>
@@ -10751,7 +10796,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>17</v>
       </c>
@@ -10765,7 +10810,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>17</v>
       </c>
@@ -10779,7 +10824,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>17</v>
       </c>
@@ -10793,7 +10838,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>17</v>
       </c>
@@ -10807,7 +10852,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>17</v>
       </c>
@@ -10821,7 +10866,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>17</v>
       </c>
@@ -10835,7 +10880,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>17</v>
       </c>
@@ -10849,7 +10894,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>17</v>
       </c>
@@ -10863,7 +10908,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>17</v>
       </c>
@@ -10877,7 +10922,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>17</v>
       </c>
@@ -10891,7 +10936,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>17</v>
       </c>
@@ -10905,7 +10950,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>17</v>
       </c>
@@ -10925,7 +10970,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>421</v>
       </c>
@@ -10945,7 +10990,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>421</v>
       </c>
@@ -10965,7 +11010,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>428</v>
       </c>
@@ -10985,7 +11030,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>428</v>
       </c>
@@ -11005,7 +11050,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>435</v>
       </c>
@@ -11025,7 +11070,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>435</v>
       </c>
@@ -11045,7 +11090,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>442</v>
       </c>
@@ -11065,7 +11110,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>442</v>
       </c>
@@ -11085,7 +11130,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>449</v>
       </c>
@@ -11105,7 +11150,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>449</v>
       </c>
@@ -11125,7 +11170,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>456</v>
       </c>
@@ -11145,7 +11190,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>456</v>
       </c>
@@ -11165,7 +11210,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>461</v>
       </c>
@@ -11185,7 +11230,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>461</v>
       </c>
@@ -11205,7 +11250,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>467</v>
       </c>
@@ -11225,7 +11270,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>467</v>
       </c>
@@ -11245,7 +11290,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>474</v>
       </c>
@@ -11265,7 +11310,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>474</v>
       </c>
@@ -11285,7 +11330,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>17</v>
       </c>
@@ -11305,7 +11350,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>17</v>
       </c>
@@ -11325,7 +11370,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>17</v>
       </c>
@@ -11345,7 +11390,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>17</v>
       </c>
@@ -11365,7 +11410,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>17</v>
       </c>
@@ -11385,7 +11430,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>17</v>
       </c>
@@ -11405,7 +11450,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>17</v>
       </c>
@@ -11425,7 +11470,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>17</v>
       </c>
@@ -11445,7 +11490,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>17</v>
       </c>
@@ -11465,7 +11510,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>17</v>
       </c>
@@ -11485,7 +11530,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>17</v>
       </c>
@@ -11505,7 +11550,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>17</v>
       </c>
@@ -11525,7 +11570,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>17</v>
       </c>
@@ -11545,7 +11590,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>17</v>
       </c>
@@ -11565,7 +11610,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>17</v>
       </c>
@@ -11585,7 +11630,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>17</v>
       </c>
@@ -11605,7 +11650,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>17</v>
       </c>
@@ -11625,7 +11670,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>17</v>
       </c>
@@ -11645,7 +11690,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>17</v>
       </c>
@@ -11665,7 +11710,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>17</v>
       </c>
@@ -11679,7 +11724,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>17</v>
       </c>
@@ -11699,7 +11744,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>17</v>
       </c>
@@ -11719,7 +11764,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>17</v>
       </c>
@@ -11739,7 +11784,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>17</v>
       </c>
@@ -11759,7 +11804,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>17</v>
       </c>
@@ -11779,7 +11824,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>17</v>
       </c>
@@ -11799,7 +11844,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>17</v>
       </c>
@@ -11819,7 +11864,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>17</v>
       </c>
@@ -11839,7 +11884,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>17</v>
       </c>
@@ -11859,7 +11904,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>17</v>
       </c>
@@ -11879,7 +11924,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>17</v>
       </c>
@@ -11899,7 +11944,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>17</v>
       </c>
@@ -11919,7 +11964,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>17</v>
       </c>
@@ -11939,7 +11984,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>17</v>
       </c>
@@ -11959,7 +12004,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>17</v>
       </c>
@@ -11979,7 +12024,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>17</v>
       </c>
@@ -11999,7 +12044,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>17</v>
       </c>
@@ -12019,7 +12064,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>17</v>
       </c>
@@ -12039,7 +12084,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>17</v>
       </c>
@@ -12059,7 +12104,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>17</v>
       </c>
@@ -12079,7 +12124,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>17</v>
       </c>
@@ -12099,7 +12144,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>17</v>
       </c>
@@ -12119,7 +12164,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>17</v>
       </c>
@@ -12139,7 +12184,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>17</v>
       </c>
@@ -12159,7 +12204,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>17</v>
       </c>
@@ -12179,7 +12224,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>17</v>
       </c>
@@ -12199,7 +12244,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>17</v>
       </c>
@@ -12219,7 +12264,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>17</v>
       </c>
@@ -12239,7 +12284,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>17</v>
       </c>
@@ -12259,7 +12304,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>17</v>
       </c>
@@ -12279,7 +12324,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>17</v>
       </c>
@@ -12299,7 +12344,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>17</v>
       </c>
@@ -12319,7 +12364,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>17</v>
       </c>
@@ -12339,7 +12384,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>17</v>
       </c>
@@ -12359,7 +12404,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>17</v>
       </c>
@@ -12379,7 +12424,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>17</v>
       </c>
@@ -12399,7 +12444,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>17</v>
       </c>
@@ -12419,7 +12464,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>17</v>
       </c>
@@ -12439,7 +12484,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>17</v>
       </c>
@@ -12459,7 +12504,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>17</v>
       </c>
@@ -12479,7 +12524,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>17</v>
       </c>
@@ -12499,7 +12544,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>17</v>
       </c>
@@ -12519,7 +12564,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>17</v>
       </c>
@@ -12539,7 +12584,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>17</v>
       </c>
@@ -12559,7 +12604,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>17</v>
       </c>
@@ -12579,7 +12624,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>17</v>
       </c>
@@ -12599,7 +12644,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>17</v>
       </c>
@@ -12619,7 +12664,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>17</v>
       </c>
@@ -12639,7 +12684,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>17</v>
       </c>
@@ -12659,7 +12704,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -12673,7 +12718,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>17</v>
       </c>
@@ -12693,7 +12738,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="305" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>17</v>
       </c>
@@ -12713,7 +12758,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="306" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>17</v>
       </c>
@@ -12733,7 +12778,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="307" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>574</v>
       </c>
@@ -12780,7 +12825,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="308" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>17</v>
       </c>
@@ -12794,7 +12839,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="309" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>17</v>
       </c>
@@ -12808,7 +12853,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="310" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>17</v>
       </c>
@@ -12822,7 +12867,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="311" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>17</v>
       </c>
@@ -12848,7 +12893,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="312" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>17</v>
       </c>
@@ -12862,7 +12907,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="313" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>17</v>
       </c>
@@ -12888,7 +12933,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="314" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>17</v>
       </c>
@@ -12902,7 +12947,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="315" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>17</v>
       </c>
@@ -12928,7 +12973,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="316" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>17</v>
       </c>
@@ -12942,7 +12987,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="317" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>17</v>
       </c>
@@ -12968,7 +13013,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="318" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>17</v>
       </c>
@@ -12982,7 +13027,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="319" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>17</v>
       </c>
@@ -13008,7 +13053,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="320" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>17</v>
       </c>
@@ -13022,7 +13067,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>17</v>
       </c>
@@ -13048,7 +13093,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="322" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>17</v>
       </c>
@@ -13062,7 +13107,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>17</v>
       </c>
@@ -13088,7 +13133,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="324" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>17</v>
       </c>
@@ -13102,7 +13147,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>17</v>
       </c>
@@ -13128,7 +13173,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="326" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>17</v>
       </c>
@@ -13142,7 +13187,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>17</v>
       </c>
@@ -13168,7 +13213,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="328" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>17</v>
       </c>
@@ -13182,7 +13227,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>17</v>
       </c>
@@ -13208,7 +13253,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="330" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>17</v>
       </c>
@@ -13222,7 +13267,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>17</v>
       </c>
@@ -13248,7 +13293,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="332" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>17</v>
       </c>
@@ -13262,7 +13307,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>17</v>
       </c>
@@ -13288,7 +13333,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="334" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>17</v>
       </c>
@@ -13302,7 +13347,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>17</v>
       </c>
@@ -13328,7 +13373,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="336" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>17</v>
       </c>
@@ -13342,7 +13387,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>17</v>
       </c>
@@ -13368,7 +13413,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="338" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>17</v>
       </c>
@@ -13382,7 +13427,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>17</v>
       </c>
@@ -13408,7 +13453,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="340" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>17</v>
       </c>
@@ -13422,7 +13467,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>17</v>
       </c>
@@ -13448,7 +13493,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="342" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>17</v>
       </c>
@@ -13462,7 +13507,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>17</v>
       </c>
@@ -13488,7 +13533,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="344" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>17</v>
       </c>
@@ -13502,7 +13547,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>17</v>
       </c>
@@ -13528,7 +13573,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="346" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>17</v>
       </c>
@@ -13542,7 +13587,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>17</v>
       </c>
@@ -13568,7 +13613,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="348" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -13582,7 +13627,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>17</v>
       </c>
@@ -13608,7 +13653,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="350" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>17</v>
       </c>
@@ -13622,7 +13667,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>17</v>
       </c>
@@ -13648,7 +13693,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="352" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>17</v>
       </c>
@@ -13662,7 +13707,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>17</v>
       </c>
@@ -13688,7 +13733,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="354" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>17</v>
       </c>
@@ -13702,7 +13747,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>17</v>
       </c>
@@ -13728,7 +13773,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="356" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>17</v>
       </c>
@@ -13742,7 +13787,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>17</v>
       </c>
@@ -13768,7 +13813,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="358" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>17</v>
       </c>
@@ -13782,7 +13827,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>17</v>
       </c>
@@ -13808,7 +13853,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="360" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>17</v>
       </c>
@@ -13822,7 +13867,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>17</v>
       </c>
@@ -13848,7 +13893,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="362" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>17</v>
       </c>
@@ -13862,7 +13907,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>17</v>
       </c>
@@ -13888,7 +13933,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="364" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>17</v>
       </c>
@@ -13902,7 +13947,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>17</v>
       </c>
@@ -13928,7 +13973,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="366" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -13942,7 +13987,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>17</v>
       </c>
@@ -13968,7 +14013,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="368" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>17</v>
       </c>
@@ -13982,7 +14027,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -14008,7 +14053,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="370" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>17</v>
       </c>
@@ -14022,7 +14067,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>17</v>
       </c>
@@ -14048,7 +14093,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="372" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>17</v>
       </c>
@@ -14062,7 +14107,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>17</v>
       </c>
@@ -14088,7 +14133,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="374" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>17</v>
       </c>
@@ -14102,7 +14147,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>17</v>
       </c>
@@ -14128,7 +14173,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="376" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>17</v>
       </c>
@@ -14142,7 +14187,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>17</v>
       </c>
@@ -14168,7 +14213,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="378" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>17</v>
       </c>
@@ -14182,7 +14227,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>17</v>
       </c>
@@ -14208,7 +14253,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="380" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>17</v>
       </c>
@@ -14222,7 +14267,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>17</v>
       </c>
@@ -14248,7 +14293,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="382" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>17</v>
       </c>
@@ -14262,7 +14307,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>17</v>
       </c>
@@ -14288,7 +14333,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="384" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>17</v>
       </c>
@@ -14302,7 +14347,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>17</v>
       </c>
@@ -14328,7 +14373,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>17</v>
       </c>
@@ -14342,7 +14387,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>17</v>
       </c>
@@ -14368,7 +14413,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>17</v>
       </c>
@@ -14382,7 +14427,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>17</v>
       </c>
@@ -14396,7 +14441,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>17</v>
       </c>
@@ -14422,7 +14467,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>17</v>
       </c>
@@ -14436,7 +14481,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>17</v>
       </c>
@@ -14462,7 +14507,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>17</v>
       </c>
@@ -14476,7 +14521,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>17</v>
       </c>
@@ -14502,7 +14547,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>17</v>
       </c>
@@ -14516,7 +14561,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>17</v>
       </c>
@@ -14542,7 +14587,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>17</v>
       </c>
@@ -14556,7 +14601,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>17</v>
       </c>
@@ -14582,7 +14627,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>17</v>
       </c>
@@ -14596,7 +14641,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>17</v>
       </c>
@@ -14622,7 +14667,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="401" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>17</v>
       </c>
@@ -14636,7 +14681,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>17</v>
       </c>
@@ -14662,7 +14707,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="403" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>17</v>
       </c>
@@ -14676,7 +14721,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>17</v>
       </c>
@@ -14702,7 +14747,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="405" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>17</v>
       </c>
@@ -14716,7 +14761,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>17</v>
       </c>
@@ -14742,7 +14787,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="407" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>17</v>
       </c>
@@ -14756,7 +14801,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>17</v>
       </c>
@@ -14782,7 +14827,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="409" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>17</v>
       </c>
@@ -14796,7 +14841,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>17</v>
       </c>
@@ -14822,7 +14867,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="411" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>17</v>
       </c>
@@ -14836,7 +14881,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>17</v>
       </c>
@@ -14862,7 +14907,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="413" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>17</v>
       </c>
@@ -14876,7 +14921,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>17</v>
       </c>
@@ -14902,7 +14947,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="415" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>17</v>
       </c>
@@ -14916,7 +14961,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>17</v>
       </c>
@@ -14942,7 +14987,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>17</v>
       </c>
@@ -14956,7 +15001,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>17</v>
       </c>
@@ -14982,7 +15027,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>17</v>
       </c>
@@ -14996,7 +15041,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>17</v>
       </c>
@@ -15022,7 +15067,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>17</v>
       </c>
@@ -15036,7 +15081,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>17</v>
       </c>
@@ -15062,7 +15107,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>17</v>
       </c>
@@ -15076,7 +15121,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>17</v>
       </c>
@@ -15102,7 +15147,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>17</v>
       </c>
@@ -15116,7 +15161,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>17</v>
       </c>
@@ -15142,7 +15187,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>17</v>
       </c>
@@ -15156,7 +15201,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>17</v>
       </c>
@@ -15182,7 +15227,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -15196,7 +15241,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>17</v>
       </c>
@@ -15222,7 +15267,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>17</v>
       </c>
@@ -15236,7 +15281,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>17</v>
       </c>
@@ -15262,7 +15307,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>17</v>
       </c>
@@ -15276,7 +15321,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>17</v>
       </c>
@@ -15302,7 +15347,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>17</v>
       </c>
@@ -15316,7 +15361,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>17</v>
       </c>
@@ -15342,7 +15387,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>17</v>
       </c>
@@ -15356,7 +15401,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>17</v>
       </c>
@@ -15382,7 +15427,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>17</v>
       </c>
@@ -15396,7 +15441,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>17</v>
       </c>
@@ -15422,7 +15467,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>17</v>
       </c>
@@ -15436,7 +15481,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>17</v>
       </c>
@@ -15462,7 +15507,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>17</v>
       </c>
@@ -15476,7 +15521,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>17</v>
       </c>
@@ -15502,7 +15547,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>17</v>
       </c>
@@ -15516,7 +15561,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>17</v>
       </c>
@@ -15542,7 +15587,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>17</v>
       </c>
@@ -15556,7 +15601,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>17</v>
       </c>
@@ -15582,7 +15627,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>17</v>
       </c>
@@ -15596,7 +15641,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>17</v>
       </c>
@@ -15622,7 +15667,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>17</v>
       </c>
@@ -15636,7 +15681,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>17</v>
       </c>
@@ -15662,7 +15707,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>17</v>
       </c>
@@ -15676,7 +15721,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>17</v>
       </c>
@@ -15702,7 +15747,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>17</v>
       </c>
@@ -15716,7 +15761,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>17</v>
       </c>
@@ -15742,7 +15787,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>17</v>
       </c>
@@ -15756,7 +15801,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>17</v>
       </c>
@@ -15782,7 +15827,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>17</v>
       </c>
@@ -15796,7 +15841,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>17</v>
       </c>
@@ -15822,7 +15867,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>17</v>
       </c>
@@ -15836,7 +15881,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>17</v>
       </c>
@@ -15862,7 +15907,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>17</v>
       </c>
@@ -15876,7 +15921,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>17</v>
       </c>
@@ -15902,7 +15947,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>17</v>
       </c>
@@ -15916,7 +15961,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>17</v>
       </c>
@@ -15942,7 +15987,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>17</v>
       </c>
@@ -15956,7 +16001,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>17</v>
       </c>
@@ -15982,7 +16027,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>17</v>
       </c>
@@ -15996,7 +16041,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>17</v>
       </c>
@@ -16022,7 +16067,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>17</v>
       </c>
@@ -16036,7 +16081,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>17</v>
       </c>
@@ -16062,7 +16107,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>17</v>
       </c>
@@ -16076,7 +16121,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>17</v>
       </c>
@@ -16102,7 +16147,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>17</v>
       </c>
@@ -16116,7 +16161,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>17</v>
       </c>
@@ -16142,7 +16187,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>17</v>
       </c>
@@ -16156,7 +16201,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>17</v>
       </c>
@@ -16182,7 +16227,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>17</v>
       </c>
@@ -16196,7 +16241,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>17</v>
       </c>
@@ -16222,7 +16267,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>17</v>
       </c>
@@ -16236,7 +16281,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>17</v>
       </c>
@@ -16262,7 +16307,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>17</v>
       </c>
@@ -16276,7 +16321,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>17</v>
       </c>
@@ -16302,7 +16347,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>17</v>
       </c>
@@ -16316,7 +16361,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>17</v>
       </c>
@@ -16342,7 +16387,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>17</v>
       </c>
@@ -16356,7 +16401,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>17</v>
       </c>
@@ -16370,7 +16415,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>17</v>
       </c>
@@ -16384,7 +16429,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>17</v>
       </c>
@@ -16398,7 +16443,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>17</v>
       </c>
@@ -16412,7 +16457,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>17</v>
       </c>
@@ -16426,7 +16471,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>17</v>
       </c>
@@ -16440,7 +16485,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>17</v>
       </c>
@@ -16454,7 +16499,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>17</v>
       </c>
@@ -16468,7 +16513,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>17</v>
       </c>
@@ -16482,7 +16527,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>17</v>
       </c>
@@ -16496,7 +16541,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>17</v>
       </c>
@@ -16510,7 +16555,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>17</v>
       </c>
@@ -16524,7 +16569,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>17</v>
       </c>
@@ -16538,7 +16583,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>17</v>
       </c>
@@ -16552,7 +16597,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>17</v>
       </c>
@@ -16566,7 +16611,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>17</v>
       </c>
@@ -16580,7 +16625,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>17</v>
       </c>
@@ -16594,7 +16639,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>17</v>
       </c>
@@ -16608,7 +16653,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>17</v>
       </c>
@@ -16622,7 +16667,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>17</v>
       </c>
@@ -16642,7 +16687,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>17</v>
       </c>
@@ -16662,7 +16707,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>17</v>
       </c>
@@ -16682,7 +16727,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>17</v>
       </c>
@@ -16702,7 +16747,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>17</v>
       </c>
@@ -16722,7 +16767,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>17</v>
       </c>
@@ -16742,7 +16787,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>17</v>
       </c>
@@ -16756,7 +16801,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>17</v>
       </c>
@@ -16770,7 +16815,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>17</v>
       </c>
@@ -16790,7 +16835,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>17</v>
       </c>
@@ -16810,7 +16855,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>17</v>
       </c>
@@ -16830,7 +16875,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>17</v>
       </c>
@@ -16850,7 +16895,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>17</v>
       </c>
@@ -16870,7 +16915,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>17</v>
       </c>
@@ -16884,7 +16929,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>17</v>
       </c>
@@ -16898,7 +16943,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>17</v>
       </c>
@@ -16912,7 +16957,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>17</v>
       </c>
@@ -16932,7 +16977,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>17</v>
       </c>
@@ -16952,7 +16997,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>17</v>
       </c>
@@ -16972,7 +17017,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>17</v>
       </c>
@@ -16992,7 +17037,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>17</v>
       </c>
@@ -17012,7 +17057,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>17</v>
       </c>
@@ -17032,7 +17077,7 @@
         <v>1905</v>
       </c>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>17</v>
       </c>
@@ -17052,7 +17097,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>17</v>
       </c>
@@ -17072,7 +17117,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>17</v>
       </c>
@@ -17092,7 +17137,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>17</v>
       </c>
@@ -17112,7 +17157,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>17</v>
       </c>
@@ -17132,7 +17177,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>17</v>
       </c>
@@ -17152,7 +17197,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>17</v>
       </c>
@@ -17172,7 +17217,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>17</v>
       </c>
@@ -17192,7 +17237,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>17</v>
       </c>
@@ -17212,7 +17257,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>17</v>
       </c>
@@ -17232,7 +17277,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>17</v>
       </c>
@@ -17252,7 +17297,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>17</v>
       </c>
@@ -17272,7 +17317,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>17</v>
       </c>
@@ -17292,7 +17337,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>17</v>
       </c>
@@ -17312,7 +17357,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>17</v>
       </c>
@@ -17332,7 +17377,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>17</v>
       </c>
@@ -17352,7 +17397,7 @@
         <v>1921</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>17</v>
       </c>
@@ -17372,7 +17417,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>17</v>
       </c>
@@ -17392,7 +17437,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>17</v>
       </c>
@@ -17412,7 +17457,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>17</v>
       </c>
@@ -17432,7 +17477,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>17</v>
       </c>
@@ -17452,7 +17497,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>17</v>
       </c>
@@ -17472,7 +17517,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>17</v>
       </c>
@@ -17492,7 +17537,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>17</v>
       </c>
@@ -17512,7 +17557,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>17</v>
       </c>
@@ -17532,7 +17577,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>17</v>
       </c>
@@ -17552,7 +17597,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>17</v>
       </c>
@@ -17572,7 +17617,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>17</v>
       </c>
@@ -17592,7 +17637,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>17</v>
       </c>
@@ -17612,7 +17657,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>17</v>
       </c>
@@ -17632,7 +17677,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>17</v>
       </c>
@@ -17652,7 +17697,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>17</v>
       </c>
@@ -17672,7 +17717,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>17</v>
       </c>
@@ -17692,7 +17737,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>17</v>
       </c>
@@ -17712,7 +17757,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>17</v>
       </c>
@@ -17732,7 +17777,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>17</v>
       </c>
@@ -17752,7 +17797,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>17</v>
       </c>
@@ -17772,7 +17817,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>17</v>
       </c>
@@ -17792,7 +17837,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>17</v>
       </c>
@@ -17812,7 +17857,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>17</v>
       </c>
@@ -17832,7 +17877,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>17</v>
       </c>
@@ -17852,7 +17897,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>17</v>
       </c>
@@ -17872,7 +17917,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>17</v>
       </c>
@@ -17892,7 +17937,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>17</v>
       </c>
@@ -17912,7 +17957,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>17</v>
       </c>
@@ -17932,7 +17977,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>17</v>
       </c>
@@ -17952,7 +17997,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>17</v>
       </c>
@@ -17972,7 +18017,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>17</v>
       </c>
@@ -17992,7 +18037,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>17</v>
       </c>
@@ -18012,7 +18057,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>17</v>
       </c>
@@ -18032,7 +18077,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>17</v>
       </c>
@@ -18052,7 +18097,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>17</v>
       </c>
@@ -18072,7 +18117,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>17</v>
       </c>
@@ -18092,7 +18137,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>17</v>
       </c>
@@ -18112,7 +18157,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>17</v>
       </c>
@@ -18132,7 +18177,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>17</v>
       </c>
@@ -18152,7 +18197,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>17</v>
       </c>
@@ -18172,7 +18217,7 @@
         <v>1962</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>17</v>
       </c>
@@ -18192,7 +18237,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>17</v>
       </c>
@@ -18212,7 +18257,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>17</v>
       </c>
@@ -18232,7 +18277,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>17</v>
       </c>
@@ -18252,7 +18297,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>17</v>
       </c>
@@ -18272,7 +18317,7 @@
         <v>1967</v>
       </c>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>17</v>
       </c>
@@ -18292,7 +18337,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>17</v>
       </c>
@@ -18312,7 +18357,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>17</v>
       </c>
@@ -18332,7 +18377,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>17</v>
       </c>
@@ -18352,7 +18397,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>17</v>
       </c>
@@ -18372,7 +18417,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>17</v>
       </c>
@@ -18392,7 +18437,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>17</v>
       </c>
@@ -18412,7 +18457,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>17</v>
       </c>
@@ -18432,7 +18477,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>17</v>
       </c>
@@ -18452,7 +18497,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>17</v>
       </c>
@@ -18472,7 +18517,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>17</v>
       </c>
@@ -18492,7 +18537,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>17</v>
       </c>
@@ -18512,7 +18557,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>17</v>
       </c>
@@ -18532,7 +18577,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>17</v>
       </c>
@@ -18552,7 +18597,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>17</v>
       </c>
@@ -18572,7 +18617,7 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>17</v>
       </c>
@@ -18592,7 +18637,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>17</v>
       </c>
@@ -18612,7 +18657,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>17</v>
       </c>
@@ -18632,7 +18677,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>17</v>
       </c>
@@ -18652,7 +18697,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>17</v>
       </c>
@@ -18672,7 +18717,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>17</v>
       </c>
@@ -18692,7 +18737,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>17</v>
       </c>
@@ -18712,7 +18757,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>17</v>
       </c>
@@ -18732,7 +18777,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>17</v>
       </c>
@@ -18752,7 +18797,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>17</v>
       </c>
@@ -18772,7 +18817,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>17</v>
       </c>
@@ -18792,7 +18837,7 @@
         <v>1994</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>17</v>
       </c>
@@ -18812,7 +18857,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>17</v>
       </c>
@@ -18826,7 +18871,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>17</v>
       </c>
@@ -18840,7 +18885,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>17</v>
       </c>
@@ -18854,7 +18899,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>17</v>
       </c>
@@ -18868,7 +18913,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>17</v>
       </c>
@@ -18882,7 +18927,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>17</v>
       </c>
@@ -18896,7 +18941,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>17</v>
       </c>
@@ -18910,7 +18955,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="625" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>17</v>
       </c>
@@ -18924,7 +18969,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="626" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>17</v>
       </c>
@@ -18938,7 +18983,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="627" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>17</v>
       </c>
@@ -18952,7 +18997,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="628" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>17</v>
       </c>
@@ -18966,7 +19011,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="629" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>17</v>
       </c>
@@ -18980,7 +19025,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="630" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>17</v>
       </c>
@@ -18994,7 +19039,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="631" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>17</v>
       </c>
@@ -19008,7 +19053,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="632" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>17</v>
       </c>
@@ -19022,7 +19067,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="633" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>17</v>
       </c>
@@ -19036,7 +19081,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="634" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>17</v>
       </c>
@@ -19050,7 +19095,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="635" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>17</v>
       </c>
@@ -19064,7 +19109,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="636" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>17</v>
       </c>
@@ -19078,7 +19123,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="637" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>17</v>
       </c>
@@ -19092,7 +19137,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="638" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>17</v>
       </c>
@@ -19106,7 +19151,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="639" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>17</v>
       </c>
@@ -19120,7 +19165,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="640" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>17</v>
       </c>
@@ -19134,7 +19179,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="641" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>17</v>
       </c>
@@ -19148,7 +19193,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="642" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>17</v>
       </c>
@@ -19162,7 +19207,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="643" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>17</v>
       </c>
@@ -19176,7 +19221,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="644" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>17</v>
       </c>
@@ -19190,7 +19235,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="645" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>17</v>
       </c>
@@ -19204,7 +19249,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="646" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>17</v>
       </c>
@@ -19218,7 +19263,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="647" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>17</v>
       </c>
@@ -19232,7 +19277,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="648" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>17</v>
       </c>
@@ -19246,7 +19291,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="649" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>17</v>
       </c>
@@ -19260,7 +19305,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="650" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>17</v>
       </c>
@@ -19274,7 +19319,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="651" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>17</v>
       </c>
@@ -19288,7 +19333,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="652" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>17</v>
       </c>
@@ -19302,7 +19347,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="653" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>17</v>
       </c>
@@ -19316,7 +19361,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="654" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>17</v>
       </c>
@@ -19330,7 +19375,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="655" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>17</v>
       </c>
@@ -19344,7 +19389,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="656" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>17</v>
       </c>
@@ -19358,7 +19403,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>17</v>
       </c>
@@ -19378,7 +19423,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>17</v>
       </c>
@@ -19398,7 +19443,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>17</v>
       </c>
@@ -19418,7 +19463,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>17</v>
       </c>
@@ -19438,7 +19483,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>17</v>
       </c>
@@ -19452,7 +19497,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>17</v>
       </c>
@@ -19466,7 +19511,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>17</v>
       </c>
@@ -19480,7 +19525,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>17</v>
       </c>
@@ -19500,7 +19545,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>17</v>
       </c>
@@ -19520,7 +19565,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>17</v>
       </c>
@@ -19540,7 +19585,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>17</v>
       </c>
@@ -19560,7 +19605,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>17</v>
       </c>
@@ -19580,7 +19625,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>17</v>
       </c>
@@ -19600,7 +19645,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>17</v>
       </c>
@@ -19620,7 +19665,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>17</v>
       </c>
@@ -19640,7 +19685,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>17</v>
       </c>
@@ -19660,7 +19705,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>17</v>
       </c>
@@ -19674,7 +19719,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>17</v>
       </c>
@@ -19688,7 +19733,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>17</v>
       </c>
@@ -19702,7 +19747,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>17</v>
       </c>
@@ -19716,7 +19761,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>17</v>
       </c>
@@ -19730,7 +19775,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>17</v>
       </c>
@@ -19744,7 +19789,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>17</v>
       </c>
@@ -19758,7 +19803,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>17</v>
       </c>
@@ -19772,7 +19817,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>17</v>
       </c>
@@ -19786,7 +19831,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>17</v>
       </c>
@@ -19800,7 +19845,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>17</v>
       </c>
@@ -19814,7 +19859,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>17</v>
       </c>
@@ -19828,7 +19873,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>17</v>
       </c>
@@ -19842,7 +19887,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>17</v>
       </c>
@@ -19856,7 +19901,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>17</v>
       </c>
@@ -19876,7 +19921,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>17</v>
       </c>
@@ -19896,7 +19941,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>17</v>
       </c>
@@ -19916,7 +19961,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>17</v>
       </c>
@@ -19936,7 +19981,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>17</v>
       </c>
@@ -19956,7 +20001,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>17</v>
       </c>
@@ -19976,7 +20021,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>17</v>
       </c>
@@ -19996,7 +20041,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>17</v>
       </c>
@@ -20016,7 +20061,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>17</v>
       </c>
@@ -20036,7 +20081,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>17</v>
       </c>
@@ -20056,7 +20101,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>17</v>
       </c>
@@ -20076,7 +20121,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>17</v>
       </c>
@@ -20096,7 +20141,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>17</v>
       </c>
@@ -20116,7 +20161,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>17</v>
       </c>
@@ -20136,7 +20181,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>17</v>
       </c>
@@ -20156,7 +20201,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>17</v>
       </c>
@@ -20176,7 +20221,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>17</v>
       </c>
@@ -20190,7 +20235,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>17</v>
       </c>
@@ -20204,7 +20249,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>17</v>
       </c>
@@ -20218,7 +20263,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>17</v>
       </c>
@@ -20238,7 +20283,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>17</v>
       </c>
@@ -20258,7 +20303,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>17</v>
       </c>
@@ -20278,7 +20323,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>17</v>
       </c>
@@ -20298,7 +20343,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>17</v>
       </c>
@@ -20318,7 +20363,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>17</v>
       </c>
@@ -20338,7 +20383,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>17</v>
       </c>
@@ -20358,7 +20403,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>17</v>
       </c>
@@ -20378,7 +20423,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>17</v>
       </c>
@@ -20398,7 +20443,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>17</v>
       </c>
@@ -20418,7 +20463,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>17</v>
       </c>
@@ -20438,7 +20483,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>17</v>
       </c>
@@ -20458,7 +20503,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>17</v>
       </c>
@@ -20478,7 +20523,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>17</v>
       </c>
@@ -20498,7 +20543,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>17</v>
       </c>
@@ -20518,7 +20563,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>17</v>
       </c>
@@ -20538,7 +20583,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>17</v>
       </c>
@@ -20558,7 +20603,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>17</v>
       </c>
@@ -20578,7 +20623,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>17</v>
       </c>
@@ -20598,7 +20643,7 @@
         <v>1441</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>17</v>
       </c>
@@ -20618,7 +20663,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>17</v>
       </c>
@@ -20638,7 +20683,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>17</v>
       </c>
@@ -20658,7 +20703,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>17</v>
       </c>
@@ -20678,7 +20723,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>17</v>
       </c>
@@ -20698,7 +20743,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>17</v>
       </c>
@@ -20718,7 +20763,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>17</v>
       </c>
@@ -20738,7 +20783,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>17</v>
       </c>
@@ -20758,7 +20803,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>17</v>
       </c>
@@ -20778,7 +20823,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>17</v>
       </c>
@@ -20798,7 +20843,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>17</v>
       </c>
@@ -20818,7 +20863,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>17</v>
       </c>
@@ -20838,7 +20883,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>17</v>
       </c>
@@ -20858,7 +20903,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>17</v>
       </c>
@@ -20878,7 +20923,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>17</v>
       </c>
@@ -20898,7 +20943,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>17</v>
       </c>
@@ -20918,7 +20963,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>17</v>
       </c>
@@ -20938,7 +20983,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>17</v>
       </c>
@@ -20958,7 +21003,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>17</v>
       </c>
@@ -20978,7 +21023,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>17</v>
       </c>
@@ -20998,7 +21043,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>17</v>
       </c>
@@ -21018,7 +21063,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>17</v>
       </c>
@@ -21038,7 +21083,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>17</v>
       </c>
@@ -21058,7 +21103,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>17</v>
       </c>
@@ -21078,7 +21123,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>17</v>
       </c>
@@ -21098,7 +21143,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>17</v>
       </c>
@@ -21118,7 +21163,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>17</v>
       </c>
@@ -21138,7 +21183,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>17</v>
       </c>
@@ -21158,7 +21203,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>17</v>
       </c>
@@ -21178,7 +21223,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>17</v>
       </c>
@@ -21198,7 +21243,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>17</v>
       </c>
@@ -21218,7 +21263,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>17</v>
       </c>
@@ -21238,7 +21283,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>17</v>
       </c>
@@ -21258,7 +21303,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>17</v>
       </c>
@@ -21278,7 +21323,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>17</v>
       </c>
@@ -21298,7 +21343,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>17</v>
       </c>
@@ -21318,7 +21363,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>17</v>
       </c>
@@ -21338,7 +21383,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>17</v>
       </c>
@@ -21358,7 +21403,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>17</v>
       </c>
@@ -21378,7 +21423,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>17</v>
       </c>
@@ -21398,7 +21443,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>17</v>
       </c>
@@ -21418,7 +21463,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>17</v>
       </c>
@@ -21438,7 +21483,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>17</v>
       </c>
@@ -21458,7 +21503,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>17</v>
       </c>
@@ -21478,7 +21523,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>17</v>
       </c>
@@ -21498,7 +21543,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>17</v>
       </c>
@@ -21518,7 +21563,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>17</v>
       </c>
@@ -21538,7 +21583,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>17</v>
       </c>
@@ -21558,7 +21603,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>17</v>
       </c>
@@ -21578,7 +21623,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>17</v>
       </c>
@@ -21598,7 +21643,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>17</v>
       </c>
@@ -21618,7 +21663,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>17</v>
       </c>
@@ -21638,7 +21683,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>17</v>
       </c>
@@ -21658,7 +21703,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>17</v>
       </c>
@@ -21678,7 +21723,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>17</v>
       </c>
@@ -21698,7 +21743,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>17</v>
       </c>
@@ -21718,7 +21763,7 @@
         <v>1559</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>17</v>
       </c>
@@ -21738,7 +21783,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>17</v>
       </c>
@@ -21758,7 +21803,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>17</v>
       </c>
@@ -21778,7 +21823,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>17</v>
       </c>
@@ -21798,7 +21843,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>17</v>
       </c>
@@ -21818,7 +21863,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>17</v>
       </c>
@@ -21838,7 +21883,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>17</v>
       </c>
@@ -21858,7 +21903,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>17</v>
       </c>
@@ -21878,7 +21923,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>17</v>
       </c>
@@ -21898,7 +21943,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>17</v>
       </c>
@@ -21918,7 +21963,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>17</v>
       </c>
@@ -21938,7 +21983,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>17</v>
       </c>
@@ -21958,7 +22003,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>17</v>
       </c>
@@ -21978,7 +22023,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>17</v>
       </c>
@@ -21992,7 +22037,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>17</v>
       </c>
@@ -22012,7 +22057,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>17</v>
       </c>
@@ -22032,7 +22077,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>17</v>
       </c>
@@ -22046,7 +22091,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>17</v>
       </c>
@@ -22060,7 +22105,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>17</v>
       </c>
@@ -22074,7 +22119,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>17</v>
       </c>
@@ -22088,7 +22133,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="801" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>17</v>
       </c>
@@ -22102,7 +22147,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="802" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>17</v>
       </c>
@@ -22116,7 +22161,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="803" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>17</v>
       </c>
@@ -22130,7 +22175,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="804" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>17</v>
       </c>
@@ -22144,7 +22189,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="805" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>17</v>
       </c>
@@ -22158,7 +22203,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="806" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>17</v>
       </c>
@@ -22172,7 +22217,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="807" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>17</v>
       </c>
@@ -22186,7 +22231,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="808" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>17</v>
       </c>
@@ -22200,7 +22245,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="809" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>17</v>
       </c>
@@ -22214,7 +22259,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="810" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>17</v>
       </c>
@@ -22228,7 +22273,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="811" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>17</v>
       </c>
@@ -22242,7 +22287,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="812" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>17</v>
       </c>
@@ -22256,7 +22301,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="813" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>17</v>
       </c>
@@ -22270,7 +22315,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="814" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>17</v>
       </c>
@@ -22284,7 +22329,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="815" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>17</v>
       </c>
@@ -22298,7 +22343,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="816" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>17</v>
       </c>
@@ -22312,7 +22357,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>17</v>
       </c>
@@ -22326,7 +22371,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>17</v>
       </c>
@@ -22340,7 +22385,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>17</v>
       </c>
@@ -22354,7 +22399,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>17</v>
       </c>
@@ -22368,7 +22413,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>17</v>
       </c>
@@ -22388,7 +22433,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>17</v>
       </c>
@@ -22408,7 +22453,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>17</v>
       </c>
@@ -22428,7 +22473,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>17</v>
       </c>
@@ -22448,7 +22493,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>17</v>
       </c>
@@ -22468,7 +22513,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>17</v>
       </c>
@@ -22488,7 +22533,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>17</v>
       </c>
@@ -22508,7 +22553,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>17</v>
       </c>
@@ -22528,7 +22573,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>17</v>
       </c>
@@ -22548,7 +22593,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>17</v>
       </c>
@@ -22568,7 +22613,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>17</v>
       </c>
@@ -22588,7 +22633,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>17</v>
       </c>
@@ -22608,7 +22653,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="833" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>17</v>
       </c>
@@ -22628,7 +22673,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="834" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>17</v>
       </c>
@@ -22642,7 +22687,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="835" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>17</v>
       </c>
@@ -22656,7 +22701,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="836" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>17</v>
       </c>
@@ -22676,7 +22721,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="837" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>17</v>
       </c>
@@ -22696,7 +22741,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="838" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>17</v>
       </c>
@@ -22716,7 +22761,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="839" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>17</v>
       </c>
@@ -22736,7 +22781,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="840" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>17</v>
       </c>
@@ -22756,7 +22801,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="841" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>17</v>
       </c>
@@ -22791,7 +22836,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="842" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>17</v>
       </c>
@@ -22826,7 +22871,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="843" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>17</v>
       </c>
@@ -22861,7 +22906,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="844" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>17</v>
       </c>
@@ -22875,7 +22920,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="845" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>17</v>
       </c>
@@ -22889,7 +22934,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="846" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>17</v>
       </c>
@@ -22903,7 +22948,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="847" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>17</v>
       </c>
@@ -22917,7 +22962,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="848" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>17</v>
       </c>
@@ -22931,7 +22976,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>17</v>
       </c>
@@ -22945,7 +22990,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>17</v>
       </c>
@@ -22959,7 +23004,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>17</v>
       </c>
@@ -22979,7 +23024,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>17</v>
       </c>
@@ -22999,7 +23044,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>17</v>
       </c>
@@ -23019,7 +23064,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>17</v>
       </c>
@@ -23039,7 +23084,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>17</v>
       </c>
@@ -23059,7 +23104,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>17</v>
       </c>
@@ -23079,7 +23124,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>17</v>
       </c>
@@ -23099,7 +23144,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>17</v>
       </c>
@@ -23119,7 +23164,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>17</v>
       </c>
@@ -23139,7 +23184,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>17</v>
       </c>
@@ -23159,7 +23204,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>17</v>
       </c>
@@ -23179,7 +23224,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>17</v>
       </c>
@@ -23199,7 +23244,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>17</v>
       </c>
@@ -23219,7 +23264,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>17</v>
       </c>
@@ -23239,7 +23284,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>17</v>
       </c>
@@ -23259,7 +23304,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>17</v>
       </c>
@@ -23279,7 +23324,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="867" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>17</v>
       </c>
@@ -23299,7 +23344,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="868" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>17</v>
       </c>
@@ -23319,7 +23364,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="869" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>17</v>
       </c>
@@ -23339,7 +23384,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="870" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>17</v>
       </c>
@@ -23359,7 +23404,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="871" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>17</v>
       </c>
@@ -23379,7 +23424,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="872" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>17</v>
       </c>
@@ -23399,7 +23444,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="873" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>17</v>
       </c>
@@ -23419,7 +23464,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="874" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>17</v>
       </c>
@@ -23439,7 +23484,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="875" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>17</v>
       </c>
@@ -23459,7 +23504,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="876" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>17</v>
       </c>
@@ -23479,7 +23524,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="877" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>17</v>
       </c>
@@ -23499,7 +23544,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="878" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>17</v>
       </c>
@@ -23519,7 +23564,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="879" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>17</v>
       </c>
@@ -23539,7 +23584,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="880" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>17</v>
       </c>
@@ -23559,7 +23604,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="881" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>17</v>
       </c>
@@ -23579,7 +23624,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="882" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>17</v>
       </c>
@@ -23599,7 +23644,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="883" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>17</v>
       </c>
@@ -23619,7 +23664,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="884" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>17</v>
       </c>
@@ -23639,7 +23684,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="885" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>17</v>
       </c>
@@ -23659,7 +23704,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="886" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>17</v>
       </c>
@@ -23679,7 +23724,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="887" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>17</v>
       </c>
@@ -23699,7 +23744,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="888" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>17</v>
       </c>
@@ -23719,7 +23764,7 @@
         <v>1765</v>
       </c>
     </row>
-    <row r="889" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>17</v>
       </c>
@@ -23739,7 +23784,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="890" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>17</v>
       </c>
@@ -23759,7 +23804,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="891" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>17</v>
       </c>
@@ -23779,7 +23824,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="892" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>17</v>
       </c>
@@ -23799,7 +23844,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="893" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>17</v>
       </c>
@@ -23819,7 +23864,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="894" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>17</v>
       </c>
@@ -23839,7 +23884,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="895" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>17</v>
       </c>
@@ -23859,7 +23904,7 @@
         <v>1777</v>
       </c>
     </row>
-    <row r="896" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>17</v>
       </c>
@@ -23879,7 +23924,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="897" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>17</v>
       </c>
@@ -23899,7 +23944,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="898" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>17</v>
       </c>
@@ -23919,7 +23964,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="899" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>17</v>
       </c>
@@ -23939,7 +23984,7 @@
         <v>1781</v>
       </c>
     </row>
-    <row r="900" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>17</v>
       </c>
@@ -23959,7 +24004,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="901" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>17</v>
       </c>
@@ -23979,7 +24024,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="902" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>17</v>
       </c>
@@ -23999,7 +24044,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="903" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>17</v>
       </c>
@@ -24019,7 +24064,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="904" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>17</v>
       </c>
@@ -24039,7 +24084,7 @@
         <v>1791</v>
       </c>
     </row>
-    <row r="905" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>17</v>
       </c>
@@ -24059,7 +24104,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="906" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>17</v>
       </c>
@@ -24079,7 +24124,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="907" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>17</v>
       </c>
@@ -24099,7 +24144,7 @@
         <v>1797</v>
       </c>
     </row>
-    <row r="908" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>17</v>
       </c>
@@ -24119,7 +24164,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="909" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>17</v>
       </c>
@@ -24139,7 +24184,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="910" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>17</v>
       </c>
@@ -24159,7 +24204,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="911" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>17</v>
       </c>
@@ -24173,7 +24218,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="912" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>17</v>
       </c>
@@ -24187,7 +24232,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="913" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>17</v>
       </c>
@@ -24201,7 +24246,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="914" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>17</v>
       </c>
@@ -24215,7 +24260,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="915" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>17</v>
       </c>
@@ -24235,7 +24280,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="916" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>17</v>
       </c>
@@ -24255,7 +24300,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="917" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>17</v>
       </c>
@@ -24275,7 +24320,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="918" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>17</v>
       </c>
@@ -24295,7 +24340,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="919" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>17</v>
       </c>
@@ -24315,7 +24360,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="920" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>17</v>
       </c>
@@ -24335,7 +24380,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="921" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>17</v>
       </c>
@@ -24355,7 +24400,7 @@
         <v>1820</v>
       </c>
     </row>
-    <row r="922" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>17</v>
       </c>
@@ -24375,7 +24420,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="923" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>17</v>
       </c>
@@ -24395,7 +24440,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="924" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>17</v>
       </c>
@@ -24415,7 +24460,7 @@
         <v>1826</v>
       </c>
     </row>
-    <row r="925" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>17</v>
       </c>
@@ -24435,7 +24480,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="926" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>17</v>
       </c>
@@ -24455,7 +24500,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="927" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>17</v>
       </c>
@@ -24475,7 +24520,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="928" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>17</v>
       </c>
@@ -24495,7 +24540,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="929" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>17</v>
       </c>
@@ -24515,7 +24560,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="930" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>17</v>
       </c>
@@ -24535,7 +24580,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="931" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>17</v>
       </c>
@@ -24549,7 +24594,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="932" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>17</v>
       </c>
@@ -24563,7 +24608,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="933" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>17</v>
       </c>
@@ -24577,7 +24622,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="934" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>17</v>
       </c>
@@ -24591,7 +24636,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="935" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>17</v>
       </c>
@@ -24605,7 +24650,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="936" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>17</v>
       </c>
@@ -24619,7 +24664,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="937" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>17</v>
       </c>
@@ -24633,7 +24678,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="938" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>17</v>
       </c>
@@ -24647,7 +24692,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="939" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>17</v>
       </c>
@@ -24661,7 +24706,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="940" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>17</v>
       </c>
@@ -24675,7 +24720,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="941" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>17</v>
       </c>
@@ -24689,7 +24734,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="942" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>17</v>
       </c>
@@ -24703,7 +24748,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="943" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>17</v>
       </c>
@@ -24717,7 +24762,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="944" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>17</v>
       </c>
@@ -24731,7 +24776,7 @@
         <v>1850</v>
       </c>
     </row>
-    <row r="945" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>17</v>
       </c>
@@ -24745,7 +24790,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="946" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>17</v>
       </c>
@@ -24759,7 +24804,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="947" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>17</v>
       </c>
@@ -24773,7 +24818,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="948" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>17</v>
       </c>
@@ -24787,7 +24832,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="949" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>17</v>
       </c>
@@ -24800,8 +24845,14 @@
       <c r="D949" t="s">
         <v>1855</v>
       </c>
-    </row>
-    <row r="950" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G949" t="s">
+        <v>1855</v>
+      </c>
+      <c r="I949" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="950" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>17</v>
       </c>
@@ -24815,13 +24866,13 @@
         <v>1856</v>
       </c>
       <c r="G950" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="I950" t="s">
         <v>1885</v>
       </c>
     </row>
-    <row r="951" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>17</v>
       </c>
@@ -24834,8 +24885,14 @@
       <c r="D951" t="s">
         <v>1857</v>
       </c>
-    </row>
-    <row r="952" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G951" t="s">
+        <v>1857</v>
+      </c>
+      <c r="I951" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="952" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>17</v>
       </c>
@@ -24849,13 +24906,13 @@
         <v>1858</v>
       </c>
       <c r="G952" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="I952" t="s">
         <v>1886</v>
       </c>
     </row>
-    <row r="953" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>17</v>
       </c>
@@ -24868,8 +24925,14 @@
       <c r="D953" t="s">
         <v>1859</v>
       </c>
-    </row>
-    <row r="954" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G953" t="s">
+        <v>1859</v>
+      </c>
+      <c r="I953" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="954" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>17</v>
       </c>
@@ -24883,13 +24946,13 @@
         <v>1860</v>
       </c>
       <c r="G954" t="s">
-        <v>1860</v>
+        <v>1865</v>
       </c>
       <c r="I954" t="s">
         <v>1887</v>
       </c>
     </row>
-    <row r="955" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>17</v>
       </c>
@@ -24902,8 +24965,14 @@
       <c r="D955" t="s">
         <v>1861</v>
       </c>
-    </row>
-    <row r="956" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G955" t="s">
+        <v>1861</v>
+      </c>
+      <c r="I955" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="956" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>17</v>
       </c>
@@ -24917,13 +24986,13 @@
         <v>1862</v>
       </c>
       <c r="G956" t="s">
-        <v>1862</v>
+        <v>1869</v>
       </c>
       <c r="I956" t="s">
         <v>1888</v>
       </c>
     </row>
-    <row r="957" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>17</v>
       </c>
@@ -24936,8 +25005,14 @@
       <c r="D957" t="s">
         <v>1863</v>
       </c>
-    </row>
-    <row r="958" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G957" t="s">
+        <v>1863</v>
+      </c>
+      <c r="I957" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="958" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>17</v>
       </c>
@@ -24951,13 +25026,13 @@
         <v>1864</v>
       </c>
       <c r="G958" t="s">
-        <v>1864</v>
+        <v>1873</v>
       </c>
       <c r="I958" t="s">
         <v>1889</v>
       </c>
     </row>
-    <row r="959" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>17</v>
       </c>
@@ -24970,8 +25045,14 @@
       <c r="D959" t="s">
         <v>1865</v>
       </c>
-    </row>
-    <row r="960" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G959" t="s">
+        <v>1865</v>
+      </c>
+      <c r="I959" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="960" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>17</v>
       </c>
@@ -24985,13 +25066,13 @@
         <v>1866</v>
       </c>
       <c r="G960" t="s">
-        <v>1866</v>
+        <v>1877</v>
       </c>
       <c r="I960" t="s">
         <v>1890</v>
       </c>
     </row>
-    <row r="961" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>17</v>
       </c>
@@ -25004,8 +25085,14 @@
       <c r="D961" t="s">
         <v>1867</v>
       </c>
-    </row>
-    <row r="962" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G961" t="s">
+        <v>1867</v>
+      </c>
+      <c r="I961" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="962" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>17</v>
       </c>
@@ -25019,13 +25106,13 @@
         <v>1868</v>
       </c>
       <c r="G962" t="s">
-        <v>1868</v>
+        <v>1881</v>
       </c>
       <c r="I962" t="s">
         <v>1891</v>
       </c>
     </row>
-    <row r="963" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>17</v>
       </c>
@@ -25038,8 +25125,14 @@
       <c r="D963" t="s">
         <v>1869</v>
       </c>
-    </row>
-    <row r="964" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G963" t="s">
+        <v>1869</v>
+      </c>
+      <c r="I963" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="964" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>17</v>
       </c>
@@ -25059,7 +25152,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="965" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>17</v>
       </c>
@@ -25072,8 +25165,14 @@
       <c r="D965" t="s">
         <v>1871</v>
       </c>
-    </row>
-    <row r="966" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G965" t="s">
+        <v>1871</v>
+      </c>
+      <c r="I965" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="966" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>17</v>
       </c>
@@ -25093,7 +25192,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="967" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>17</v>
       </c>
@@ -25106,8 +25205,14 @@
       <c r="D967" t="s">
         <v>1873</v>
       </c>
-    </row>
-    <row r="968" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G967" t="s">
+        <v>1873</v>
+      </c>
+      <c r="I967" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="968" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>17</v>
       </c>
@@ -25127,7 +25232,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="969" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>17</v>
       </c>
@@ -25140,8 +25245,14 @@
       <c r="D969" t="s">
         <v>1875</v>
       </c>
-    </row>
-    <row r="970" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G969" t="s">
+        <v>1875</v>
+      </c>
+      <c r="I969" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="970" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>17</v>
       </c>
@@ -25161,7 +25272,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="971" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>17</v>
       </c>
@@ -25174,8 +25285,14 @@
       <c r="D971" t="s">
         <v>1877</v>
       </c>
-    </row>
-    <row r="972" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G971" t="s">
+        <v>1877</v>
+      </c>
+      <c r="I971" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="972" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>17</v>
       </c>
@@ -25195,7 +25312,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="973" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>17</v>
       </c>
@@ -25208,8 +25325,14 @@
       <c r="D973" t="s">
         <v>1879</v>
       </c>
-    </row>
-    <row r="974" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G973" t="s">
+        <v>1879</v>
+      </c>
+      <c r="I973" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="974" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>17</v>
       </c>
@@ -25229,7 +25352,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="975" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>17</v>
       </c>
@@ -25242,8 +25365,14 @@
       <c r="D975" t="s">
         <v>1881</v>
       </c>
-    </row>
-    <row r="976" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G975" t="s">
+        <v>1881</v>
+      </c>
+      <c r="I975" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="976" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>17</v>
       </c>
@@ -25263,7 +25392,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="977" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>17</v>
       </c>
@@ -25276,8 +25405,14 @@
       <c r="D977" t="s">
         <v>1883</v>
       </c>
-    </row>
-    <row r="978" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G977" t="s">
+        <v>1883</v>
+      </c>
+      <c r="I977" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="978" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>17</v>
       </c>
@@ -25300,11 +25435,10 @@
   </sheetData>
   <autoFilter ref="A1:Q978" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/_Localizations.xlsx
+++ b/_Localizations.xlsx
@@ -3676,6 +3676,9 @@
   </x:si>
   <x:si>
     <x:t>Auf dem Markt habe ich schon ruhigere Menschenmengen gesehen.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>我在市場上見過比這更平靜的人群。</x:t>
   </x:si>
   <x:si>
     <x:t>Dust everywhere, and nowhere to sit.</x:t>
@@ -17583,6 +17586,9 @@
       <x:c r="I536" s="0" t="s">
         <x:v>1219</x:v>
       </x:c>
+      <x:c r="Q536" s="0" t="s">
+        <x:v>1220</x:v>
+      </x:c>
     </x:row>
     <x:row r="537" spans="1:17">
       <x:c r="A537" s="0" t="s">
@@ -17595,13 +17601,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D537" s="0" t="s">
-        <x:v>1220</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="G537" s="0" t="s">
-        <x:v>1220</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="I537" s="0" t="s">
-        <x:v>1221</x:v>
+        <x:v>1222</x:v>
       </x:c>
     </x:row>
     <x:row r="538" spans="1:17">
@@ -17615,13 +17621,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D538" s="0" t="s">
-        <x:v>1222</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="G538" s="0" t="s">
-        <x:v>1222</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="I538" s="0" t="s">
-        <x:v>1223</x:v>
+        <x:v>1224</x:v>
       </x:c>
     </x:row>
     <x:row r="539" spans="1:17">
@@ -17635,13 +17641,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D539" s="0" t="s">
-        <x:v>1224</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="G539" s="0" t="s">
-        <x:v>1224</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="I539" s="0" t="s">
-        <x:v>1225</x:v>
+        <x:v>1226</x:v>
       </x:c>
     </x:row>
     <x:row r="540" spans="1:17">
@@ -17655,13 +17661,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D540" s="0" t="s">
-        <x:v>1226</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="G540" s="0" t="s">
-        <x:v>1226</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="I540" s="0" t="s">
-        <x:v>1227</x:v>
+        <x:v>1228</x:v>
       </x:c>
     </x:row>
     <x:row r="541" spans="1:17">
@@ -17675,13 +17681,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D541" s="0" t="s">
-        <x:v>1228</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="G541" s="0" t="s">
-        <x:v>1228</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="I541" s="0" t="s">
-        <x:v>1229</x:v>
+        <x:v>1230</x:v>
       </x:c>
     </x:row>
     <x:row r="542" spans="1:17">
@@ -17695,13 +17701,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D542" s="0" t="s">
-        <x:v>1230</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="G542" s="0" t="s">
-        <x:v>1230</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="I542" s="0" t="s">
-        <x:v>1231</x:v>
+        <x:v>1232</x:v>
       </x:c>
     </x:row>
     <x:row r="543" spans="1:17">
@@ -17715,13 +17721,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D543" s="0" t="s">
-        <x:v>1232</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="G543" s="0" t="s">
-        <x:v>1232</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="I543" s="0" t="s">
-        <x:v>1233</x:v>
+        <x:v>1234</x:v>
       </x:c>
     </x:row>
     <x:row r="544" spans="1:17">
@@ -17735,13 +17741,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D544" s="0" t="s">
-        <x:v>1234</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="G544" s="0" t="s">
-        <x:v>1234</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="I544" s="0" t="s">
-        <x:v>1235</x:v>
+        <x:v>1236</x:v>
       </x:c>
     </x:row>
     <x:row r="545" spans="1:17">
@@ -17755,13 +17761,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D545" s="0" t="s">
-        <x:v>1236</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="G545" s="0" t="s">
-        <x:v>1236</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="I545" s="0" t="s">
-        <x:v>1237</x:v>
+        <x:v>1238</x:v>
       </x:c>
     </x:row>
     <x:row r="546" spans="1:17">
@@ -17775,13 +17781,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D546" s="0" t="s">
-        <x:v>1238</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="G546" s="0" t="s">
-        <x:v>1238</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="I546" s="0" t="s">
-        <x:v>1239</x:v>
+        <x:v>1240</x:v>
       </x:c>
     </x:row>
     <x:row r="547" spans="1:17">
@@ -17795,13 +17801,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D547" s="0" t="s">
-        <x:v>1240</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="G547" s="0" t="s">
-        <x:v>1240</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="I547" s="0" t="s">
-        <x:v>1241</x:v>
+        <x:v>1242</x:v>
       </x:c>
     </x:row>
     <x:row r="548" spans="1:17">
@@ -17815,13 +17821,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D548" s="0" t="s">
-        <x:v>1242</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="G548" s="0" t="s">
-        <x:v>1242</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="I548" s="0" t="s">
-        <x:v>1243</x:v>
+        <x:v>1244</x:v>
       </x:c>
     </x:row>
     <x:row r="549" spans="1:17">
@@ -17835,13 +17841,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D549" s="0" t="s">
-        <x:v>1244</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="G549" s="0" t="s">
-        <x:v>1244</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="I549" s="0" t="s">
-        <x:v>1245</x:v>
+        <x:v>1246</x:v>
       </x:c>
     </x:row>
     <x:row r="550" spans="1:17">
@@ -17855,13 +17861,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D550" s="0" t="s">
-        <x:v>1246</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="G550" s="0" t="s">
-        <x:v>1246</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="I550" s="0" t="s">
-        <x:v>1247</x:v>
+        <x:v>1248</x:v>
       </x:c>
     </x:row>
     <x:row r="551" spans="1:17">
@@ -17875,13 +17881,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D551" s="0" t="s">
-        <x:v>1248</x:v>
+        <x:v>1249</x:v>
       </x:c>
       <x:c r="G551" s="0" t="s">
-        <x:v>1248</x:v>
+        <x:v>1249</x:v>
       </x:c>
       <x:c r="I551" s="0" t="s">
-        <x:v>1249</x:v>
+        <x:v>1250</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:17">
@@ -17895,13 +17901,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D552" s="0" t="s">
-        <x:v>1250</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="G552" s="0" t="s">
-        <x:v>1250</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="I552" s="0" t="s">
-        <x:v>1251</x:v>
+        <x:v>1252</x:v>
       </x:c>
     </x:row>
     <x:row r="553" spans="1:17">
@@ -17915,13 +17921,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D553" s="0" t="s">
-        <x:v>1252</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="G553" s="0" t="s">
-        <x:v>1252</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="I553" s="0" t="s">
-        <x:v>1253</x:v>
+        <x:v>1254</x:v>
       </x:c>
     </x:row>
     <x:row r="554" spans="1:17">
@@ -17935,13 +17941,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D554" s="0" t="s">
-        <x:v>1254</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="G554" s="0" t="s">
-        <x:v>1254</x:v>
+        <x:v>1255</x:v>
       </x:c>
       <x:c r="I554" s="0" t="s">
-        <x:v>1255</x:v>
+        <x:v>1256</x:v>
       </x:c>
     </x:row>
     <x:row r="555" spans="1:17">
@@ -17955,13 +17961,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D555" s="0" t="s">
-        <x:v>1256</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="G555" s="0" t="s">
-        <x:v>1256</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="I555" s="0" t="s">
-        <x:v>1257</x:v>
+        <x:v>1258</x:v>
       </x:c>
     </x:row>
     <x:row r="556" spans="1:17">
@@ -17975,13 +17981,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D556" s="0" t="s">
-        <x:v>1258</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="G556" s="0" t="s">
-        <x:v>1258</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="I556" s="0" t="s">
-        <x:v>1259</x:v>
+        <x:v>1260</x:v>
       </x:c>
     </x:row>
     <x:row r="557" spans="1:17">
@@ -17995,13 +18001,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D557" s="0" t="s">
-        <x:v>1260</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="G557" s="0" t="s">
-        <x:v>1260</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="I557" s="0" t="s">
-        <x:v>1261</x:v>
+        <x:v>1262</x:v>
       </x:c>
     </x:row>
     <x:row r="558" spans="1:17">
@@ -18015,13 +18021,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D558" s="0" t="s">
-        <x:v>1262</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="G558" s="0" t="s">
-        <x:v>1262</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="I558" s="0" t="s">
-        <x:v>1263</x:v>
+        <x:v>1264</x:v>
       </x:c>
     </x:row>
     <x:row r="559" spans="1:17">
@@ -18035,13 +18041,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D559" s="0" t="s">
-        <x:v>1264</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="G559" s="0" t="s">
-        <x:v>1264</x:v>
+        <x:v>1265</x:v>
       </x:c>
       <x:c r="I559" s="0" t="s">
-        <x:v>1265</x:v>
+        <x:v>1266</x:v>
       </x:c>
     </x:row>
     <x:row r="560" spans="1:17">
@@ -18055,13 +18061,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D560" s="0" t="s">
-        <x:v>1266</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="G560" s="0" t="s">
-        <x:v>1266</x:v>
+        <x:v>1267</x:v>
       </x:c>
       <x:c r="I560" s="0" t="s">
-        <x:v>1267</x:v>
+        <x:v>1268</x:v>
       </x:c>
     </x:row>
     <x:row r="561" spans="1:17">
@@ -18075,13 +18081,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D561" s="0" t="s">
-        <x:v>1268</x:v>
+        <x:v>1269</x:v>
       </x:c>
       <x:c r="G561" s="0" t="s">
-        <x:v>1268</x:v>
+        <x:v>1269</x:v>
       </x:c>
       <x:c r="I561" s="0" t="s">
-        <x:v>1269</x:v>
+        <x:v>1270</x:v>
       </x:c>
     </x:row>
     <x:row r="562" spans="1:17">
@@ -18095,13 +18101,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D562" s="0" t="s">
-        <x:v>1270</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="G562" s="0" t="s">
-        <x:v>1270</x:v>
+        <x:v>1271</x:v>
       </x:c>
       <x:c r="I562" s="0" t="s">
-        <x:v>1271</x:v>
+        <x:v>1272</x:v>
       </x:c>
     </x:row>
     <x:row r="563" spans="1:17">
@@ -18115,13 +18121,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D563" s="0" t="s">
-        <x:v>1272</x:v>
+        <x:v>1273</x:v>
       </x:c>
       <x:c r="G563" s="0" t="s">
-        <x:v>1272</x:v>
+        <x:v>1273</x:v>
       </x:c>
       <x:c r="I563" s="0" t="s">
-        <x:v>1273</x:v>
+        <x:v>1274</x:v>
       </x:c>
     </x:row>
     <x:row r="564" spans="1:17">
@@ -18135,13 +18141,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D564" s="0" t="s">
-        <x:v>1274</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="G564" s="0" t="s">
-        <x:v>1274</x:v>
+        <x:v>1275</x:v>
       </x:c>
       <x:c r="I564" s="0" t="s">
-        <x:v>1275</x:v>
+        <x:v>1276</x:v>
       </x:c>
     </x:row>
     <x:row r="565" spans="1:17">
@@ -18155,13 +18161,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D565" s="0" t="s">
-        <x:v>1276</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="G565" s="0" t="s">
-        <x:v>1276</x:v>
+        <x:v>1277</x:v>
       </x:c>
       <x:c r="I565" s="0" t="s">
-        <x:v>1277</x:v>
+        <x:v>1278</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:17">
@@ -18175,13 +18181,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D566" s="0" t="s">
-        <x:v>1278</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="G566" s="0" t="s">
-        <x:v>1278</x:v>
+        <x:v>1279</x:v>
       </x:c>
       <x:c r="I566" s="0" t="s">
-        <x:v>1279</x:v>
+        <x:v>1280</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:17">
@@ -18195,13 +18201,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D567" s="0" t="s">
-        <x:v>1280</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="G567" s="0" t="s">
-        <x:v>1280</x:v>
+        <x:v>1281</x:v>
       </x:c>
       <x:c r="I567" s="0" t="s">
-        <x:v>1281</x:v>
+        <x:v>1282</x:v>
       </x:c>
     </x:row>
     <x:row r="568" spans="1:17">
@@ -18215,13 +18221,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D568" s="0" t="s">
-        <x:v>1282</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="G568" s="0" t="s">
-        <x:v>1282</x:v>
+        <x:v>1283</x:v>
       </x:c>
       <x:c r="I568" s="0" t="s">
-        <x:v>1283</x:v>
+        <x:v>1284</x:v>
       </x:c>
     </x:row>
     <x:row r="569" spans="1:17">
@@ -18235,13 +18241,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D569" s="0" t="s">
-        <x:v>1284</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="G569" s="0" t="s">
-        <x:v>1284</x:v>
+        <x:v>1285</x:v>
       </x:c>
       <x:c r="I569" s="0" t="s">
-        <x:v>1285</x:v>
+        <x:v>1286</x:v>
       </x:c>
     </x:row>
     <x:row r="570" spans="1:17">
@@ -18255,13 +18261,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D570" s="0" t="s">
-        <x:v>1286</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="G570" s="0" t="s">
-        <x:v>1286</x:v>
+        <x:v>1287</x:v>
       </x:c>
       <x:c r="I570" s="0" t="s">
-        <x:v>1287</x:v>
+        <x:v>1288</x:v>
       </x:c>
     </x:row>
     <x:row r="571" spans="1:17">
@@ -18275,13 +18281,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D571" s="0" t="s">
-        <x:v>1288</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="G571" s="0" t="s">
-        <x:v>1288</x:v>
+        <x:v>1289</x:v>
       </x:c>
       <x:c r="I571" s="0" t="s">
-        <x:v>1289</x:v>
+        <x:v>1290</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:17">
@@ -18295,13 +18301,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D572" s="0" t="s">
-        <x:v>1290</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="G572" s="0" t="s">
-        <x:v>1290</x:v>
+        <x:v>1291</x:v>
       </x:c>
       <x:c r="I572" s="0" t="s">
-        <x:v>1291</x:v>
+        <x:v>1292</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:17">
@@ -18315,13 +18321,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D573" s="0" t="s">
-        <x:v>1292</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="G573" s="0" t="s">
-        <x:v>1292</x:v>
+        <x:v>1293</x:v>
       </x:c>
       <x:c r="I573" s="0" t="s">
-        <x:v>1293</x:v>
+        <x:v>1294</x:v>
       </x:c>
     </x:row>
     <x:row r="574" spans="1:17">
@@ -18335,13 +18341,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D574" s="0" t="s">
-        <x:v>1294</x:v>
+        <x:v>1295</x:v>
       </x:c>
       <x:c r="G574" s="0" t="s">
-        <x:v>1294</x:v>
+        <x:v>1295</x:v>
       </x:c>
       <x:c r="I574" s="0" t="s">
-        <x:v>1295</x:v>
+        <x:v>1296</x:v>
       </x:c>
     </x:row>
     <x:row r="575" spans="1:17">
@@ -18355,13 +18361,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D575" s="0" t="s">
-        <x:v>1296</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="G575" s="0" t="s">
-        <x:v>1296</x:v>
+        <x:v>1297</x:v>
       </x:c>
       <x:c r="I575" s="0" t="s">
-        <x:v>1297</x:v>
+        <x:v>1298</x:v>
       </x:c>
     </x:row>
     <x:row r="576" spans="1:17">
@@ -18375,13 +18381,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D576" s="0" t="s">
-        <x:v>1298</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="G576" s="0" t="s">
-        <x:v>1298</x:v>
+        <x:v>1299</x:v>
       </x:c>
       <x:c r="I576" s="0" t="s">
-        <x:v>1299</x:v>
+        <x:v>1300</x:v>
       </x:c>
     </x:row>
     <x:row r="577" spans="1:17">
@@ -18395,13 +18401,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D577" s="0" t="s">
-        <x:v>1300</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="G577" s="0" t="s">
-        <x:v>1300</x:v>
+        <x:v>1301</x:v>
       </x:c>
       <x:c r="I577" s="0" t="s">
-        <x:v>1301</x:v>
+        <x:v>1302</x:v>
       </x:c>
     </x:row>
     <x:row r="578" spans="1:17">
@@ -18415,13 +18421,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D578" s="0" t="s">
-        <x:v>1302</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="G578" s="0" t="s">
-        <x:v>1302</x:v>
+        <x:v>1303</x:v>
       </x:c>
       <x:c r="I578" s="0" t="s">
-        <x:v>1303</x:v>
+        <x:v>1304</x:v>
       </x:c>
     </x:row>
     <x:row r="579" spans="1:17">
@@ -18435,13 +18441,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D579" s="0" t="s">
-        <x:v>1304</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="G579" s="0" t="s">
-        <x:v>1304</x:v>
+        <x:v>1305</x:v>
       </x:c>
       <x:c r="I579" s="0" t="s">
-        <x:v>1305</x:v>
+        <x:v>1306</x:v>
       </x:c>
     </x:row>
     <x:row r="580" spans="1:17">
@@ -18455,13 +18461,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D580" s="0" t="s">
-        <x:v>1306</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="G580" s="0" t="s">
-        <x:v>1306</x:v>
+        <x:v>1307</x:v>
       </x:c>
       <x:c r="I580" s="0" t="s">
-        <x:v>1307</x:v>
+        <x:v>1308</x:v>
       </x:c>
     </x:row>
     <x:row r="581" spans="1:17">
@@ -18475,13 +18481,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D581" s="0" t="s">
-        <x:v>1308</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="G581" s="0" t="s">
-        <x:v>1308</x:v>
+        <x:v>1309</x:v>
       </x:c>
       <x:c r="I581" s="0" t="s">
-        <x:v>1309</x:v>
+        <x:v>1310</x:v>
       </x:c>
     </x:row>
     <x:row r="582" spans="1:17">
@@ -18495,13 +18501,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D582" s="0" t="s">
-        <x:v>1310</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="G582" s="0" t="s">
-        <x:v>1310</x:v>
+        <x:v>1311</x:v>
       </x:c>
       <x:c r="I582" s="0" t="s">
-        <x:v>1311</x:v>
+        <x:v>1312</x:v>
       </x:c>
     </x:row>
     <x:row r="583" spans="1:17">
@@ -18515,13 +18521,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D583" s="0" t="s">
-        <x:v>1312</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="G583" s="0" t="s">
-        <x:v>1312</x:v>
+        <x:v>1313</x:v>
       </x:c>
       <x:c r="I583" s="0" t="s">
-        <x:v>1313</x:v>
+        <x:v>1314</x:v>
       </x:c>
     </x:row>
     <x:row r="584" spans="1:17">
@@ -18535,13 +18541,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D584" s="0" t="s">
-        <x:v>1314</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="G584" s="0" t="s">
-        <x:v>1314</x:v>
+        <x:v>1315</x:v>
       </x:c>
       <x:c r="I584" s="0" t="s">
-        <x:v>1315</x:v>
+        <x:v>1316</x:v>
       </x:c>
     </x:row>
     <x:row r="585" spans="1:17">
@@ -18555,13 +18561,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D585" s="0" t="s">
-        <x:v>1316</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="G585" s="0" t="s">
-        <x:v>1316</x:v>
+        <x:v>1317</x:v>
       </x:c>
       <x:c r="I585" s="0" t="s">
-        <x:v>1317</x:v>
+        <x:v>1318</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:17">
@@ -18575,13 +18581,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D586" s="0" t="s">
-        <x:v>1318</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="G586" s="0" t="s">
-        <x:v>1318</x:v>
+        <x:v>1319</x:v>
       </x:c>
       <x:c r="I586" s="0" t="s">
-        <x:v>1319</x:v>
+        <x:v>1320</x:v>
       </x:c>
     </x:row>
     <x:row r="587" spans="1:17">
@@ -18595,13 +18601,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D587" s="0" t="s">
-        <x:v>1320</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="G587" s="0" t="s">
-        <x:v>1320</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="I587" s="0" t="s">
-        <x:v>1321</x:v>
+        <x:v>1322</x:v>
       </x:c>
     </x:row>
     <x:row r="588" spans="1:17">
@@ -18615,13 +18621,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D588" s="0" t="s">
-        <x:v>1322</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="G588" s="0" t="s">
-        <x:v>1322</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="I588" s="0" t="s">
-        <x:v>1323</x:v>
+        <x:v>1324</x:v>
       </x:c>
     </x:row>
     <x:row r="589" spans="1:17">
@@ -18635,13 +18641,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D589" s="0" t="s">
-        <x:v>1324</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="G589" s="0" t="s">
-        <x:v>1324</x:v>
+        <x:v>1325</x:v>
       </x:c>
       <x:c r="I589" s="0" t="s">
-        <x:v>1325</x:v>
+        <x:v>1326</x:v>
       </x:c>
     </x:row>
     <x:row r="590" spans="1:17">
@@ -18655,13 +18661,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D590" s="0" t="s">
-        <x:v>1326</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="G590" s="0" t="s">
-        <x:v>1326</x:v>
+        <x:v>1327</x:v>
       </x:c>
       <x:c r="I590" s="0" t="s">
-        <x:v>1327</x:v>
+        <x:v>1328</x:v>
       </x:c>
     </x:row>
     <x:row r="591" spans="1:17">
@@ -18675,13 +18681,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D591" s="0" t="s">
-        <x:v>1328</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="G591" s="0" t="s">
-        <x:v>1328</x:v>
+        <x:v>1329</x:v>
       </x:c>
       <x:c r="I591" s="0" t="s">
-        <x:v>1329</x:v>
+        <x:v>1330</x:v>
       </x:c>
     </x:row>
     <x:row r="592" spans="1:17">
@@ -18695,13 +18701,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D592" s="0" t="s">
-        <x:v>1330</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="G592" s="0" t="s">
-        <x:v>1330</x:v>
+        <x:v>1331</x:v>
       </x:c>
       <x:c r="I592" s="0" t="s">
-        <x:v>1331</x:v>
+        <x:v>1332</x:v>
       </x:c>
     </x:row>
     <x:row r="593" spans="1:17">
@@ -18715,13 +18721,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D593" s="0" t="s">
-        <x:v>1332</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="G593" s="0" t="s">
-        <x:v>1332</x:v>
+        <x:v>1333</x:v>
       </x:c>
       <x:c r="I593" s="0" t="s">
-        <x:v>1333</x:v>
+        <x:v>1334</x:v>
       </x:c>
     </x:row>
     <x:row r="594" spans="1:17">
@@ -18735,13 +18741,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D594" s="0" t="s">
-        <x:v>1334</x:v>
+        <x:v>1335</x:v>
       </x:c>
       <x:c r="G594" s="0" t="s">
-        <x:v>1334</x:v>
+        <x:v>1335</x:v>
       </x:c>
       <x:c r="I594" s="0" t="s">
-        <x:v>1335</x:v>
+        <x:v>1336</x:v>
       </x:c>
     </x:row>
     <x:row r="595" spans="1:17">
@@ -18755,13 +18761,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D595" s="0" t="s">
-        <x:v>1336</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="G595" s="0" t="s">
-        <x:v>1336</x:v>
+        <x:v>1337</x:v>
       </x:c>
       <x:c r="I595" s="0" t="s">
-        <x:v>1337</x:v>
+        <x:v>1338</x:v>
       </x:c>
     </x:row>
     <x:row r="596" spans="1:17">
@@ -18775,13 +18781,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D596" s="0" t="s">
-        <x:v>1338</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="G596" s="0" t="s">
-        <x:v>1338</x:v>
+        <x:v>1339</x:v>
       </x:c>
       <x:c r="I596" s="0" t="s">
-        <x:v>1339</x:v>
+        <x:v>1340</x:v>
       </x:c>
     </x:row>
     <x:row r="597" spans="1:17">
@@ -18795,13 +18801,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D597" s="0" t="s">
-        <x:v>1340</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="G597" s="0" t="s">
-        <x:v>1340</x:v>
+        <x:v>1341</x:v>
       </x:c>
       <x:c r="I597" s="0" t="s">
-        <x:v>1341</x:v>
+        <x:v>1342</x:v>
       </x:c>
     </x:row>
     <x:row r="598" spans="1:17">
@@ -18815,13 +18821,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D598" s="0" t="s">
-        <x:v>1342</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="G598" s="0" t="s">
-        <x:v>1342</x:v>
+        <x:v>1343</x:v>
       </x:c>
       <x:c r="I598" s="0" t="s">
-        <x:v>1343</x:v>
+        <x:v>1344</x:v>
       </x:c>
     </x:row>
     <x:row r="599" spans="1:17">
@@ -18835,13 +18841,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D599" s="0" t="s">
-        <x:v>1344</x:v>
+        <x:v>1345</x:v>
       </x:c>
       <x:c r="G599" s="0" t="s">
-        <x:v>1344</x:v>
+        <x:v>1345</x:v>
       </x:c>
       <x:c r="I599" s="0" t="s">
-        <x:v>1345</x:v>
+        <x:v>1346</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:17">
@@ -18855,13 +18861,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D600" s="0" t="s">
-        <x:v>1346</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="G600" s="0" t="s">
-        <x:v>1346</x:v>
+        <x:v>1347</x:v>
       </x:c>
       <x:c r="I600" s="0" t="s">
-        <x:v>1347</x:v>
+        <x:v>1348</x:v>
       </x:c>
     </x:row>
     <x:row r="601" spans="1:17">
@@ -18875,13 +18881,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D601" s="0" t="s">
-        <x:v>1348</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="G601" s="0" t="s">
-        <x:v>1348</x:v>
+        <x:v>1349</x:v>
       </x:c>
       <x:c r="I601" s="0" t="s">
-        <x:v>1349</x:v>
+        <x:v>1350</x:v>
       </x:c>
     </x:row>
     <x:row r="602" spans="1:17">
@@ -18895,13 +18901,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D602" s="0" t="s">
-        <x:v>1350</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="G602" s="0" t="s">
-        <x:v>1350</x:v>
+        <x:v>1351</x:v>
       </x:c>
       <x:c r="I602" s="0" t="s">
-        <x:v>1351</x:v>
+        <x:v>1352</x:v>
       </x:c>
     </x:row>
     <x:row r="603" spans="1:17">
@@ -18915,13 +18921,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D603" s="0" t="s">
-        <x:v>1352</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="G603" s="0" t="s">
-        <x:v>1352</x:v>
+        <x:v>1353</x:v>
       </x:c>
       <x:c r="I603" s="0" t="s">
-        <x:v>1353</x:v>
+        <x:v>1354</x:v>
       </x:c>
     </x:row>
     <x:row r="604" spans="1:17">
@@ -18935,13 +18941,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D604" s="0" t="s">
-        <x:v>1354</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="G604" s="0" t="s">
-        <x:v>1354</x:v>
+        <x:v>1355</x:v>
       </x:c>
       <x:c r="I604" s="0" t="s">
-        <x:v>1355</x:v>
+        <x:v>1356</x:v>
       </x:c>
     </x:row>
     <x:row r="605" spans="1:17">
@@ -18955,13 +18961,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D605" s="0" t="s">
-        <x:v>1356</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="G605" s="0" t="s">
-        <x:v>1356</x:v>
+        <x:v>1357</x:v>
       </x:c>
       <x:c r="I605" s="0" t="s">
-        <x:v>1357</x:v>
+        <x:v>1358</x:v>
       </x:c>
     </x:row>
     <x:row r="606" spans="1:17">
@@ -18975,13 +18981,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D606" s="0" t="s">
-        <x:v>1358</x:v>
+        <x:v>1359</x:v>
       </x:c>
       <x:c r="G606" s="0" t="s">
-        <x:v>1358</x:v>
+        <x:v>1359</x:v>
       </x:c>
       <x:c r="I606" s="0" t="s">
-        <x:v>1359</x:v>
+        <x:v>1360</x:v>
       </x:c>
     </x:row>
     <x:row r="607" spans="1:17">
@@ -18995,13 +19001,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D607" s="0" t="s">
-        <x:v>1360</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="G607" s="0" t="s">
-        <x:v>1360</x:v>
+        <x:v>1361</x:v>
       </x:c>
       <x:c r="I607" s="0" t="s">
-        <x:v>1361</x:v>
+        <x:v>1362</x:v>
       </x:c>
     </x:row>
     <x:row r="608" spans="1:17">
@@ -19015,13 +19021,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D608" s="0" t="s">
-        <x:v>1362</x:v>
+        <x:v>1363</x:v>
       </x:c>
       <x:c r="G608" s="0" t="s">
-        <x:v>1362</x:v>
+        <x:v>1363</x:v>
       </x:c>
       <x:c r="I608" s="0" t="s">
-        <x:v>1363</x:v>
+        <x:v>1364</x:v>
       </x:c>
     </x:row>
     <x:row r="609" spans="1:17">
@@ -19035,13 +19041,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D609" s="0" t="s">
-        <x:v>1364</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="G609" s="0" t="s">
-        <x:v>1364</x:v>
+        <x:v>1365</x:v>
       </x:c>
       <x:c r="I609" s="0" t="s">
-        <x:v>1365</x:v>
+        <x:v>1366</x:v>
       </x:c>
     </x:row>
     <x:row r="610" spans="1:17">
@@ -19055,13 +19061,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D610" s="0" t="s">
-        <x:v>1366</x:v>
+        <x:v>1367</x:v>
       </x:c>
       <x:c r="G610" s="0" t="s">
-        <x:v>1366</x:v>
+        <x:v>1367</x:v>
       </x:c>
       <x:c r="I610" s="0" t="s">
-        <x:v>1367</x:v>
+        <x:v>1368</x:v>
       </x:c>
     </x:row>
     <x:row r="611" spans="1:17">
@@ -19075,13 +19081,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D611" s="0" t="s">
-        <x:v>1368</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="G611" s="0" t="s">
-        <x:v>1368</x:v>
+        <x:v>1369</x:v>
       </x:c>
       <x:c r="I611" s="0" t="s">
-        <x:v>1369</x:v>
+        <x:v>1370</x:v>
       </x:c>
     </x:row>
     <x:row r="612" spans="1:17">
@@ -19095,13 +19101,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D612" s="0" t="s">
-        <x:v>1370</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="G612" s="0" t="s">
-        <x:v>1370</x:v>
+        <x:v>1371</x:v>
       </x:c>
       <x:c r="I612" s="0" t="s">
-        <x:v>1371</x:v>
+        <x:v>1372</x:v>
       </x:c>
     </x:row>
     <x:row r="613" spans="1:17">
@@ -19115,13 +19121,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D613" s="0" t="s">
-        <x:v>1372</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="G613" s="0" t="s">
-        <x:v>1372</x:v>
+        <x:v>1373</x:v>
       </x:c>
       <x:c r="I613" s="0" t="s">
-        <x:v>1373</x:v>
+        <x:v>1374</x:v>
       </x:c>
     </x:row>
     <x:row r="614" spans="1:17">
@@ -19135,13 +19141,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D614" s="0" t="s">
-        <x:v>1374</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="G614" s="0" t="s">
-        <x:v>1374</x:v>
+        <x:v>1375</x:v>
       </x:c>
       <x:c r="I614" s="0" t="s">
-        <x:v>1375</x:v>
+        <x:v>1376</x:v>
       </x:c>
     </x:row>
     <x:row r="615" spans="1:17">
@@ -19155,13 +19161,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D615" s="0" t="s">
-        <x:v>1376</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="G615" s="0" t="s">
-        <x:v>1376</x:v>
+        <x:v>1377</x:v>
       </x:c>
       <x:c r="I615" s="0" t="s">
-        <x:v>1377</x:v>
+        <x:v>1378</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:17">
@@ -19175,13 +19181,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D616" s="0" t="s">
-        <x:v>1378</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="G616" s="0" t="s">
-        <x:v>1378</x:v>
+        <x:v>1379</x:v>
       </x:c>
       <x:c r="I616" s="0" t="s">
-        <x:v>1379</x:v>
+        <x:v>1380</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:17">
@@ -19195,13 +19201,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D617" s="0" t="s">
-        <x:v>1380</x:v>
+        <x:v>1381</x:v>
       </x:c>
       <x:c r="G617" s="0" t="s">
-        <x:v>1380</x:v>
+        <x:v>1381</x:v>
       </x:c>
       <x:c r="I617" s="0" t="s">
-        <x:v>1381</x:v>
+        <x:v>1382</x:v>
       </x:c>
     </x:row>
     <x:row r="618" spans="1:17">
@@ -19212,10 +19218,10 @@
         <x:v>1404000753</x:v>
       </x:c>
       <x:c r="C618" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D618" s="0" t="s">
-        <x:v>1383</x:v>
+        <x:v>1384</x:v>
       </x:c>
     </x:row>
     <x:row r="619" spans="1:17">
@@ -19226,10 +19232,10 @@
         <x:v>1404000754</x:v>
       </x:c>
       <x:c r="C619" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D619" s="0" t="s">
-        <x:v>1384</x:v>
+        <x:v>1385</x:v>
       </x:c>
     </x:row>
     <x:row r="620" spans="1:17">
@@ -19240,10 +19246,10 @@
         <x:v>1404000755</x:v>
       </x:c>
       <x:c r="C620" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D620" s="0" t="s">
-        <x:v>1385</x:v>
+        <x:v>1386</x:v>
       </x:c>
     </x:row>
     <x:row r="621" spans="1:17">
@@ -19254,10 +19260,10 @@
         <x:v>1404000756</x:v>
       </x:c>
       <x:c r="C621" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D621" s="0" t="s">
-        <x:v>1386</x:v>
+        <x:v>1387</x:v>
       </x:c>
     </x:row>
     <x:row r="622" spans="1:17">
@@ -19268,10 +19274,10 @@
         <x:v>1404000757</x:v>
       </x:c>
       <x:c r="C622" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D622" s="0" t="s">
-        <x:v>1387</x:v>
+        <x:v>1388</x:v>
       </x:c>
     </x:row>
     <x:row r="623" spans="1:17">
@@ -19282,10 +19288,10 @@
         <x:v>1404000758</x:v>
       </x:c>
       <x:c r="C623" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D623" s="0" t="s">
-        <x:v>1388</x:v>
+        <x:v>1389</x:v>
       </x:c>
     </x:row>
     <x:row r="624" spans="1:17">
@@ -19296,10 +19302,10 @@
         <x:v>1404000759</x:v>
       </x:c>
       <x:c r="C624" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D624" s="0" t="s">
-        <x:v>1389</x:v>
+        <x:v>1390</x:v>
       </x:c>
     </x:row>
     <x:row r="625" spans="1:17">
@@ -19310,10 +19316,10 @@
         <x:v>1404000760</x:v>
       </x:c>
       <x:c r="C625" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D625" s="0" t="s">
-        <x:v>1390</x:v>
+        <x:v>1391</x:v>
       </x:c>
     </x:row>
     <x:row r="626" spans="1:17">
@@ -19324,10 +19330,10 @@
         <x:v>1404000761</x:v>
       </x:c>
       <x:c r="C626" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D626" s="0" t="s">
-        <x:v>1391</x:v>
+        <x:v>1392</x:v>
       </x:c>
     </x:row>
     <x:row r="627" spans="1:17">
@@ -19338,10 +19344,10 @@
         <x:v>1404000763</x:v>
       </x:c>
       <x:c r="C627" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D627" s="0" t="s">
-        <x:v>1393</x:v>
+        <x:v>1394</x:v>
       </x:c>
     </x:row>
     <x:row r="628" spans="1:17">
@@ -19352,10 +19358,10 @@
         <x:v>1404000764</x:v>
       </x:c>
       <x:c r="C628" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D628" s="0" t="s">
-        <x:v>1394</x:v>
+        <x:v>1395</x:v>
       </x:c>
     </x:row>
     <x:row r="629" spans="1:17">
@@ -19366,10 +19372,10 @@
         <x:v>1404000765</x:v>
       </x:c>
       <x:c r="C629" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D629" s="0" t="s">
-        <x:v>1395</x:v>
+        <x:v>1396</x:v>
       </x:c>
     </x:row>
     <x:row r="630" spans="1:17">
@@ -19380,10 +19386,10 @@
         <x:v>1404000766</x:v>
       </x:c>
       <x:c r="C630" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D630" s="0" t="s">
-        <x:v>1396</x:v>
+        <x:v>1397</x:v>
       </x:c>
     </x:row>
     <x:row r="631" spans="1:17">
@@ -19394,10 +19400,10 @@
         <x:v>1404000767</x:v>
       </x:c>
       <x:c r="C631" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D631" s="0" t="s">
-        <x:v>1397</x:v>
+        <x:v>1398</x:v>
       </x:c>
     </x:row>
     <x:row r="632" spans="1:17">
@@ -19408,10 +19414,10 @@
         <x:v>1404000768</x:v>
       </x:c>
       <x:c r="C632" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D632" s="0" t="s">
-        <x:v>1398</x:v>
+        <x:v>1399</x:v>
       </x:c>
     </x:row>
     <x:row r="633" spans="1:17">
@@ -19422,10 +19428,10 @@
         <x:v>1404000769</x:v>
       </x:c>
       <x:c r="C633" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D633" s="0" t="s">
-        <x:v>1399</x:v>
+        <x:v>1400</x:v>
       </x:c>
     </x:row>
     <x:row r="634" spans="1:17">
@@ -19436,10 +19442,10 @@
         <x:v>1404000770</x:v>
       </x:c>
       <x:c r="C634" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D634" s="0" t="s">
-        <x:v>1400</x:v>
+        <x:v>1401</x:v>
       </x:c>
     </x:row>
     <x:row r="635" spans="1:17">
@@ -19450,10 +19456,10 @@
         <x:v>1404000771</x:v>
       </x:c>
       <x:c r="C635" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D635" s="0" t="s">
-        <x:v>1401</x:v>
+        <x:v>1402</x:v>
       </x:c>
     </x:row>
     <x:row r="636" spans="1:17">
@@ -19464,10 +19470,10 @@
         <x:v>1404000772</x:v>
       </x:c>
       <x:c r="C636" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D636" s="0" t="s">
-        <x:v>1402</x:v>
+        <x:v>1403</x:v>
       </x:c>
     </x:row>
     <x:row r="637" spans="1:17">
@@ -19478,10 +19484,10 @@
         <x:v>1404000773</x:v>
       </x:c>
       <x:c r="C637" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D637" s="0" t="s">
-        <x:v>1403</x:v>
+        <x:v>1404</x:v>
       </x:c>
     </x:row>
     <x:row r="638" spans="1:17">
@@ -19492,10 +19498,10 @@
         <x:v>1404000774</x:v>
       </x:c>
       <x:c r="C638" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D638" s="0" t="s">
-        <x:v>1404</x:v>
+        <x:v>1405</x:v>
       </x:c>
     </x:row>
     <x:row r="639" spans="1:17">
@@ -19506,10 +19512,10 @@
         <x:v>1404000775</x:v>
       </x:c>
       <x:c r="C639" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D639" s="0" t="s">
-        <x:v>1405</x:v>
+        <x:v>1406</x:v>
       </x:c>
     </x:row>
     <x:row r="640" spans="1:17">
@@ -19520,10 +19526,10 @@
         <x:v>1404000776</x:v>
       </x:c>
       <x:c r="C640" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D640" s="0" t="s">
-        <x:v>1406</x:v>
+        <x:v>1407</x:v>
       </x:c>
     </x:row>
     <x:row r="641" spans="1:17">
@@ -19534,10 +19540,10 @@
         <x:v>1404000777</x:v>
       </x:c>
       <x:c r="C641" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D641" s="0" t="s">
-        <x:v>1407</x:v>
+        <x:v>1408</x:v>
       </x:c>
     </x:row>
     <x:row r="642" spans="1:17">
@@ -19548,10 +19554,10 @@
         <x:v>1404000778</x:v>
       </x:c>
       <x:c r="C642" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D642" s="0" t="s">
-        <x:v>1408</x:v>
+        <x:v>1409</x:v>
       </x:c>
     </x:row>
     <x:row r="643" spans="1:17">
@@ -19562,10 +19568,10 @@
         <x:v>1404000779</x:v>
       </x:c>
       <x:c r="C643" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D643" s="0" t="s">
-        <x:v>1409</x:v>
+        <x:v>1410</x:v>
       </x:c>
     </x:row>
     <x:row r="644" spans="1:17">
@@ -19576,10 +19582,10 @@
         <x:v>1404000780</x:v>
       </x:c>
       <x:c r="C644" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D644" s="0" t="s">
-        <x:v>1410</x:v>
+        <x:v>1411</x:v>
       </x:c>
     </x:row>
     <x:row r="645" spans="1:17">
@@ -19590,10 +19596,10 @@
         <x:v>1404000781</x:v>
       </x:c>
       <x:c r="C645" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D645" s="0" t="s">
-        <x:v>1411</x:v>
+        <x:v>1412</x:v>
       </x:c>
     </x:row>
     <x:row r="646" spans="1:17">
@@ -19604,10 +19610,10 @@
         <x:v>1404000782</x:v>
       </x:c>
       <x:c r="C646" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D646" s="0" t="s">
-        <x:v>1412</x:v>
+        <x:v>1413</x:v>
       </x:c>
     </x:row>
     <x:row r="647" spans="1:17">
@@ -19618,10 +19624,10 @@
         <x:v>1404000783</x:v>
       </x:c>
       <x:c r="C647" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D647" s="0" t="s">
-        <x:v>1413</x:v>
+        <x:v>1414</x:v>
       </x:c>
     </x:row>
     <x:row r="648" spans="1:17">
@@ -19632,10 +19638,10 @@
         <x:v>1404000784</x:v>
       </x:c>
       <x:c r="C648" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D648" s="0" t="s">
-        <x:v>1414</x:v>
+        <x:v>1415</x:v>
       </x:c>
     </x:row>
     <x:row r="649" spans="1:17">
@@ -19646,10 +19652,10 @@
         <x:v>1404000785</x:v>
       </x:c>
       <x:c r="C649" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D649" s="0" t="s">
-        <x:v>1415</x:v>
+        <x:v>1416</x:v>
       </x:c>
     </x:row>
     <x:row r="650" spans="1:17">
@@ -19660,10 +19666,10 @@
         <x:v>1404000786</x:v>
       </x:c>
       <x:c r="C650" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D650" s="0" t="s">
-        <x:v>1416</x:v>
+        <x:v>1417</x:v>
       </x:c>
     </x:row>
     <x:row r="651" spans="1:17">
@@ -19674,10 +19680,10 @@
         <x:v>1404000787</x:v>
       </x:c>
       <x:c r="C651" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D651" s="0" t="s">
-        <x:v>1417</x:v>
+        <x:v>1418</x:v>
       </x:c>
     </x:row>
     <x:row r="652" spans="1:17">
@@ -19688,10 +19694,10 @@
         <x:v>1404000788</x:v>
       </x:c>
       <x:c r="C652" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D652" s="0" t="s">
-        <x:v>1418</x:v>
+        <x:v>1419</x:v>
       </x:c>
     </x:row>
     <x:row r="653" spans="1:17">
@@ -19702,10 +19708,10 @@
         <x:v>1404000789</x:v>
       </x:c>
       <x:c r="C653" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D653" s="0" t="s">
-        <x:v>1419</x:v>
+        <x:v>1420</x:v>
       </x:c>
     </x:row>
     <x:row r="654" spans="1:17">
@@ -19716,10 +19722,10 @@
         <x:v>1404000790</x:v>
       </x:c>
       <x:c r="C654" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D654" s="0" t="s">
-        <x:v>1420</x:v>
+        <x:v>1421</x:v>
       </x:c>
     </x:row>
     <x:row r="655" spans="1:17">
@@ -19730,10 +19736,10 @@
         <x:v>1404000791</x:v>
       </x:c>
       <x:c r="C655" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D655" s="0" t="s">
-        <x:v>1422</x:v>
+        <x:v>1423</x:v>
       </x:c>
     </x:row>
     <x:row r="656" spans="1:17">
@@ -19744,10 +19750,10 @@
         <x:v>1404000792</x:v>
       </x:c>
       <x:c r="C656" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D656" s="0" t="s">
-        <x:v>1423</x:v>
+        <x:v>1424</x:v>
       </x:c>
     </x:row>
     <x:row r="657" spans="1:17">
@@ -19764,10 +19770,10 @@
         <x:v>579</x:v>
       </x:c>
       <x:c r="G657" s="0" t="s">
-        <x:v>1424</x:v>
+        <x:v>1425</x:v>
       </x:c>
       <x:c r="I657" s="0" t="s">
-        <x:v>1425</x:v>
+        <x:v>1426</x:v>
       </x:c>
     </x:row>
     <x:row r="658" spans="1:17">
@@ -19781,13 +19787,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D658" s="0" t="s">
-        <x:v>1426</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="G658" s="0" t="s">
-        <x:v>1426</x:v>
+        <x:v>1427</x:v>
       </x:c>
       <x:c r="I658" s="0" t="s">
-        <x:v>1427</x:v>
+        <x:v>1428</x:v>
       </x:c>
     </x:row>
     <x:row r="659" spans="1:17">
@@ -19801,13 +19807,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D659" s="0" t="s">
-        <x:v>1428</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="G659" s="0" t="s">
-        <x:v>1428</x:v>
+        <x:v>1429</x:v>
       </x:c>
       <x:c r="I659" s="0" t="s">
-        <x:v>1429</x:v>
+        <x:v>1430</x:v>
       </x:c>
     </x:row>
     <x:row r="660" spans="1:17">
@@ -19821,13 +19827,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D660" s="0" t="s">
-        <x:v>1430</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="G660" s="0" t="s">
-        <x:v>1430</x:v>
+        <x:v>1431</x:v>
       </x:c>
       <x:c r="I660" s="0" t="s">
-        <x:v>1431</x:v>
+        <x:v>1432</x:v>
       </x:c>
     </x:row>
     <x:row r="661" spans="1:17">
@@ -19838,10 +19844,10 @@
         <x:v>1404000797</x:v>
       </x:c>
       <x:c r="C661" s="0" t="s">
-        <x:v>1432</x:v>
+        <x:v>1433</x:v>
       </x:c>
       <x:c r="D661" s="0" t="s">
-        <x:v>1433</x:v>
+        <x:v>1434</x:v>
       </x:c>
     </x:row>
     <x:row r="662" spans="1:17">
@@ -19852,10 +19858,10 @@
         <x:v>1404000798</x:v>
       </x:c>
       <x:c r="C662" s="0" t="s">
-        <x:v>1434</x:v>
+        <x:v>1435</x:v>
       </x:c>
       <x:c r="D662" s="0" t="s">
-        <x:v>1435</x:v>
+        <x:v>1436</x:v>
       </x:c>
     </x:row>
     <x:row r="663" spans="1:17">
@@ -19866,10 +19872,10 @@
         <x:v>1404000799</x:v>
       </x:c>
       <x:c r="C663" s="0" t="s">
-        <x:v>1436</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="D663" s="0" t="s">
-        <x:v>1437</x:v>
+        <x:v>1438</x:v>
       </x:c>
     </x:row>
     <x:row r="664" spans="1:17">
@@ -19880,16 +19886,16 @@
         <x:v>1404000800</x:v>
       </x:c>
       <x:c r="C664" s="0" t="s">
-        <x:v>1438</x:v>
+        <x:v>1439</x:v>
       </x:c>
       <x:c r="D664" s="0" t="s">
-        <x:v>1439</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="G664" s="0" t="s">
-        <x:v>1440</x:v>
+        <x:v>1441</x:v>
       </x:c>
       <x:c r="I664" s="0" t="s">
-        <x:v>1441</x:v>
+        <x:v>1442</x:v>
       </x:c>
     </x:row>
     <x:row r="665" spans="1:17">
@@ -19900,16 +19906,16 @@
         <x:v>1404000801</x:v>
       </x:c>
       <x:c r="C665" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D665" s="0" t="s">
-        <x:v>1443</x:v>
+        <x:v>1444</x:v>
       </x:c>
       <x:c r="G665" s="0" t="s">
-        <x:v>1444</x:v>
+        <x:v>1445</x:v>
       </x:c>
       <x:c r="I665" s="0" t="s">
-        <x:v>1445</x:v>
+        <x:v>1446</x:v>
       </x:c>
     </x:row>
     <x:row r="666" spans="1:17">
@@ -19920,16 +19926,16 @@
         <x:v>1404000802</x:v>
       </x:c>
       <x:c r="C666" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D666" s="0" t="s">
-        <x:v>1446</x:v>
+        <x:v>1447</x:v>
       </x:c>
       <x:c r="G666" s="0" t="s">
-        <x:v>1447</x:v>
+        <x:v>1448</x:v>
       </x:c>
       <x:c r="I666" s="0" t="s">
-        <x:v>1448</x:v>
+        <x:v>1449</x:v>
       </x:c>
     </x:row>
     <x:row r="667" spans="1:17">
@@ -19940,16 +19946,16 @@
         <x:v>1404000803</x:v>
       </x:c>
       <x:c r="C667" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D667" s="0" t="s">
-        <x:v>1449</x:v>
+        <x:v>1450</x:v>
       </x:c>
       <x:c r="G667" s="0" t="s">
-        <x:v>1450</x:v>
+        <x:v>1451</x:v>
       </x:c>
       <x:c r="I667" s="0" t="s">
-        <x:v>1451</x:v>
+        <x:v>1452</x:v>
       </x:c>
     </x:row>
     <x:row r="668" spans="1:17">
@@ -19960,16 +19966,16 @@
         <x:v>1404000804</x:v>
       </x:c>
       <x:c r="C668" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D668" s="0" t="s">
-        <x:v>1452</x:v>
+        <x:v>1453</x:v>
       </x:c>
       <x:c r="G668" s="0" t="s">
-        <x:v>1453</x:v>
+        <x:v>1454</x:v>
       </x:c>
       <x:c r="I668" s="0" t="s">
-        <x:v>1454</x:v>
+        <x:v>1455</x:v>
       </x:c>
     </x:row>
     <x:row r="669" spans="1:17">
@@ -19980,16 +19986,16 @@
         <x:v>1404000805</x:v>
       </x:c>
       <x:c r="C669" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D669" s="0" t="s">
-        <x:v>1455</x:v>
+        <x:v>1456</x:v>
       </x:c>
       <x:c r="G669" s="0" t="s">
-        <x:v>1456</x:v>
+        <x:v>1457</x:v>
       </x:c>
       <x:c r="I669" s="0" t="s">
-        <x:v>1457</x:v>
+        <x:v>1458</x:v>
       </x:c>
     </x:row>
     <x:row r="670" spans="1:17">
@@ -20000,16 +20006,16 @@
         <x:v>1404000806</x:v>
       </x:c>
       <x:c r="C670" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D670" s="0" t="s">
-        <x:v>1458</x:v>
+        <x:v>1459</x:v>
       </x:c>
       <x:c r="G670" s="0" t="s">
-        <x:v>1459</x:v>
+        <x:v>1460</x:v>
       </x:c>
       <x:c r="I670" s="0" t="s">
-        <x:v>1460</x:v>
+        <x:v>1461</x:v>
       </x:c>
     </x:row>
     <x:row r="671" spans="1:17">
@@ -20020,16 +20026,16 @@
         <x:v>1404000807</x:v>
       </x:c>
       <x:c r="C671" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D671" s="0" t="s">
-        <x:v>1461</x:v>
+        <x:v>1462</x:v>
       </x:c>
       <x:c r="G671" s="0" t="s">
-        <x:v>1462</x:v>
+        <x:v>1463</x:v>
       </x:c>
       <x:c r="I671" s="0" t="s">
-        <x:v>1463</x:v>
+        <x:v>1464</x:v>
       </x:c>
     </x:row>
     <x:row r="672" spans="1:17">
@@ -20040,16 +20046,16 @@
         <x:v>1404000808</x:v>
       </x:c>
       <x:c r="C672" s="0" t="s">
-        <x:v>1442</x:v>
+        <x:v>1443</x:v>
       </x:c>
       <x:c r="D672" s="0" t="s">
-        <x:v>1464</x:v>
+        <x:v>1465</x:v>
       </x:c>
       <x:c r="G672" s="0" t="s">
-        <x:v>1465</x:v>
+        <x:v>1466</x:v>
       </x:c>
       <x:c r="I672" s="0" t="s">
-        <x:v>1466</x:v>
+        <x:v>1467</x:v>
       </x:c>
     </x:row>
     <x:row r="673" spans="1:17">
@@ -20063,7 +20069,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D673" s="0" t="s">
-        <x:v>1467</x:v>
+        <x:v>1468</x:v>
       </x:c>
     </x:row>
     <x:row r="674" spans="1:17">
@@ -20077,7 +20083,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D674" s="0" t="s">
-        <x:v>1468</x:v>
+        <x:v>1469</x:v>
       </x:c>
     </x:row>
     <x:row r="675" spans="1:17">
@@ -20088,10 +20094,10 @@
         <x:v>1404000814</x:v>
       </x:c>
       <x:c r="C675" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D675" s="0" t="s">
-        <x:v>1469</x:v>
+        <x:v>1470</x:v>
       </x:c>
     </x:row>
     <x:row r="676" spans="1:17">
@@ -20102,10 +20108,10 @@
         <x:v>1404000815</x:v>
       </x:c>
       <x:c r="C676" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D676" s="0" t="s">
-        <x:v>1470</x:v>
+        <x:v>1471</x:v>
       </x:c>
     </x:row>
     <x:row r="677" spans="1:17">
@@ -20116,10 +20122,10 @@
         <x:v>1404000816</x:v>
       </x:c>
       <x:c r="C677" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D677" s="0" t="s">
-        <x:v>1471</x:v>
+        <x:v>1472</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:17">
@@ -20130,10 +20136,10 @@
         <x:v>1404000817</x:v>
       </x:c>
       <x:c r="C678" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D678" s="0" t="s">
-        <x:v>1472</x:v>
+        <x:v>1473</x:v>
       </x:c>
     </x:row>
     <x:row r="679" spans="1:17">
@@ -20144,10 +20150,10 @@
         <x:v>1404000818</x:v>
       </x:c>
       <x:c r="C679" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D679" s="0" t="s">
-        <x:v>1473</x:v>
+        <x:v>1474</x:v>
       </x:c>
     </x:row>
     <x:row r="680" spans="1:17">
@@ -20158,10 +20164,10 @@
         <x:v>1404000819</x:v>
       </x:c>
       <x:c r="C680" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D680" s="0" t="s">
-        <x:v>1474</x:v>
+        <x:v>1475</x:v>
       </x:c>
     </x:row>
     <x:row r="681" spans="1:17">
@@ -20172,10 +20178,10 @@
         <x:v>1404000820</x:v>
       </x:c>
       <x:c r="C681" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D681" s="0" t="s">
-        <x:v>1475</x:v>
+        <x:v>1476</x:v>
       </x:c>
     </x:row>
     <x:row r="682" spans="1:17">
@@ -20186,10 +20192,10 @@
         <x:v>1404000821</x:v>
       </x:c>
       <x:c r="C682" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D682" s="0" t="s">
-        <x:v>1476</x:v>
+        <x:v>1477</x:v>
       </x:c>
     </x:row>
     <x:row r="683" spans="1:17">
@@ -20200,10 +20206,10 @@
         <x:v>1404000822</x:v>
       </x:c>
       <x:c r="C683" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D683" s="0" t="s">
-        <x:v>1477</x:v>
+        <x:v>1478</x:v>
       </x:c>
     </x:row>
     <x:row r="684" spans="1:17">
@@ -20214,10 +20220,10 @@
         <x:v>1404000823</x:v>
       </x:c>
       <x:c r="C684" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D684" s="0" t="s">
-        <x:v>1478</x:v>
+        <x:v>1479</x:v>
       </x:c>
     </x:row>
     <x:row r="685" spans="1:17">
@@ -20228,10 +20234,10 @@
         <x:v>1404000824</x:v>
       </x:c>
       <x:c r="C685" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D685" s="0" t="s">
-        <x:v>1479</x:v>
+        <x:v>1480</x:v>
       </x:c>
     </x:row>
     <x:row r="686" spans="1:17">
@@ -20242,10 +20248,10 @@
         <x:v>1404000825</x:v>
       </x:c>
       <x:c r="C686" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D686" s="0" t="s">
-        <x:v>1480</x:v>
+        <x:v>1481</x:v>
       </x:c>
     </x:row>
     <x:row r="687" spans="1:17">
@@ -20259,13 +20265,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D687" s="0" t="s">
-        <x:v>1481</x:v>
+        <x:v>1482</x:v>
       </x:c>
       <x:c r="G687" s="0" t="s">
-        <x:v>1481</x:v>
+        <x:v>1482</x:v>
       </x:c>
       <x:c r="I687" s="0" t="s">
-        <x:v>1482</x:v>
+        <x:v>1483</x:v>
       </x:c>
     </x:row>
     <x:row r="688" spans="1:17">
@@ -20279,13 +20285,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D688" s="0" t="s">
-        <x:v>1483</x:v>
+        <x:v>1484</x:v>
       </x:c>
       <x:c r="G688" s="0" t="s">
-        <x:v>1483</x:v>
+        <x:v>1484</x:v>
       </x:c>
       <x:c r="I688" s="0" t="s">
-        <x:v>1484</x:v>
+        <x:v>1485</x:v>
       </x:c>
     </x:row>
     <x:row r="689" spans="1:17">
@@ -20299,13 +20305,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D689" s="0" t="s">
-        <x:v>1485</x:v>
+        <x:v>1486</x:v>
       </x:c>
       <x:c r="G689" s="0" t="s">
-        <x:v>1485</x:v>
+        <x:v>1486</x:v>
       </x:c>
       <x:c r="I689" s="0" t="s">
-        <x:v>1486</x:v>
+        <x:v>1487</x:v>
       </x:c>
     </x:row>
     <x:row r="690" spans="1:17">
@@ -20319,13 +20325,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D690" s="0" t="s">
-        <x:v>1487</x:v>
+        <x:v>1488</x:v>
       </x:c>
       <x:c r="G690" s="0" t="s">
-        <x:v>1487</x:v>
+        <x:v>1488</x:v>
       </x:c>
       <x:c r="I690" s="0" t="s">
-        <x:v>1488</x:v>
+        <x:v>1489</x:v>
       </x:c>
     </x:row>
     <x:row r="691" spans="1:17">
@@ -20339,13 +20345,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D691" s="0" t="s">
-        <x:v>1489</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="G691" s="0" t="s">
-        <x:v>1489</x:v>
+        <x:v>1490</x:v>
       </x:c>
       <x:c r="I691" s="0" t="s">
-        <x:v>1490</x:v>
+        <x:v>1491</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:17">
@@ -20359,13 +20365,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D692" s="0" t="s">
-        <x:v>1491</x:v>
+        <x:v>1492</x:v>
       </x:c>
       <x:c r="G692" s="0" t="s">
-        <x:v>1491</x:v>
+        <x:v>1492</x:v>
       </x:c>
       <x:c r="I692" s="0" t="s">
-        <x:v>1492</x:v>
+        <x:v>1493</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:17">
@@ -20379,13 +20385,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D693" s="0" t="s">
-        <x:v>1493</x:v>
+        <x:v>1494</x:v>
       </x:c>
       <x:c r="G693" s="0" t="s">
-        <x:v>1493</x:v>
+        <x:v>1494</x:v>
       </x:c>
       <x:c r="I693" s="0" t="s">
-        <x:v>1494</x:v>
+        <x:v>1495</x:v>
       </x:c>
     </x:row>
     <x:row r="694" spans="1:17">
@@ -20399,13 +20405,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D694" s="0" t="s">
-        <x:v>1495</x:v>
+        <x:v>1496</x:v>
       </x:c>
       <x:c r="G694" s="0" t="s">
-        <x:v>1495</x:v>
+        <x:v>1496</x:v>
       </x:c>
       <x:c r="I694" s="0" t="s">
-        <x:v>1496</x:v>
+        <x:v>1497</x:v>
       </x:c>
     </x:row>
     <x:row r="695" spans="1:17">
@@ -20419,13 +20425,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D695" s="0" t="s">
-        <x:v>1497</x:v>
+        <x:v>1498</x:v>
       </x:c>
       <x:c r="G695" s="0" t="s">
-        <x:v>1497</x:v>
+        <x:v>1498</x:v>
       </x:c>
       <x:c r="I695" s="0" t="s">
-        <x:v>1498</x:v>
+        <x:v>1499</x:v>
       </x:c>
     </x:row>
     <x:row r="696" spans="1:17">
@@ -20439,13 +20445,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D696" s="0" t="s">
-        <x:v>1499</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="G696" s="0" t="s">
-        <x:v>1499</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="I696" s="0" t="s">
-        <x:v>1500</x:v>
+        <x:v>1501</x:v>
       </x:c>
     </x:row>
     <x:row r="697" spans="1:17">
@@ -20459,13 +20465,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D697" s="0" t="s">
-        <x:v>1501</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="G697" s="0" t="s">
-        <x:v>1501</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="I697" s="0" t="s">
-        <x:v>1502</x:v>
+        <x:v>1503</x:v>
       </x:c>
     </x:row>
     <x:row r="698" spans="1:17">
@@ -20479,13 +20485,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D698" s="0" t="s">
-        <x:v>1503</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="G698" s="0" t="s">
-        <x:v>1503</x:v>
+        <x:v>1504</x:v>
       </x:c>
       <x:c r="I698" s="0" t="s">
-        <x:v>1504</x:v>
+        <x:v>1505</x:v>
       </x:c>
     </x:row>
     <x:row r="699" spans="1:17">
@@ -20499,13 +20505,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D699" s="0" t="s">
-        <x:v>1505</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="G699" s="0" t="s">
-        <x:v>1505</x:v>
+        <x:v>1506</x:v>
       </x:c>
       <x:c r="I699" s="0" t="s">
-        <x:v>1506</x:v>
+        <x:v>1507</x:v>
       </x:c>
     </x:row>
     <x:row r="700" spans="1:17">
@@ -20519,13 +20525,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D700" s="0" t="s">
-        <x:v>1507</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="G700" s="0" t="s">
-        <x:v>1507</x:v>
+        <x:v>1508</x:v>
       </x:c>
       <x:c r="I700" s="0" t="s">
-        <x:v>1508</x:v>
+        <x:v>1509</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:17">
@@ -20539,13 +20545,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D701" s="0" t="s">
-        <x:v>1509</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="G701" s="0" t="s">
-        <x:v>1509</x:v>
+        <x:v>1510</x:v>
       </x:c>
       <x:c r="I701" s="0" t="s">
-        <x:v>1510</x:v>
+        <x:v>1511</x:v>
       </x:c>
     </x:row>
     <x:row r="702" spans="1:17">
@@ -20559,13 +20565,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D702" s="0" t="s">
-        <x:v>1511</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="G702" s="0" t="s">
-        <x:v>1511</x:v>
+        <x:v>1512</x:v>
       </x:c>
       <x:c r="I702" s="0" t="s">
-        <x:v>1512</x:v>
+        <x:v>1513</x:v>
       </x:c>
     </x:row>
     <x:row r="703" spans="1:17">
@@ -20576,10 +20582,10 @@
         <x:v>1404000844</x:v>
       </x:c>
       <x:c r="C703" s="0" t="s">
-        <x:v>1513</x:v>
+        <x:v>1514</x:v>
       </x:c>
       <x:c r="D703" s="0" t="s">
-        <x:v>1514</x:v>
+        <x:v>1515</x:v>
       </x:c>
     </x:row>
     <x:row r="704" spans="1:17">
@@ -20593,7 +20599,7 @@
         <x:v>292</x:v>
       </x:c>
       <x:c r="D704" s="0" t="s">
-        <x:v>1515</x:v>
+        <x:v>1516</x:v>
       </x:c>
     </x:row>
     <x:row r="705" spans="1:17">
@@ -20604,10 +20610,10 @@
         <x:v>1404000846</x:v>
       </x:c>
       <x:c r="C705" s="0" t="s">
-        <x:v>1516</x:v>
+        <x:v>1517</x:v>
       </x:c>
       <x:c r="D705" s="0" t="s">
-        <x:v>1517</x:v>
+        <x:v>1518</x:v>
       </x:c>
     </x:row>
     <x:row r="706" spans="1:17">
@@ -20621,13 +20627,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D706" s="0" t="s">
-        <x:v>1518</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="G706" s="0" t="s">
-        <x:v>1519</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="I706" s="0" t="s">
-        <x:v>1520</x:v>
+        <x:v>1521</x:v>
       </x:c>
     </x:row>
     <x:row r="707" spans="1:17">
@@ -20641,13 +20647,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D707" s="0" t="s">
-        <x:v>1518</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="G707" s="0" t="s">
-        <x:v>1521</x:v>
+        <x:v>1522</x:v>
       </x:c>
       <x:c r="I707" s="0" t="s">
-        <x:v>1522</x:v>
+        <x:v>1523</x:v>
       </x:c>
     </x:row>
     <x:row r="708" spans="1:17">
@@ -20658,16 +20664,16 @@
         <x:v>1404000849</x:v>
       </x:c>
       <x:c r="C708" s="0" t="s">
-        <x:v>1523</x:v>
+        <x:v>1524</x:v>
       </x:c>
       <x:c r="D708" s="0" t="s">
-        <x:v>1518</x:v>
+        <x:v>1519</x:v>
       </x:c>
       <x:c r="G708" s="0" t="s">
-        <x:v>1519</x:v>
+        <x:v>1520</x:v>
       </x:c>
       <x:c r="I708" s="0" t="s">
-        <x:v>1520</x:v>
+        <x:v>1521</x:v>
       </x:c>
     </x:row>
     <x:row r="709" spans="1:17">
@@ -20678,16 +20684,16 @@
         <x:v>1404000850</x:v>
       </x:c>
       <x:c r="C709" s="0" t="s">
+        <x:v>1524</x:v>
+      </x:c>
+      <x:c r="D709" s="0" t="s">
+        <x:v>1519</x:v>
+      </x:c>
+      <x:c r="G709" s="0" t="s">
+        <x:v>1522</x:v>
+      </x:c>
+      <x:c r="I709" s="0" t="s">
         <x:v>1523</x:v>
-      </x:c>
-      <x:c r="D709" s="0" t="s">
-        <x:v>1518</x:v>
-      </x:c>
-      <x:c r="G709" s="0" t="s">
-        <x:v>1521</x:v>
-      </x:c>
-      <x:c r="I709" s="0" t="s">
-        <x:v>1522</x:v>
       </x:c>
     </x:row>
     <x:row r="710" spans="1:17">
@@ -20698,10 +20704,10 @@
         <x:v>1404000851</x:v>
       </x:c>
       <x:c r="C710" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D710" s="0" t="s">
-        <x:v>1524</x:v>
+        <x:v>1525</x:v>
       </x:c>
     </x:row>
     <x:row r="711" spans="1:17">
@@ -20726,16 +20732,16 @@
         <x:v>1404000888</x:v>
       </x:c>
       <x:c r="C712" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D712" s="0" t="s">
-        <x:v>1526</x:v>
+        <x:v>1527</x:v>
       </x:c>
       <x:c r="G712" s="0" t="s">
-        <x:v>1526</x:v>
+        <x:v>1527</x:v>
       </x:c>
       <x:c r="I712" s="0" t="s">
-        <x:v>1527</x:v>
+        <x:v>1528</x:v>
       </x:c>
     </x:row>
     <x:row r="713" spans="1:17">
@@ -20746,16 +20752,16 @@
         <x:v>1404000889</x:v>
       </x:c>
       <x:c r="C713" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D713" s="0" t="s">
-        <x:v>1528</x:v>
+        <x:v>1529</x:v>
       </x:c>
       <x:c r="G713" s="0" t="s">
-        <x:v>1528</x:v>
+        <x:v>1529</x:v>
       </x:c>
       <x:c r="I713" s="0" t="s">
-        <x:v>1529</x:v>
+        <x:v>1530</x:v>
       </x:c>
     </x:row>
     <x:row r="714" spans="1:17">
@@ -20766,16 +20772,16 @@
         <x:v>1404000890</x:v>
       </x:c>
       <x:c r="C714" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D714" s="0" t="s">
-        <x:v>1530</x:v>
+        <x:v>1531</x:v>
       </x:c>
       <x:c r="G714" s="0" t="s">
-        <x:v>1530</x:v>
+        <x:v>1531</x:v>
       </x:c>
       <x:c r="I714" s="0" t="s">
-        <x:v>1531</x:v>
+        <x:v>1532</x:v>
       </x:c>
     </x:row>
     <x:row r="715" spans="1:17">
@@ -20786,16 +20792,16 @@
         <x:v>1404000891</x:v>
       </x:c>
       <x:c r="C715" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D715" s="0" t="s">
-        <x:v>1532</x:v>
+        <x:v>1533</x:v>
       </x:c>
       <x:c r="G715" s="0" t="s">
-        <x:v>1532</x:v>
+        <x:v>1533</x:v>
       </x:c>
       <x:c r="I715" s="0" t="s">
-        <x:v>1533</x:v>
+        <x:v>1534</x:v>
       </x:c>
     </x:row>
     <x:row r="716" spans="1:17">
@@ -20806,16 +20812,16 @@
         <x:v>1404000892</x:v>
       </x:c>
       <x:c r="C716" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D716" s="0" t="s">
-        <x:v>1534</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="G716" s="0" t="s">
-        <x:v>1534</x:v>
+        <x:v>1535</x:v>
       </x:c>
       <x:c r="I716" s="0" t="s">
-        <x:v>1535</x:v>
+        <x:v>1536</x:v>
       </x:c>
     </x:row>
     <x:row r="717" spans="1:17">
@@ -20826,16 +20832,16 @@
         <x:v>1404000893</x:v>
       </x:c>
       <x:c r="C717" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D717" s="0" t="s">
-        <x:v>1536</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="G717" s="0" t="s">
-        <x:v>1536</x:v>
+        <x:v>1537</x:v>
       </x:c>
       <x:c r="I717" s="0" t="s">
-        <x:v>1537</x:v>
+        <x:v>1538</x:v>
       </x:c>
     </x:row>
     <x:row r="718" spans="1:17">
@@ -20846,16 +20852,16 @@
         <x:v>1404000894</x:v>
       </x:c>
       <x:c r="C718" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D718" s="0" t="s">
-        <x:v>1538</x:v>
+        <x:v>1539</x:v>
       </x:c>
       <x:c r="G718" s="0" t="s">
-        <x:v>1538</x:v>
+        <x:v>1539</x:v>
       </x:c>
       <x:c r="I718" s="0" t="s">
-        <x:v>1539</x:v>
+        <x:v>1540</x:v>
       </x:c>
     </x:row>
     <x:row r="719" spans="1:17">
@@ -20866,16 +20872,16 @@
         <x:v>1404000895</x:v>
       </x:c>
       <x:c r="C719" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D719" s="0" t="s">
-        <x:v>1540</x:v>
+        <x:v>1541</x:v>
       </x:c>
       <x:c r="G719" s="0" t="s">
-        <x:v>1540</x:v>
+        <x:v>1541</x:v>
       </x:c>
       <x:c r="I719" s="0" t="s">
-        <x:v>1541</x:v>
+        <x:v>1542</x:v>
       </x:c>
     </x:row>
     <x:row r="720" spans="1:17">
@@ -20886,16 +20892,16 @@
         <x:v>1404000896</x:v>
       </x:c>
       <x:c r="C720" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D720" s="0" t="s">
-        <x:v>1542</x:v>
+        <x:v>1543</x:v>
       </x:c>
       <x:c r="G720" s="0" t="s">
-        <x:v>1542</x:v>
+        <x:v>1543</x:v>
       </x:c>
       <x:c r="I720" s="0" t="s">
-        <x:v>1543</x:v>
+        <x:v>1544</x:v>
       </x:c>
     </x:row>
     <x:row r="721" spans="1:17">
@@ -20906,16 +20912,16 @@
         <x:v>1404000897</x:v>
       </x:c>
       <x:c r="C721" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D721" s="0" t="s">
-        <x:v>1544</x:v>
+        <x:v>1545</x:v>
       </x:c>
       <x:c r="G721" s="0" t="s">
-        <x:v>1544</x:v>
+        <x:v>1545</x:v>
       </x:c>
       <x:c r="I721" s="0" t="s">
-        <x:v>1545</x:v>
+        <x:v>1546</x:v>
       </x:c>
     </x:row>
     <x:row r="722" spans="1:17">
@@ -20926,16 +20932,16 @@
         <x:v>1404000898</x:v>
       </x:c>
       <x:c r="C722" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D722" s="0" t="s">
-        <x:v>1546</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="G722" s="0" t="s">
-        <x:v>1546</x:v>
+        <x:v>1547</x:v>
       </x:c>
       <x:c r="I722" s="0" t="s">
-        <x:v>1547</x:v>
+        <x:v>1548</x:v>
       </x:c>
     </x:row>
     <x:row r="723" spans="1:17">
@@ -20946,16 +20952,16 @@
         <x:v>1404000899</x:v>
       </x:c>
       <x:c r="C723" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D723" s="0" t="s">
-        <x:v>1548</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="G723" s="0" t="s">
-        <x:v>1548</x:v>
+        <x:v>1549</x:v>
       </x:c>
       <x:c r="I723" s="0" t="s">
-        <x:v>1549</x:v>
+        <x:v>1550</x:v>
       </x:c>
     </x:row>
     <x:row r="724" spans="1:17">
@@ -20966,16 +20972,16 @@
         <x:v>1404000900</x:v>
       </x:c>
       <x:c r="C724" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D724" s="0" t="s">
-        <x:v>1550</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="G724" s="0" t="s">
-        <x:v>1550</x:v>
+        <x:v>1551</x:v>
       </x:c>
       <x:c r="I724" s="0" t="s">
-        <x:v>1551</x:v>
+        <x:v>1552</x:v>
       </x:c>
     </x:row>
     <x:row r="725" spans="1:17">
@@ -20986,16 +20992,16 @@
         <x:v>1404000901</x:v>
       </x:c>
       <x:c r="C725" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D725" s="0" t="s">
-        <x:v>1552</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="G725" s="0" t="s">
-        <x:v>1552</x:v>
+        <x:v>1553</x:v>
       </x:c>
       <x:c r="I725" s="0" t="s">
-        <x:v>1553</x:v>
+        <x:v>1554</x:v>
       </x:c>
     </x:row>
     <x:row r="726" spans="1:17">
@@ -21006,16 +21012,16 @@
         <x:v>1404000902</x:v>
       </x:c>
       <x:c r="C726" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D726" s="0" t="s">
-        <x:v>1554</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="G726" s="0" t="s">
-        <x:v>1554</x:v>
+        <x:v>1555</x:v>
       </x:c>
       <x:c r="I726" s="0" t="s">
-        <x:v>1555</x:v>
+        <x:v>1556</x:v>
       </x:c>
     </x:row>
     <x:row r="727" spans="1:17">
@@ -21026,16 +21032,16 @@
         <x:v>1404000903</x:v>
       </x:c>
       <x:c r="C727" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D727" s="0" t="s">
-        <x:v>1556</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="G727" s="0" t="s">
-        <x:v>1556</x:v>
+        <x:v>1557</x:v>
       </x:c>
       <x:c r="I727" s="0" t="s">
-        <x:v>1557</x:v>
+        <x:v>1558</x:v>
       </x:c>
     </x:row>
     <x:row r="728" spans="1:17">
@@ -21046,16 +21052,16 @@
         <x:v>1404000904</x:v>
       </x:c>
       <x:c r="C728" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D728" s="0" t="s">
-        <x:v>1558</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="G728" s="0" t="s">
-        <x:v>1558</x:v>
+        <x:v>1559</x:v>
       </x:c>
       <x:c r="I728" s="0" t="s">
-        <x:v>1559</x:v>
+        <x:v>1560</x:v>
       </x:c>
     </x:row>
     <x:row r="729" spans="1:17">
@@ -21066,16 +21072,16 @@
         <x:v>1404000905</x:v>
       </x:c>
       <x:c r="C729" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D729" s="0" t="s">
-        <x:v>1560</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="G729" s="0" t="s">
-        <x:v>1560</x:v>
+        <x:v>1561</x:v>
       </x:c>
       <x:c r="I729" s="0" t="s">
-        <x:v>1561</x:v>
+        <x:v>1562</x:v>
       </x:c>
     </x:row>
     <x:row r="730" spans="1:17">
@@ -21086,16 +21092,16 @@
         <x:v>1404000906</x:v>
       </x:c>
       <x:c r="C730" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D730" s="0" t="s">
-        <x:v>1562</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="G730" s="0" t="s">
-        <x:v>1562</x:v>
+        <x:v>1563</x:v>
       </x:c>
       <x:c r="I730" s="0" t="s">
-        <x:v>1563</x:v>
+        <x:v>1564</x:v>
       </x:c>
     </x:row>
     <x:row r="731" spans="1:17">
@@ -21106,16 +21112,16 @@
         <x:v>1404000907</x:v>
       </x:c>
       <x:c r="C731" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D731" s="0" t="s">
-        <x:v>1564</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="G731" s="0" t="s">
-        <x:v>1564</x:v>
+        <x:v>1565</x:v>
       </x:c>
       <x:c r="I731" s="0" t="s">
-        <x:v>1565</x:v>
+        <x:v>1566</x:v>
       </x:c>
     </x:row>
     <x:row r="732" spans="1:17">
@@ -21126,16 +21132,16 @@
         <x:v>1404000908</x:v>
       </x:c>
       <x:c r="C732" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D732" s="0" t="s">
-        <x:v>1566</x:v>
+        <x:v>1567</x:v>
       </x:c>
       <x:c r="G732" s="0" t="s">
-        <x:v>1566</x:v>
+        <x:v>1567</x:v>
       </x:c>
       <x:c r="I732" s="0" t="s">
-        <x:v>1567</x:v>
+        <x:v>1568</x:v>
       </x:c>
     </x:row>
     <x:row r="733" spans="1:17">
@@ -21146,16 +21152,16 @@
         <x:v>1404000909</x:v>
       </x:c>
       <x:c r="C733" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D733" s="0" t="s">
-        <x:v>1568</x:v>
+        <x:v>1569</x:v>
       </x:c>
       <x:c r="G733" s="0" t="s">
-        <x:v>1569</x:v>
+        <x:v>1570</x:v>
       </x:c>
       <x:c r="I733" s="0" t="s">
-        <x:v>1570</x:v>
+        <x:v>1571</x:v>
       </x:c>
     </x:row>
     <x:row r="734" spans="1:17">
@@ -21166,16 +21172,16 @@
         <x:v>1404000910</x:v>
       </x:c>
       <x:c r="C734" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D734" s="0" t="s">
-        <x:v>1571</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="G734" s="0" t="s">
-        <x:v>1571</x:v>
+        <x:v>1572</x:v>
       </x:c>
       <x:c r="I734" s="0" t="s">
-        <x:v>1572</x:v>
+        <x:v>1573</x:v>
       </x:c>
     </x:row>
     <x:row r="735" spans="1:17">
@@ -21186,16 +21192,16 @@
         <x:v>1404000911</x:v>
       </x:c>
       <x:c r="C735" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D735" s="0" t="s">
-        <x:v>1573</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="G735" s="0" t="s">
-        <x:v>1573</x:v>
+        <x:v>1574</x:v>
       </x:c>
       <x:c r="I735" s="0" t="s">
-        <x:v>1574</x:v>
+        <x:v>1575</x:v>
       </x:c>
     </x:row>
     <x:row r="736" spans="1:17">
@@ -21206,16 +21212,16 @@
         <x:v>1404000912</x:v>
       </x:c>
       <x:c r="C736" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D736" s="0" t="s">
-        <x:v>1575</x:v>
+        <x:v>1576</x:v>
       </x:c>
       <x:c r="G736" s="0" t="s">
-        <x:v>1576</x:v>
+        <x:v>1577</x:v>
       </x:c>
       <x:c r="I736" s="0" t="s">
-        <x:v>1577</x:v>
+        <x:v>1578</x:v>
       </x:c>
     </x:row>
     <x:row r="737" spans="1:17">
@@ -21226,16 +21232,16 @@
         <x:v>1404000913</x:v>
       </x:c>
       <x:c r="C737" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D737" s="0" t="s">
-        <x:v>1578</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="G737" s="0" t="s">
-        <x:v>1578</x:v>
+        <x:v>1579</x:v>
       </x:c>
       <x:c r="I737" s="0" t="s">
-        <x:v>1579</x:v>
+        <x:v>1580</x:v>
       </x:c>
     </x:row>
     <x:row r="738" spans="1:17">
@@ -21246,16 +21252,16 @@
         <x:v>1404000914</x:v>
       </x:c>
       <x:c r="C738" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D738" s="0" t="s">
-        <x:v>1580</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="G738" s="0" t="s">
-        <x:v>1580</x:v>
+        <x:v>1581</x:v>
       </x:c>
       <x:c r="I738" s="0" t="s">
-        <x:v>1581</x:v>
+        <x:v>1582</x:v>
       </x:c>
     </x:row>
     <x:row r="739" spans="1:17">
@@ -21266,16 +21272,16 @@
         <x:v>1404000915</x:v>
       </x:c>
       <x:c r="C739" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D739" s="0" t="s">
-        <x:v>1582</x:v>
+        <x:v>1583</x:v>
       </x:c>
       <x:c r="G739" s="0" t="s">
-        <x:v>1582</x:v>
+        <x:v>1583</x:v>
       </x:c>
       <x:c r="I739" s="0" t="s">
-        <x:v>1583</x:v>
+        <x:v>1584</x:v>
       </x:c>
     </x:row>
     <x:row r="740" spans="1:17">
@@ -21286,16 +21292,16 @@
         <x:v>1404000916</x:v>
       </x:c>
       <x:c r="C740" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D740" s="0" t="s">
-        <x:v>1584</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="G740" s="0" t="s">
-        <x:v>1584</x:v>
+        <x:v>1585</x:v>
       </x:c>
       <x:c r="I740" s="0" t="s">
-        <x:v>1585</x:v>
+        <x:v>1586</x:v>
       </x:c>
     </x:row>
     <x:row r="741" spans="1:17">
@@ -21306,16 +21312,16 @@
         <x:v>1404000917</x:v>
       </x:c>
       <x:c r="C741" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D741" s="0" t="s">
-        <x:v>1586</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="G741" s="0" t="s">
-        <x:v>1586</x:v>
+        <x:v>1587</x:v>
       </x:c>
       <x:c r="I741" s="0" t="s">
-        <x:v>1587</x:v>
+        <x:v>1588</x:v>
       </x:c>
     </x:row>
     <x:row r="742" spans="1:17">
@@ -21326,16 +21332,16 @@
         <x:v>1404000918</x:v>
       </x:c>
       <x:c r="C742" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D742" s="0" t="s">
-        <x:v>1588</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="G742" s="0" t="s">
-        <x:v>1588</x:v>
+        <x:v>1589</x:v>
       </x:c>
       <x:c r="I742" s="0" t="s">
-        <x:v>1589</x:v>
+        <x:v>1590</x:v>
       </x:c>
     </x:row>
     <x:row r="743" spans="1:17">
@@ -21346,16 +21352,16 @@
         <x:v>1404000919</x:v>
       </x:c>
       <x:c r="C743" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D743" s="0" t="s">
-        <x:v>1590</x:v>
+        <x:v>1591</x:v>
       </x:c>
       <x:c r="G743" s="0" t="s">
-        <x:v>1591</x:v>
+        <x:v>1592</x:v>
       </x:c>
       <x:c r="I743" s="0" t="s">
-        <x:v>1592</x:v>
+        <x:v>1593</x:v>
       </x:c>
     </x:row>
     <x:row r="744" spans="1:17">
@@ -21366,16 +21372,16 @@
         <x:v>1404000920</x:v>
       </x:c>
       <x:c r="C744" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D744" s="0" t="s">
-        <x:v>1593</x:v>
+        <x:v>1594</x:v>
       </x:c>
       <x:c r="G744" s="0" t="s">
-        <x:v>1593</x:v>
+        <x:v>1594</x:v>
       </x:c>
       <x:c r="I744" s="0" t="s">
-        <x:v>1594</x:v>
+        <x:v>1595</x:v>
       </x:c>
     </x:row>
     <x:row r="745" spans="1:17">
@@ -21386,16 +21392,16 @@
         <x:v>1404000921</x:v>
       </x:c>
       <x:c r="C745" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D745" s="0" t="s">
-        <x:v>1596</x:v>
+        <x:v>1597</x:v>
       </x:c>
       <x:c r="G745" s="0" t="s">
-        <x:v>1596</x:v>
+        <x:v>1597</x:v>
       </x:c>
       <x:c r="I745" s="0" t="s">
-        <x:v>1597</x:v>
+        <x:v>1598</x:v>
       </x:c>
     </x:row>
     <x:row r="746" spans="1:17">
@@ -21406,16 +21412,16 @@
         <x:v>1404000922</x:v>
       </x:c>
       <x:c r="C746" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D746" s="0" t="s">
-        <x:v>1598</x:v>
+        <x:v>1599</x:v>
       </x:c>
       <x:c r="G746" s="0" t="s">
-        <x:v>1599</x:v>
+        <x:v>1600</x:v>
       </x:c>
       <x:c r="I746" s="0" t="s">
-        <x:v>1600</x:v>
+        <x:v>1601</x:v>
       </x:c>
     </x:row>
     <x:row r="747" spans="1:17">
@@ -21426,16 +21432,16 @@
         <x:v>1404000923</x:v>
       </x:c>
       <x:c r="C747" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D747" s="0" t="s">
-        <x:v>1598</x:v>
+        <x:v>1599</x:v>
       </x:c>
       <x:c r="G747" s="0" t="s">
-        <x:v>1601</x:v>
+        <x:v>1602</x:v>
       </x:c>
       <x:c r="I747" s="0" t="s">
-        <x:v>1602</x:v>
+        <x:v>1603</x:v>
       </x:c>
     </x:row>
     <x:row r="748" spans="1:17">
@@ -21446,16 +21452,16 @@
         <x:v>1404000924</x:v>
       </x:c>
       <x:c r="C748" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D748" s="0" t="s">
-        <x:v>1603</x:v>
+        <x:v>1604</x:v>
       </x:c>
       <x:c r="G748" s="0" t="s">
-        <x:v>1603</x:v>
+        <x:v>1604</x:v>
       </x:c>
       <x:c r="I748" s="0" t="s">
-        <x:v>1604</x:v>
+        <x:v>1605</x:v>
       </x:c>
     </x:row>
     <x:row r="749" spans="1:17">
@@ -21466,16 +21472,16 @@
         <x:v>1404000925</x:v>
       </x:c>
       <x:c r="C749" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D749" s="0" t="s">
-        <x:v>1605</x:v>
+        <x:v>1606</x:v>
       </x:c>
       <x:c r="G749" s="0" t="s">
-        <x:v>1605</x:v>
+        <x:v>1606</x:v>
       </x:c>
       <x:c r="I749" s="0" t="s">
-        <x:v>1606</x:v>
+        <x:v>1607</x:v>
       </x:c>
     </x:row>
     <x:row r="750" spans="1:17">
@@ -21486,16 +21492,16 @@
         <x:v>1404000926</x:v>
       </x:c>
       <x:c r="C750" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D750" s="0" t="s">
-        <x:v>1607</x:v>
+        <x:v>1608</x:v>
       </x:c>
       <x:c r="G750" s="0" t="s">
-        <x:v>1608</x:v>
+        <x:v>1609</x:v>
       </x:c>
       <x:c r="I750" s="0" t="s">
-        <x:v>1609</x:v>
+        <x:v>1610</x:v>
       </x:c>
     </x:row>
     <x:row r="751" spans="1:17">
@@ -21506,16 +21512,16 @@
         <x:v>1404000927</x:v>
       </x:c>
       <x:c r="C751" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D751" s="0" t="s">
-        <x:v>1610</x:v>
+        <x:v>1611</x:v>
       </x:c>
       <x:c r="G751" s="0" t="s">
-        <x:v>1610</x:v>
+        <x:v>1611</x:v>
       </x:c>
       <x:c r="I751" s="0" t="s">
-        <x:v>1611</x:v>
+        <x:v>1612</x:v>
       </x:c>
     </x:row>
     <x:row r="752" spans="1:17">
@@ -21526,16 +21532,16 @@
         <x:v>1404000928</x:v>
       </x:c>
       <x:c r="C752" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D752" s="0" t="s">
-        <x:v>1612</x:v>
+        <x:v>1613</x:v>
       </x:c>
       <x:c r="G752" s="0" t="s">
-        <x:v>1612</x:v>
+        <x:v>1613</x:v>
       </x:c>
       <x:c r="I752" s="0" t="s">
-        <x:v>1613</x:v>
+        <x:v>1614</x:v>
       </x:c>
     </x:row>
     <x:row r="753" spans="1:17">
@@ -21546,16 +21552,16 @@
         <x:v>1404000930</x:v>
       </x:c>
       <x:c r="C753" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D753" s="0" t="s">
-        <x:v>1614</x:v>
+        <x:v>1615</x:v>
       </x:c>
       <x:c r="G753" s="0" t="s">
-        <x:v>1614</x:v>
+        <x:v>1615</x:v>
       </x:c>
       <x:c r="I753" s="0" t="s">
-        <x:v>1615</x:v>
+        <x:v>1616</x:v>
       </x:c>
     </x:row>
     <x:row r="754" spans="1:17">
@@ -21569,13 +21575,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D754" s="0" t="s">
-        <x:v>1616</x:v>
+        <x:v>1617</x:v>
       </x:c>
       <x:c r="G754" s="0" t="s">
-        <x:v>1616</x:v>
+        <x:v>1617</x:v>
       </x:c>
       <x:c r="I754" s="0" t="s">
-        <x:v>1617</x:v>
+        <x:v>1618</x:v>
       </x:c>
     </x:row>
     <x:row r="755" spans="1:17">
@@ -21589,13 +21595,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D755" s="0" t="s">
-        <x:v>1618</x:v>
+        <x:v>1619</x:v>
       </x:c>
       <x:c r="G755" s="0" t="s">
-        <x:v>1618</x:v>
+        <x:v>1619</x:v>
       </x:c>
       <x:c r="I755" s="0" t="s">
-        <x:v>1619</x:v>
+        <x:v>1620</x:v>
       </x:c>
     </x:row>
     <x:row r="756" spans="1:17">
@@ -21609,13 +21615,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D756" s="0" t="s">
-        <x:v>1620</x:v>
+        <x:v>1621</x:v>
       </x:c>
       <x:c r="G756" s="0" t="s">
-        <x:v>1620</x:v>
+        <x:v>1621</x:v>
       </x:c>
       <x:c r="I756" s="0" t="s">
-        <x:v>1621</x:v>
+        <x:v>1622</x:v>
       </x:c>
     </x:row>
     <x:row r="757" spans="1:17">
@@ -21629,13 +21635,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D757" s="0" t="s">
-        <x:v>1622</x:v>
+        <x:v>1623</x:v>
       </x:c>
       <x:c r="G757" s="0" t="s">
-        <x:v>1622</x:v>
+        <x:v>1623</x:v>
       </x:c>
       <x:c r="I757" s="0" t="s">
-        <x:v>1623</x:v>
+        <x:v>1624</x:v>
       </x:c>
     </x:row>
     <x:row r="758" spans="1:17">
@@ -21649,13 +21655,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D758" s="0" t="s">
-        <x:v>1624</x:v>
+        <x:v>1625</x:v>
       </x:c>
       <x:c r="G758" s="0" t="s">
-        <x:v>1624</x:v>
+        <x:v>1625</x:v>
       </x:c>
       <x:c r="I758" s="0" t="s">
-        <x:v>1625</x:v>
+        <x:v>1626</x:v>
       </x:c>
     </x:row>
     <x:row r="759" spans="1:17">
@@ -21669,13 +21675,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D759" s="0" t="s">
-        <x:v>1626</x:v>
+        <x:v>1627</x:v>
       </x:c>
       <x:c r="G759" s="0" t="s">
-        <x:v>1626</x:v>
+        <x:v>1627</x:v>
       </x:c>
       <x:c r="I759" s="0" t="s">
-        <x:v>1627</x:v>
+        <x:v>1628</x:v>
       </x:c>
     </x:row>
     <x:row r="760" spans="1:17">
@@ -21689,13 +21695,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D760" s="0" t="s">
-        <x:v>1628</x:v>
+        <x:v>1629</x:v>
       </x:c>
       <x:c r="G760" s="0" t="s">
-        <x:v>1628</x:v>
+        <x:v>1629</x:v>
       </x:c>
       <x:c r="I760" s="0" t="s">
-        <x:v>1629</x:v>
+        <x:v>1630</x:v>
       </x:c>
     </x:row>
     <x:row r="761" spans="1:17">
@@ -21709,13 +21715,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D761" s="0" t="s">
-        <x:v>1630</x:v>
+        <x:v>1631</x:v>
       </x:c>
       <x:c r="G761" s="0" t="s">
-        <x:v>1630</x:v>
+        <x:v>1631</x:v>
       </x:c>
       <x:c r="I761" s="0" t="s">
-        <x:v>1631</x:v>
+        <x:v>1632</x:v>
       </x:c>
     </x:row>
     <x:row r="762" spans="1:17">
@@ -21729,13 +21735,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D762" s="0" t="s">
-        <x:v>1632</x:v>
+        <x:v>1633</x:v>
       </x:c>
       <x:c r="G762" s="0" t="s">
-        <x:v>1632</x:v>
+        <x:v>1633</x:v>
       </x:c>
       <x:c r="I762" s="0" t="s">
-        <x:v>1633</x:v>
+        <x:v>1634</x:v>
       </x:c>
     </x:row>
     <x:row r="763" spans="1:17">
@@ -21749,13 +21755,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D763" s="0" t="s">
-        <x:v>1634</x:v>
+        <x:v>1635</x:v>
       </x:c>
       <x:c r="G763" s="0" t="s">
-        <x:v>1634</x:v>
+        <x:v>1635</x:v>
       </x:c>
       <x:c r="I763" s="0" t="s">
-        <x:v>1635</x:v>
+        <x:v>1636</x:v>
       </x:c>
     </x:row>
     <x:row r="764" spans="1:17">
@@ -21769,13 +21775,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D764" s="0" t="s">
-        <x:v>1636</x:v>
+        <x:v>1637</x:v>
       </x:c>
       <x:c r="G764" s="0" t="s">
-        <x:v>1636</x:v>
+        <x:v>1637</x:v>
       </x:c>
       <x:c r="I764" s="0" t="s">
-        <x:v>1637</x:v>
+        <x:v>1638</x:v>
       </x:c>
     </x:row>
     <x:row r="765" spans="1:17">
@@ -21789,13 +21795,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D765" s="0" t="s">
-        <x:v>1638</x:v>
+        <x:v>1639</x:v>
       </x:c>
       <x:c r="G765" s="0" t="s">
-        <x:v>1638</x:v>
+        <x:v>1639</x:v>
       </x:c>
       <x:c r="I765" s="0" t="s">
-        <x:v>1639</x:v>
+        <x:v>1640</x:v>
       </x:c>
     </x:row>
     <x:row r="766" spans="1:17">
@@ -21809,13 +21815,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D766" s="0" t="s">
-        <x:v>1640</x:v>
+        <x:v>1641</x:v>
       </x:c>
       <x:c r="G766" s="0" t="s">
-        <x:v>1640</x:v>
+        <x:v>1641</x:v>
       </x:c>
       <x:c r="I766" s="0" t="s">
-        <x:v>1641</x:v>
+        <x:v>1642</x:v>
       </x:c>
     </x:row>
     <x:row r="767" spans="1:17">
@@ -21829,13 +21835,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D767" s="0" t="s">
-        <x:v>1642</x:v>
+        <x:v>1643</x:v>
       </x:c>
       <x:c r="G767" s="0" t="s">
-        <x:v>1642</x:v>
+        <x:v>1643</x:v>
       </x:c>
       <x:c r="I767" s="0" t="s">
-        <x:v>1643</x:v>
+        <x:v>1644</x:v>
       </x:c>
     </x:row>
     <x:row r="768" spans="1:17">
@@ -21849,13 +21855,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D768" s="0" t="s">
-        <x:v>1644</x:v>
+        <x:v>1645</x:v>
       </x:c>
       <x:c r="G768" s="0" t="s">
-        <x:v>1644</x:v>
+        <x:v>1645</x:v>
       </x:c>
       <x:c r="I768" s="0" t="s">
-        <x:v>1645</x:v>
+        <x:v>1646</x:v>
       </x:c>
     </x:row>
     <x:row r="769" spans="1:17">
@@ -21869,13 +21875,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D769" s="0" t="s">
-        <x:v>1646</x:v>
+        <x:v>1647</x:v>
       </x:c>
       <x:c r="G769" s="0" t="s">
-        <x:v>1646</x:v>
+        <x:v>1647</x:v>
       </x:c>
       <x:c r="I769" s="0" t="s">
-        <x:v>1647</x:v>
+        <x:v>1648</x:v>
       </x:c>
     </x:row>
     <x:row r="770" spans="1:17">
@@ -21889,13 +21895,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D770" s="0" t="s">
-        <x:v>1648</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="G770" s="0" t="s">
-        <x:v>1648</x:v>
+        <x:v>1649</x:v>
       </x:c>
       <x:c r="I770" s="0" t="s">
-        <x:v>1649</x:v>
+        <x:v>1650</x:v>
       </x:c>
     </x:row>
     <x:row r="771" spans="1:17">
@@ -21909,13 +21915,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D771" s="0" t="s">
-        <x:v>1650</x:v>
+        <x:v>1651</x:v>
       </x:c>
       <x:c r="G771" s="0" t="s">
-        <x:v>1650</x:v>
+        <x:v>1651</x:v>
       </x:c>
       <x:c r="I771" s="0" t="s">
-        <x:v>1651</x:v>
+        <x:v>1652</x:v>
       </x:c>
     </x:row>
     <x:row r="772" spans="1:17">
@@ -21929,13 +21935,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D772" s="0" t="s">
-        <x:v>1652</x:v>
+        <x:v>1653</x:v>
       </x:c>
       <x:c r="G772" s="0" t="s">
-        <x:v>1652</x:v>
+        <x:v>1653</x:v>
       </x:c>
       <x:c r="I772" s="0" t="s">
-        <x:v>1653</x:v>
+        <x:v>1654</x:v>
       </x:c>
     </x:row>
     <x:row r="773" spans="1:17">
@@ -21949,13 +21955,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D773" s="0" t="s">
-        <x:v>1654</x:v>
+        <x:v>1655</x:v>
       </x:c>
       <x:c r="G773" s="0" t="s">
-        <x:v>1654</x:v>
+        <x:v>1655</x:v>
       </x:c>
       <x:c r="I773" s="0" t="s">
-        <x:v>1655</x:v>
+        <x:v>1656</x:v>
       </x:c>
     </x:row>
     <x:row r="774" spans="1:17">
@@ -21969,13 +21975,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D774" s="0" t="s">
-        <x:v>1656</x:v>
+        <x:v>1657</x:v>
       </x:c>
       <x:c r="G774" s="0" t="s">
-        <x:v>1656</x:v>
+        <x:v>1657</x:v>
       </x:c>
       <x:c r="I774" s="0" t="s">
-        <x:v>1657</x:v>
+        <x:v>1658</x:v>
       </x:c>
     </x:row>
     <x:row r="775" spans="1:17">
@@ -21989,13 +21995,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D775" s="0" t="s">
-        <x:v>1658</x:v>
+        <x:v>1659</x:v>
       </x:c>
       <x:c r="G775" s="0" t="s">
-        <x:v>1658</x:v>
+        <x:v>1659</x:v>
       </x:c>
       <x:c r="I775" s="0" t="s">
-        <x:v>1659</x:v>
+        <x:v>1660</x:v>
       </x:c>
     </x:row>
     <x:row r="776" spans="1:17">
@@ -22009,13 +22015,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D776" s="0" t="s">
-        <x:v>1660</x:v>
+        <x:v>1661</x:v>
       </x:c>
       <x:c r="G776" s="0" t="s">
-        <x:v>1660</x:v>
+        <x:v>1661</x:v>
       </x:c>
       <x:c r="I776" s="0" t="s">
-        <x:v>1661</x:v>
+        <x:v>1662</x:v>
       </x:c>
     </x:row>
     <x:row r="777" spans="1:17">
@@ -22029,13 +22035,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D777" s="0" t="s">
-        <x:v>1662</x:v>
+        <x:v>1663</x:v>
       </x:c>
       <x:c r="G777" s="0" t="s">
-        <x:v>1662</x:v>
+        <x:v>1663</x:v>
       </x:c>
       <x:c r="I777" s="0" t="s">
-        <x:v>1663</x:v>
+        <x:v>1664</x:v>
       </x:c>
     </x:row>
     <x:row r="778" spans="1:17">
@@ -22049,13 +22055,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D778" s="0" t="s">
-        <x:v>1664</x:v>
+        <x:v>1665</x:v>
       </x:c>
       <x:c r="G778" s="0" t="s">
-        <x:v>1664</x:v>
+        <x:v>1665</x:v>
       </x:c>
       <x:c r="I778" s="0" t="s">
-        <x:v>1665</x:v>
+        <x:v>1666</x:v>
       </x:c>
     </x:row>
     <x:row r="779" spans="1:17">
@@ -22069,13 +22075,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D779" s="0" t="s">
-        <x:v>1666</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="G779" s="0" t="s">
-        <x:v>1666</x:v>
+        <x:v>1667</x:v>
       </x:c>
       <x:c r="I779" s="0" t="s">
-        <x:v>1667</x:v>
+        <x:v>1668</x:v>
       </x:c>
     </x:row>
     <x:row r="780" spans="1:17">
@@ -22089,13 +22095,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D780" s="0" t="s">
-        <x:v>1668</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="G780" s="0" t="s">
-        <x:v>1668</x:v>
+        <x:v>1669</x:v>
       </x:c>
       <x:c r="I780" s="0" t="s">
-        <x:v>1669</x:v>
+        <x:v>1670</x:v>
       </x:c>
     </x:row>
     <x:row r="781" spans="1:17">
@@ -22109,13 +22115,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D781" s="0" t="s">
-        <x:v>1670</x:v>
+        <x:v>1671</x:v>
       </x:c>
       <x:c r="G781" s="0" t="s">
-        <x:v>1670</x:v>
+        <x:v>1671</x:v>
       </x:c>
       <x:c r="I781" s="0" t="s">
-        <x:v>1671</x:v>
+        <x:v>1672</x:v>
       </x:c>
     </x:row>
     <x:row r="782" spans="1:17">
@@ -22129,13 +22135,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D782" s="0" t="s">
-        <x:v>1672</x:v>
+        <x:v>1673</x:v>
       </x:c>
       <x:c r="G782" s="0" t="s">
-        <x:v>1672</x:v>
+        <x:v>1673</x:v>
       </x:c>
       <x:c r="I782" s="0" t="s">
-        <x:v>1673</x:v>
+        <x:v>1674</x:v>
       </x:c>
     </x:row>
     <x:row r="783" spans="1:17">
@@ -22149,13 +22155,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D783" s="0" t="s">
-        <x:v>1674</x:v>
+        <x:v>1675</x:v>
       </x:c>
       <x:c r="G783" s="0" t="s">
-        <x:v>1674</x:v>
+        <x:v>1675</x:v>
       </x:c>
       <x:c r="I783" s="0" t="s">
-        <x:v>1675</x:v>
+        <x:v>1676</x:v>
       </x:c>
     </x:row>
     <x:row r="784" spans="1:17">
@@ -22169,13 +22175,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D784" s="0" t="s">
-        <x:v>1676</x:v>
+        <x:v>1677</x:v>
       </x:c>
       <x:c r="G784" s="0" t="s">
-        <x:v>1676</x:v>
+        <x:v>1677</x:v>
       </x:c>
       <x:c r="I784" s="0" t="s">
-        <x:v>1677</x:v>
+        <x:v>1678</x:v>
       </x:c>
     </x:row>
     <x:row r="785" spans="1:17">
@@ -22189,13 +22195,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D785" s="0" t="s">
-        <x:v>1678</x:v>
+        <x:v>1679</x:v>
       </x:c>
       <x:c r="G785" s="0" t="s">
-        <x:v>1678</x:v>
+        <x:v>1679</x:v>
       </x:c>
       <x:c r="I785" s="0" t="s">
-        <x:v>1679</x:v>
+        <x:v>1680</x:v>
       </x:c>
     </x:row>
     <x:row r="786" spans="1:17">
@@ -22209,13 +22215,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D786" s="0" t="s">
-        <x:v>1680</x:v>
+        <x:v>1681</x:v>
       </x:c>
       <x:c r="G786" s="0" t="s">
-        <x:v>1680</x:v>
+        <x:v>1681</x:v>
       </x:c>
       <x:c r="I786" s="0" t="s">
-        <x:v>1681</x:v>
+        <x:v>1682</x:v>
       </x:c>
     </x:row>
     <x:row r="787" spans="1:17">
@@ -22229,13 +22235,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D787" s="0" t="s">
-        <x:v>1682</x:v>
+        <x:v>1683</x:v>
       </x:c>
       <x:c r="G787" s="0" t="s">
-        <x:v>1682</x:v>
+        <x:v>1683</x:v>
       </x:c>
       <x:c r="I787" s="0" t="s">
-        <x:v>1683</x:v>
+        <x:v>1684</x:v>
       </x:c>
     </x:row>
     <x:row r="788" spans="1:17">
@@ -22249,13 +22255,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D788" s="0" t="s">
-        <x:v>1684</x:v>
+        <x:v>1685</x:v>
       </x:c>
       <x:c r="G788" s="0" t="s">
-        <x:v>1684</x:v>
+        <x:v>1685</x:v>
       </x:c>
       <x:c r="I788" s="0" t="s">
-        <x:v>1685</x:v>
+        <x:v>1686</x:v>
       </x:c>
     </x:row>
     <x:row r="789" spans="1:17">
@@ -22269,13 +22275,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D789" s="0" t="s">
-        <x:v>1686</x:v>
+        <x:v>1687</x:v>
       </x:c>
       <x:c r="G789" s="0" t="s">
-        <x:v>1686</x:v>
+        <x:v>1687</x:v>
       </x:c>
       <x:c r="I789" s="0" t="s">
-        <x:v>1687</x:v>
+        <x:v>1688</x:v>
       </x:c>
     </x:row>
     <x:row r="790" spans="1:17">
@@ -22289,13 +22295,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D790" s="0" t="s">
-        <x:v>1688</x:v>
+        <x:v>1689</x:v>
       </x:c>
       <x:c r="G790" s="0" t="s">
-        <x:v>1688</x:v>
+        <x:v>1689</x:v>
       </x:c>
       <x:c r="I790" s="0" t="s">
-        <x:v>1689</x:v>
+        <x:v>1690</x:v>
       </x:c>
     </x:row>
     <x:row r="791" spans="1:17">
@@ -22309,13 +22315,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D791" s="0" t="s">
-        <x:v>1690</x:v>
+        <x:v>1691</x:v>
       </x:c>
       <x:c r="G791" s="0" t="s">
-        <x:v>1690</x:v>
+        <x:v>1691</x:v>
       </x:c>
       <x:c r="I791" s="0" t="s">
-        <x:v>1691</x:v>
+        <x:v>1692</x:v>
       </x:c>
     </x:row>
     <x:row r="792" spans="1:17">
@@ -22329,13 +22335,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D792" s="0" t="s">
-        <x:v>1692</x:v>
+        <x:v>1693</x:v>
       </x:c>
       <x:c r="G792" s="0" t="s">
-        <x:v>1692</x:v>
+        <x:v>1693</x:v>
       </x:c>
       <x:c r="I792" s="0" t="s">
-        <x:v>1693</x:v>
+        <x:v>1694</x:v>
       </x:c>
     </x:row>
     <x:row r="793" spans="1:17">
@@ -22349,13 +22355,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D793" s="0" t="s">
-        <x:v>1694</x:v>
+        <x:v>1695</x:v>
       </x:c>
       <x:c r="G793" s="0" t="s">
-        <x:v>1694</x:v>
+        <x:v>1695</x:v>
       </x:c>
       <x:c r="I793" s="0" t="s">
-        <x:v>1695</x:v>
+        <x:v>1696</x:v>
       </x:c>
     </x:row>
     <x:row r="794" spans="1:17">
@@ -22369,13 +22375,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D794" s="0" t="s">
-        <x:v>1696</x:v>
+        <x:v>1697</x:v>
       </x:c>
       <x:c r="G794" s="0" t="s">
-        <x:v>1696</x:v>
+        <x:v>1697</x:v>
       </x:c>
       <x:c r="I794" s="0" t="s">
-        <x:v>1697</x:v>
+        <x:v>1698</x:v>
       </x:c>
     </x:row>
     <x:row r="795" spans="1:17">
@@ -22389,13 +22395,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D795" s="0" t="s">
-        <x:v>1698</x:v>
+        <x:v>1699</x:v>
       </x:c>
       <x:c r="G795" s="0" t="s">
-        <x:v>1698</x:v>
+        <x:v>1699</x:v>
       </x:c>
       <x:c r="I795" s="0" t="s">
-        <x:v>1699</x:v>
+        <x:v>1700</x:v>
       </x:c>
     </x:row>
     <x:row r="796" spans="1:17">
@@ -22406,10 +22412,10 @@
         <x:v>1404000973</x:v>
       </x:c>
       <x:c r="C796" s="0" t="s">
-        <x:v>1700</x:v>
+        <x:v>1701</x:v>
       </x:c>
       <x:c r="D796" s="0" t="s">
-        <x:v>1701</x:v>
+        <x:v>1702</x:v>
       </x:c>
     </x:row>
     <x:row r="797" spans="1:17">
@@ -22420,16 +22426,16 @@
         <x:v>1404000976</x:v>
       </x:c>
       <x:c r="C797" s="0" t="s">
-        <x:v>1595</x:v>
+        <x:v>1596</x:v>
       </x:c>
       <x:c r="D797" s="0" t="s">
-        <x:v>1702</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="G797" s="0" t="s">
-        <x:v>1702</x:v>
+        <x:v>1703</x:v>
       </x:c>
       <x:c r="I797" s="0" t="s">
-        <x:v>1703</x:v>
+        <x:v>1704</x:v>
       </x:c>
     </x:row>
     <x:row r="798" spans="1:17">
@@ -22443,13 +22449,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D798" s="0" t="s">
-        <x:v>1704</x:v>
+        <x:v>1705</x:v>
       </x:c>
       <x:c r="G798" s="0" t="s">
-        <x:v>1704</x:v>
+        <x:v>1705</x:v>
       </x:c>
       <x:c r="I798" s="0" t="s">
-        <x:v>1705</x:v>
+        <x:v>1706</x:v>
       </x:c>
     </x:row>
     <x:row r="799" spans="1:17">
@@ -22460,10 +22466,10 @@
         <x:v>1404000978</x:v>
       </x:c>
       <x:c r="C799" s="0" t="s">
-        <x:v>1706</x:v>
+        <x:v>1707</x:v>
       </x:c>
       <x:c r="D799" s="0" t="s">
-        <x:v>1707</x:v>
+        <x:v>1708</x:v>
       </x:c>
     </x:row>
     <x:row r="800" spans="1:17">
@@ -22474,10 +22480,10 @@
         <x:v>1404000979</x:v>
       </x:c>
       <x:c r="C800" s="0" t="s">
-        <x:v>1706</x:v>
+        <x:v>1707</x:v>
       </x:c>
       <x:c r="D800" s="0" t="s">
-        <x:v>1708</x:v>
+        <x:v>1709</x:v>
       </x:c>
     </x:row>
     <x:row r="801" spans="1:17">
@@ -22488,10 +22494,10 @@
         <x:v>1404000980</x:v>
       </x:c>
       <x:c r="C801" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D801" s="0" t="s">
-        <x:v>1709</x:v>
+        <x:v>1710</x:v>
       </x:c>
     </x:row>
     <x:row r="802" spans="1:17">
@@ -22502,10 +22508,10 @@
         <x:v>1404000981</x:v>
       </x:c>
       <x:c r="C802" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D802" s="0" t="s">
-        <x:v>1710</x:v>
+        <x:v>1711</x:v>
       </x:c>
     </x:row>
     <x:row r="803" spans="1:17">
@@ -22516,10 +22522,10 @@
         <x:v>1404000982</x:v>
       </x:c>
       <x:c r="C803" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D803" s="0" t="s">
-        <x:v>1711</x:v>
+        <x:v>1712</x:v>
       </x:c>
     </x:row>
     <x:row r="804" spans="1:17">
@@ -22530,10 +22536,10 @@
         <x:v>1404000983</x:v>
       </x:c>
       <x:c r="C804" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D804" s="0" t="s">
-        <x:v>1712</x:v>
+        <x:v>1713</x:v>
       </x:c>
     </x:row>
     <x:row r="805" spans="1:17">
@@ -22544,10 +22550,10 @@
         <x:v>1404000984</x:v>
       </x:c>
       <x:c r="C805" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D805" s="0" t="s">
-        <x:v>1713</x:v>
+        <x:v>1714</x:v>
       </x:c>
     </x:row>
     <x:row r="806" spans="1:17">
@@ -22558,10 +22564,10 @@
         <x:v>1404000985</x:v>
       </x:c>
       <x:c r="C806" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D806" s="0" t="s">
-        <x:v>1714</x:v>
+        <x:v>1715</x:v>
       </x:c>
     </x:row>
     <x:row r="807" spans="1:17">
@@ -22572,10 +22578,10 @@
         <x:v>1404000986</x:v>
       </x:c>
       <x:c r="C807" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D807" s="0" t="s">
-        <x:v>1715</x:v>
+        <x:v>1716</x:v>
       </x:c>
     </x:row>
     <x:row r="808" spans="1:17">
@@ -22586,10 +22592,10 @@
         <x:v>1404000987</x:v>
       </x:c>
       <x:c r="C808" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D808" s="0" t="s">
-        <x:v>1716</x:v>
+        <x:v>1717</x:v>
       </x:c>
     </x:row>
     <x:row r="809" spans="1:17">
@@ -22600,10 +22606,10 @@
         <x:v>1404000988</x:v>
       </x:c>
       <x:c r="C809" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D809" s="0" t="s">
-        <x:v>1717</x:v>
+        <x:v>1718</x:v>
       </x:c>
     </x:row>
     <x:row r="810" spans="1:17">
@@ -22614,10 +22620,10 @@
         <x:v>1404000989</x:v>
       </x:c>
       <x:c r="C810" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D810" s="0" t="s">
-        <x:v>1718</x:v>
+        <x:v>1719</x:v>
       </x:c>
     </x:row>
     <x:row r="811" spans="1:17">
@@ -22628,10 +22634,10 @@
         <x:v>1404000990</x:v>
       </x:c>
       <x:c r="C811" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D811" s="0" t="s">
-        <x:v>1719</x:v>
+        <x:v>1720</x:v>
       </x:c>
     </x:row>
     <x:row r="812" spans="1:17">
@@ -22642,10 +22648,10 @@
         <x:v>1404000991</x:v>
       </x:c>
       <x:c r="C812" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D812" s="0" t="s">
-        <x:v>1720</x:v>
+        <x:v>1721</x:v>
       </x:c>
     </x:row>
     <x:row r="813" spans="1:17">
@@ -22656,10 +22662,10 @@
         <x:v>1404000992</x:v>
       </x:c>
       <x:c r="C813" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D813" s="0" t="s">
-        <x:v>1721</x:v>
+        <x:v>1722</x:v>
       </x:c>
     </x:row>
     <x:row r="814" spans="1:17">
@@ -22670,10 +22676,10 @@
         <x:v>1404000993</x:v>
       </x:c>
       <x:c r="C814" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D814" s="0" t="s">
-        <x:v>1722</x:v>
+        <x:v>1723</x:v>
       </x:c>
     </x:row>
     <x:row r="815" spans="1:17">
@@ -22684,10 +22690,10 @@
         <x:v>1404000994</x:v>
       </x:c>
       <x:c r="C815" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D815" s="0" t="s">
-        <x:v>1723</x:v>
+        <x:v>1724</x:v>
       </x:c>
     </x:row>
     <x:row r="816" spans="1:17">
@@ -22698,10 +22704,10 @@
         <x:v>1404000995</x:v>
       </x:c>
       <x:c r="C816" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D816" s="0" t="s">
-        <x:v>1724</x:v>
+        <x:v>1725</x:v>
       </x:c>
     </x:row>
     <x:row r="817" spans="1:17">
@@ -22712,10 +22718,10 @@
         <x:v>1404000996</x:v>
       </x:c>
       <x:c r="C817" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D817" s="0" t="s">
-        <x:v>1725</x:v>
+        <x:v>1726</x:v>
       </x:c>
     </x:row>
     <x:row r="818" spans="1:17">
@@ -22726,10 +22732,10 @@
         <x:v>1404000997</x:v>
       </x:c>
       <x:c r="C818" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D818" s="0" t="s">
-        <x:v>1726</x:v>
+        <x:v>1727</x:v>
       </x:c>
     </x:row>
     <x:row r="819" spans="1:17">
@@ -22740,10 +22746,10 @@
         <x:v>1404000998</x:v>
       </x:c>
       <x:c r="C819" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D819" s="0" t="s">
-        <x:v>1727</x:v>
+        <x:v>1728</x:v>
       </x:c>
     </x:row>
     <x:row r="820" spans="1:17">
@@ -22754,10 +22760,10 @@
         <x:v>1404000999</x:v>
       </x:c>
       <x:c r="C820" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D820" s="0" t="s">
-        <x:v>1728</x:v>
+        <x:v>1729</x:v>
       </x:c>
     </x:row>
     <x:row r="821" spans="1:17">
@@ -22768,10 +22774,10 @@
         <x:v>1404001000</x:v>
       </x:c>
       <x:c r="C821" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D821" s="0" t="s">
-        <x:v>1729</x:v>
+        <x:v>1730</x:v>
       </x:c>
     </x:row>
     <x:row r="822" spans="1:17">
@@ -22782,10 +22788,10 @@
         <x:v>1404001001</x:v>
       </x:c>
       <x:c r="C822" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D822" s="0" t="s">
-        <x:v>1730</x:v>
+        <x:v>1731</x:v>
       </x:c>
     </x:row>
     <x:row r="823" spans="1:17">
@@ -22799,13 +22805,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D823" s="0" t="s">
-        <x:v>1731</x:v>
+        <x:v>1732</x:v>
       </x:c>
       <x:c r="G823" s="0" t="s">
-        <x:v>1731</x:v>
+        <x:v>1732</x:v>
       </x:c>
       <x:c r="I823" s="0" t="s">
-        <x:v>1731</x:v>
+        <x:v>1732</x:v>
       </x:c>
     </x:row>
     <x:row r="824" spans="1:17">
@@ -22819,13 +22825,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D824" s="0" t="s">
-        <x:v>1732</x:v>
+        <x:v>1733</x:v>
       </x:c>
       <x:c r="G824" s="0" t="s">
-        <x:v>1732</x:v>
+        <x:v>1733</x:v>
       </x:c>
       <x:c r="I824" s="0" t="s">
-        <x:v>1733</x:v>
+        <x:v>1734</x:v>
       </x:c>
     </x:row>
     <x:row r="825" spans="1:17">
@@ -22839,13 +22845,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D825" s="0" t="s">
-        <x:v>1734</x:v>
+        <x:v>1735</x:v>
       </x:c>
       <x:c r="G825" s="0" t="s">
-        <x:v>1734</x:v>
+        <x:v>1735</x:v>
       </x:c>
       <x:c r="I825" s="0" t="s">
-        <x:v>1735</x:v>
+        <x:v>1736</x:v>
       </x:c>
     </x:row>
     <x:row r="826" spans="1:17">
@@ -22859,13 +22865,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D826" s="0" t="s">
-        <x:v>1736</x:v>
+        <x:v>1737</x:v>
       </x:c>
       <x:c r="G826" s="0" t="s">
-        <x:v>1736</x:v>
+        <x:v>1737</x:v>
       </x:c>
       <x:c r="I826" s="0" t="s">
-        <x:v>1737</x:v>
+        <x:v>1738</x:v>
       </x:c>
     </x:row>
     <x:row r="827" spans="1:17">
@@ -22879,13 +22885,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D827" s="0" t="s">
-        <x:v>1738</x:v>
+        <x:v>1739</x:v>
       </x:c>
       <x:c r="G827" s="0" t="s">
-        <x:v>1738</x:v>
+        <x:v>1739</x:v>
       </x:c>
       <x:c r="I827" s="0" t="s">
-        <x:v>1739</x:v>
+        <x:v>1740</x:v>
       </x:c>
     </x:row>
     <x:row r="828" spans="1:17">
@@ -22899,13 +22905,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D828" s="0" t="s">
-        <x:v>1740</x:v>
+        <x:v>1741</x:v>
       </x:c>
       <x:c r="G828" s="0" t="s">
-        <x:v>1740</x:v>
+        <x:v>1741</x:v>
       </x:c>
       <x:c r="I828" s="0" t="s">
-        <x:v>1741</x:v>
+        <x:v>1742</x:v>
       </x:c>
     </x:row>
     <x:row r="829" spans="1:17">
@@ -22919,13 +22925,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D829" s="0" t="s">
-        <x:v>1742</x:v>
+        <x:v>1743</x:v>
       </x:c>
       <x:c r="G829" s="0" t="s">
-        <x:v>1742</x:v>
+        <x:v>1743</x:v>
       </x:c>
       <x:c r="I829" s="0" t="s">
-        <x:v>1743</x:v>
+        <x:v>1744</x:v>
       </x:c>
     </x:row>
     <x:row r="830" spans="1:17">
@@ -22939,13 +22945,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D830" s="0" t="s">
-        <x:v>1744</x:v>
+        <x:v>1745</x:v>
       </x:c>
       <x:c r="G830" s="0" t="s">
-        <x:v>1744</x:v>
+        <x:v>1745</x:v>
       </x:c>
       <x:c r="I830" s="0" t="s">
-        <x:v>1745</x:v>
+        <x:v>1746</x:v>
       </x:c>
     </x:row>
     <x:row r="831" spans="1:17">
@@ -22959,13 +22965,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D831" s="0" t="s">
-        <x:v>1746</x:v>
+        <x:v>1747</x:v>
       </x:c>
       <x:c r="G831" s="0" t="s">
-        <x:v>1746</x:v>
+        <x:v>1747</x:v>
       </x:c>
       <x:c r="I831" s="0" t="s">
-        <x:v>1747</x:v>
+        <x:v>1748</x:v>
       </x:c>
     </x:row>
     <x:row r="832" spans="1:17">
@@ -22979,13 +22985,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D832" s="0" t="s">
-        <x:v>1748</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="G832" s="0" t="s">
-        <x:v>1748</x:v>
+        <x:v>1749</x:v>
       </x:c>
       <x:c r="I832" s="0" t="s">
-        <x:v>1749</x:v>
+        <x:v>1750</x:v>
       </x:c>
     </x:row>
     <x:row r="833" spans="1:17">
@@ -22999,13 +23005,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D833" s="0" t="s">
-        <x:v>1750</x:v>
+        <x:v>1751</x:v>
       </x:c>
       <x:c r="G833" s="0" t="s">
-        <x:v>1750</x:v>
+        <x:v>1751</x:v>
       </x:c>
       <x:c r="I833" s="0" t="s">
-        <x:v>1751</x:v>
+        <x:v>1752</x:v>
       </x:c>
     </x:row>
     <x:row r="834" spans="1:17">
@@ -23019,13 +23025,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D834" s="0" t="s">
-        <x:v>1752</x:v>
+        <x:v>1753</x:v>
       </x:c>
       <x:c r="G834" s="0" t="s">
-        <x:v>1752</x:v>
+        <x:v>1753</x:v>
       </x:c>
       <x:c r="I834" s="0" t="s">
-        <x:v>1753</x:v>
+        <x:v>1754</x:v>
       </x:c>
     </x:row>
     <x:row r="835" spans="1:17">
@@ -23039,13 +23045,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D835" s="0" t="s">
-        <x:v>1754</x:v>
+        <x:v>1755</x:v>
       </x:c>
       <x:c r="G835" s="0" t="s">
-        <x:v>1754</x:v>
+        <x:v>1755</x:v>
       </x:c>
       <x:c r="I835" s="0" t="s">
-        <x:v>1755</x:v>
+        <x:v>1756</x:v>
       </x:c>
     </x:row>
     <x:row r="836" spans="1:17">
@@ -23056,10 +23062,10 @@
         <x:v>1404001015</x:v>
       </x:c>
       <x:c r="C836" s="0" t="s">
-        <x:v>1756</x:v>
+        <x:v>1757</x:v>
       </x:c>
       <x:c r="D836" s="0" t="s">
-        <x:v>1757</x:v>
+        <x:v>1758</x:v>
       </x:c>
     </x:row>
     <x:row r="837" spans="1:17">
@@ -23070,10 +23076,10 @@
         <x:v>1404001016</x:v>
       </x:c>
       <x:c r="C837" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D837" s="0" t="s">
-        <x:v>1758</x:v>
+        <x:v>1759</x:v>
       </x:c>
     </x:row>
     <x:row r="838" spans="1:17">
@@ -23087,13 +23093,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D838" s="0" t="s">
-        <x:v>1759</x:v>
+        <x:v>1760</x:v>
       </x:c>
       <x:c r="G838" s="0" t="s">
-        <x:v>1759</x:v>
+        <x:v>1760</x:v>
       </x:c>
       <x:c r="I838" s="0" t="s">
-        <x:v>1760</x:v>
+        <x:v>1761</x:v>
       </x:c>
     </x:row>
     <x:row r="839" spans="1:17">
@@ -23107,13 +23113,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D839" s="0" t="s">
-        <x:v>1761</x:v>
+        <x:v>1762</x:v>
       </x:c>
       <x:c r="G839" s="0" t="s">
-        <x:v>1761</x:v>
+        <x:v>1762</x:v>
       </x:c>
       <x:c r="I839" s="0" t="s">
-        <x:v>1762</x:v>
+        <x:v>1763</x:v>
       </x:c>
     </x:row>
     <x:row r="840" spans="1:17">
@@ -23127,13 +23133,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D840" s="0" t="s">
-        <x:v>1763</x:v>
+        <x:v>1764</x:v>
       </x:c>
       <x:c r="G840" s="0" t="s">
-        <x:v>1763</x:v>
+        <x:v>1764</x:v>
       </x:c>
       <x:c r="I840" s="0" t="s">
-        <x:v>1764</x:v>
+        <x:v>1765</x:v>
       </x:c>
     </x:row>
     <x:row r="841" spans="1:17">
@@ -23144,16 +23150,16 @@
         <x:v>1404001020</x:v>
       </x:c>
       <x:c r="C841" s="0" t="s">
-        <x:v>1765</x:v>
+        <x:v>1766</x:v>
       </x:c>
       <x:c r="D841" s="0" t="s">
-        <x:v>1766</x:v>
+        <x:v>1767</x:v>
       </x:c>
       <x:c r="G841" s="0" t="s">
-        <x:v>1766</x:v>
+        <x:v>1767</x:v>
       </x:c>
       <x:c r="I841" s="0" t="s">
-        <x:v>1767</x:v>
+        <x:v>1768</x:v>
       </x:c>
     </x:row>
     <x:row r="842" spans="1:17">
@@ -23164,16 +23170,16 @@
         <x:v>1404001021</x:v>
       </x:c>
       <x:c r="C842" s="0" t="s">
-        <x:v>1768</x:v>
+        <x:v>1769</x:v>
       </x:c>
       <x:c r="D842" s="0" t="s">
-        <x:v>1769</x:v>
+        <x:v>1770</x:v>
       </x:c>
       <x:c r="G842" s="0" t="s">
-        <x:v>1769</x:v>
+        <x:v>1770</x:v>
       </x:c>
       <x:c r="I842" s="0" t="s">
-        <x:v>1770</x:v>
+        <x:v>1771</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:17">
@@ -23184,31 +23190,31 @@
         <x:v>1404001022</x:v>
       </x:c>
       <x:c r="C843" s="0" t="s">
-        <x:v>1771</x:v>
+        <x:v>1772</x:v>
       </x:c>
       <x:c r="D843" s="0" t="s">
-        <x:v>1772</x:v>
+        <x:v>1773</x:v>
       </x:c>
       <x:c r="G843" s="0" t="s">
-        <x:v>1772</x:v>
+        <x:v>1773</x:v>
       </x:c>
       <x:c r="H843" s="0" t="s">
-        <x:v>1773</x:v>
+        <x:v>1774</x:v>
       </x:c>
       <x:c r="I843" s="0" t="s">
-        <x:v>1774</x:v>
+        <x:v>1775</x:v>
       </x:c>
       <x:c r="J843" s="0" t="s">
-        <x:v>1775</x:v>
+        <x:v>1776</x:v>
       </x:c>
       <x:c r="M843" s="0" t="s">
-        <x:v>1776</x:v>
+        <x:v>1777</x:v>
       </x:c>
       <x:c r="O843" s="0" t="s">
-        <x:v>1777</x:v>
+        <x:v>1778</x:v>
       </x:c>
       <x:c r="P843" s="0" t="s">
-        <x:v>1778</x:v>
+        <x:v>1779</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:17">
@@ -23219,31 +23225,31 @@
         <x:v>1404001023</x:v>
       </x:c>
       <x:c r="C844" s="0" t="s">
-        <x:v>1771</x:v>
+        <x:v>1772</x:v>
       </x:c>
       <x:c r="D844" s="0" t="s">
-        <x:v>1779</x:v>
+        <x:v>1780</x:v>
       </x:c>
       <x:c r="G844" s="0" t="s">
-        <x:v>1780</x:v>
+        <x:v>1781</x:v>
       </x:c>
       <x:c r="H844" s="0" t="s">
-        <x:v>1781</x:v>
+        <x:v>1782</x:v>
       </x:c>
       <x:c r="I844" s="0" t="s">
-        <x:v>1782</x:v>
+        <x:v>1783</x:v>
       </x:c>
       <x:c r="J844" s="0" t="s">
-        <x:v>1783</x:v>
+        <x:v>1784</x:v>
       </x:c>
       <x:c r="M844" s="0" t="s">
-        <x:v>1784</x:v>
+        <x:v>1785</x:v>
       </x:c>
       <x:c r="O844" s="0" t="s">
-        <x:v>1785</x:v>
+        <x:v>1786</x:v>
       </x:c>
       <x:c r="P844" s="0" t="s">
-        <x:v>1786</x:v>
+        <x:v>1787</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:17">
@@ -23254,31 +23260,31 @@
         <x:v>1404001024</x:v>
       </x:c>
       <x:c r="C845" s="0" t="s">
-        <x:v>1771</x:v>
+        <x:v>1772</x:v>
       </x:c>
       <x:c r="D845" s="0" t="s">
-        <x:v>1787</x:v>
+        <x:v>1788</x:v>
       </x:c>
       <x:c r="G845" s="0" t="s">
-        <x:v>1788</x:v>
+        <x:v>1789</x:v>
       </x:c>
       <x:c r="H845" s="0" t="s">
-        <x:v>1789</x:v>
+        <x:v>1790</x:v>
       </x:c>
       <x:c r="I845" s="0" t="s">
-        <x:v>1790</x:v>
+        <x:v>1791</x:v>
       </x:c>
       <x:c r="J845" s="0" t="s">
-        <x:v>1791</x:v>
+        <x:v>1792</x:v>
       </x:c>
       <x:c r="M845" s="0" t="s">
-        <x:v>1792</x:v>
+        <x:v>1793</x:v>
       </x:c>
       <x:c r="O845" s="0" t="s">
-        <x:v>1793</x:v>
+        <x:v>1794</x:v>
       </x:c>
       <x:c r="P845" s="0" t="s">
-        <x:v>1794</x:v>
+        <x:v>1795</x:v>
       </x:c>
     </x:row>
     <x:row r="846" spans="1:17">
@@ -23289,10 +23295,10 @@
         <x:v>1404001025</x:v>
       </x:c>
       <x:c r="C846" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D846" s="0" t="s">
-        <x:v>1795</x:v>
+        <x:v>1796</x:v>
       </x:c>
     </x:row>
     <x:row r="847" spans="1:17">
@@ -23306,7 +23312,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="D847" s="0" t="s">
-        <x:v>1796</x:v>
+        <x:v>1797</x:v>
       </x:c>
     </x:row>
     <x:row r="848" spans="1:17">
@@ -23320,7 +23326,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="D848" s="0" t="s">
-        <x:v>1797</x:v>
+        <x:v>1798</x:v>
       </x:c>
     </x:row>
     <x:row r="849" spans="1:17">
@@ -23334,7 +23340,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="D849" s="0" t="s">
-        <x:v>1798</x:v>
+        <x:v>1799</x:v>
       </x:c>
     </x:row>
     <x:row r="850" spans="1:17">
@@ -23348,7 +23354,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="D850" s="0" t="s">
-        <x:v>1799</x:v>
+        <x:v>1800</x:v>
       </x:c>
     </x:row>
     <x:row r="851" spans="1:17">
@@ -23362,7 +23368,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="D851" s="0" t="s">
-        <x:v>1800</x:v>
+        <x:v>1801</x:v>
       </x:c>
     </x:row>
     <x:row r="852" spans="1:17">
@@ -23376,7 +23382,7 @@
         <x:v>353</x:v>
       </x:c>
       <x:c r="D852" s="0" t="s">
-        <x:v>1801</x:v>
+        <x:v>1802</x:v>
       </x:c>
     </x:row>
     <x:row r="853" spans="1:17">
@@ -23387,16 +23393,16 @@
         <x:v>1404001045</x:v>
       </x:c>
       <x:c r="C853" s="0" t="s">
-        <x:v>1802</x:v>
+        <x:v>1803</x:v>
       </x:c>
       <x:c r="D853" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
       <x:c r="G853" s="0" t="s">
-        <x:v>1803</x:v>
+        <x:v>1804</x:v>
       </x:c>
       <x:c r="I853" s="0" t="s">
-        <x:v>1804</x:v>
+        <x:v>1805</x:v>
       </x:c>
     </x:row>
     <x:row r="854" spans="1:17">
@@ -23407,16 +23413,16 @@
         <x:v>1404001046</x:v>
       </x:c>
       <x:c r="C854" s="0" t="s">
-        <x:v>1802</x:v>
+        <x:v>1803</x:v>
       </x:c>
       <x:c r="D854" s="0" t="s">
-        <x:v>1805</x:v>
+        <x:v>1806</x:v>
       </x:c>
       <x:c r="G854" s="0" t="s">
-        <x:v>1805</x:v>
+        <x:v>1806</x:v>
       </x:c>
       <x:c r="I854" s="0" t="s">
-        <x:v>1806</x:v>
+        <x:v>1807</x:v>
       </x:c>
     </x:row>
     <x:row r="855" spans="1:17">
@@ -23427,16 +23433,16 @@
         <x:v>1404001047</x:v>
       </x:c>
       <x:c r="C855" s="0" t="s">
-        <x:v>1802</x:v>
+        <x:v>1803</x:v>
       </x:c>
       <x:c r="D855" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1808</x:v>
       </x:c>
       <x:c r="G855" s="0" t="s">
-        <x:v>1807</x:v>
+        <x:v>1808</x:v>
       </x:c>
       <x:c r="I855" s="0" t="s">
-        <x:v>1808</x:v>
+        <x:v>1809</x:v>
       </x:c>
     </x:row>
     <x:row r="856" spans="1:17">
@@ -23447,16 +23453,16 @@
         <x:v>1404001048</x:v>
       </x:c>
       <x:c r="C856" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D856" s="0" t="s">
-        <x:v>1810</x:v>
+        <x:v>1811</x:v>
       </x:c>
       <x:c r="G856" s="0" t="s">
-        <x:v>1810</x:v>
+        <x:v>1811</x:v>
       </x:c>
       <x:c r="I856" s="0" t="s">
-        <x:v>1811</x:v>
+        <x:v>1812</x:v>
       </x:c>
     </x:row>
     <x:row r="857" spans="1:17">
@@ -23467,16 +23473,16 @@
         <x:v>1404001049</x:v>
       </x:c>
       <x:c r="C857" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D857" s="0" t="s">
-        <x:v>1813</x:v>
+        <x:v>1814</x:v>
       </x:c>
       <x:c r="G857" s="0" t="s">
-        <x:v>1813</x:v>
+        <x:v>1814</x:v>
       </x:c>
       <x:c r="I857" s="0" t="s">
-        <x:v>1814</x:v>
+        <x:v>1815</x:v>
       </x:c>
     </x:row>
     <x:row r="858" spans="1:17">
@@ -23487,16 +23493,16 @@
         <x:v>1404001050</x:v>
       </x:c>
       <x:c r="C858" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D858" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1816</x:v>
       </x:c>
       <x:c r="G858" s="0" t="s">
-        <x:v>1815</x:v>
+        <x:v>1816</x:v>
       </x:c>
       <x:c r="I858" s="0" t="s">
-        <x:v>1816</x:v>
+        <x:v>1817</x:v>
       </x:c>
     </x:row>
     <x:row r="859" spans="1:17">
@@ -23507,16 +23513,16 @@
         <x:v>1404001051</x:v>
       </x:c>
       <x:c r="C859" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D859" s="0" t="s">
-        <x:v>1817</x:v>
+        <x:v>1818</x:v>
       </x:c>
       <x:c r="G859" s="0" t="s">
-        <x:v>1817</x:v>
+        <x:v>1818</x:v>
       </x:c>
       <x:c r="I859" s="0" t="s">
-        <x:v>1818</x:v>
+        <x:v>1819</x:v>
       </x:c>
     </x:row>
     <x:row r="860" spans="1:17">
@@ -23527,16 +23533,16 @@
         <x:v>1404001052</x:v>
       </x:c>
       <x:c r="C860" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D860" s="0" t="s">
-        <x:v>1819</x:v>
+        <x:v>1820</x:v>
       </x:c>
       <x:c r="G860" s="0" t="s">
-        <x:v>1819</x:v>
+        <x:v>1820</x:v>
       </x:c>
       <x:c r="I860" s="0" t="s">
-        <x:v>1820</x:v>
+        <x:v>1821</x:v>
       </x:c>
     </x:row>
     <x:row r="861" spans="1:17">
@@ -23547,16 +23553,16 @@
         <x:v>1404001053</x:v>
       </x:c>
       <x:c r="C861" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D861" s="0" t="s">
-        <x:v>1821</x:v>
+        <x:v>1822</x:v>
       </x:c>
       <x:c r="G861" s="0" t="s">
-        <x:v>1821</x:v>
+        <x:v>1822</x:v>
       </x:c>
       <x:c r="I861" s="0" t="s">
-        <x:v>1822</x:v>
+        <x:v>1823</x:v>
       </x:c>
     </x:row>
     <x:row r="862" spans="1:17">
@@ -23567,16 +23573,16 @@
         <x:v>1404001054</x:v>
       </x:c>
       <x:c r="C862" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D862" s="0" t="s">
-        <x:v>1823</x:v>
+        <x:v>1824</x:v>
       </x:c>
       <x:c r="G862" s="0" t="s">
-        <x:v>1823</x:v>
+        <x:v>1824</x:v>
       </x:c>
       <x:c r="I862" s="0" t="s">
-        <x:v>1824</x:v>
+        <x:v>1825</x:v>
       </x:c>
     </x:row>
     <x:row r="863" spans="1:17">
@@ -23587,16 +23593,16 @@
         <x:v>1404001055</x:v>
       </x:c>
       <x:c r="C863" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D863" s="0" t="s">
-        <x:v>1825</x:v>
+        <x:v>1826</x:v>
       </x:c>
       <x:c r="G863" s="0" t="s">
-        <x:v>1825</x:v>
+        <x:v>1826</x:v>
       </x:c>
       <x:c r="I863" s="0" t="s">
-        <x:v>1826</x:v>
+        <x:v>1827</x:v>
       </x:c>
     </x:row>
     <x:row r="864" spans="1:17">
@@ -23607,16 +23613,16 @@
         <x:v>1404001056</x:v>
       </x:c>
       <x:c r="C864" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D864" s="0" t="s">
-        <x:v>1827</x:v>
+        <x:v>1828</x:v>
       </x:c>
       <x:c r="G864" s="0" t="s">
-        <x:v>1827</x:v>
+        <x:v>1828</x:v>
       </x:c>
       <x:c r="I864" s="0" t="s">
-        <x:v>1828</x:v>
+        <x:v>1829</x:v>
       </x:c>
     </x:row>
     <x:row r="865" spans="1:17">
@@ -23627,16 +23633,16 @@
         <x:v>1404001057</x:v>
       </x:c>
       <x:c r="C865" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D865" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="G865" s="0" t="s">
-        <x:v>1829</x:v>
+        <x:v>1830</x:v>
       </x:c>
       <x:c r="I865" s="0" t="s">
-        <x:v>1830</x:v>
+        <x:v>1831</x:v>
       </x:c>
     </x:row>
     <x:row r="866" spans="1:17">
@@ -23647,16 +23653,16 @@
         <x:v>1404001058</x:v>
       </x:c>
       <x:c r="C866" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D866" s="0" t="s">
-        <x:v>1831</x:v>
+        <x:v>1832</x:v>
       </x:c>
       <x:c r="G866" s="0" t="s">
-        <x:v>1831</x:v>
+        <x:v>1832</x:v>
       </x:c>
       <x:c r="I866" s="0" t="s">
-        <x:v>1832</x:v>
+        <x:v>1833</x:v>
       </x:c>
     </x:row>
     <x:row r="867" spans="1:17">
@@ -23667,16 +23673,16 @@
         <x:v>1404001059</x:v>
       </x:c>
       <x:c r="C867" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D867" s="0" t="s">
-        <x:v>1833</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="G867" s="0" t="s">
-        <x:v>1833</x:v>
+        <x:v>1834</x:v>
       </x:c>
       <x:c r="I867" s="0" t="s">
-        <x:v>1834</x:v>
+        <x:v>1835</x:v>
       </x:c>
     </x:row>
     <x:row r="868" spans="1:17">
@@ -23687,16 +23693,16 @@
         <x:v>1404001060</x:v>
       </x:c>
       <x:c r="C868" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D868" s="0" t="s">
-        <x:v>1835</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="G868" s="0" t="s">
-        <x:v>1835</x:v>
+        <x:v>1836</x:v>
       </x:c>
       <x:c r="I868" s="0" t="s">
-        <x:v>1836</x:v>
+        <x:v>1837</x:v>
       </x:c>
     </x:row>
     <x:row r="869" spans="1:17">
@@ -23707,16 +23713,16 @@
         <x:v>1404001061</x:v>
       </x:c>
       <x:c r="C869" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D869" s="0" t="s">
-        <x:v>1837</x:v>
+        <x:v>1838</x:v>
       </x:c>
       <x:c r="G869" s="0" t="s">
-        <x:v>1837</x:v>
+        <x:v>1838</x:v>
       </x:c>
       <x:c r="I869" s="0" t="s">
-        <x:v>1838</x:v>
+        <x:v>1839</x:v>
       </x:c>
     </x:row>
     <x:row r="870" spans="1:17">
@@ -23727,16 +23733,16 @@
         <x:v>1404001062</x:v>
       </x:c>
       <x:c r="C870" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D870" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1840</x:v>
       </x:c>
       <x:c r="G870" s="0" t="s">
-        <x:v>1839</x:v>
+        <x:v>1840</x:v>
       </x:c>
       <x:c r="I870" s="0" t="s">
-        <x:v>1840</x:v>
+        <x:v>1841</x:v>
       </x:c>
     </x:row>
     <x:row r="871" spans="1:17">
@@ -23747,16 +23753,16 @@
         <x:v>1404001063</x:v>
       </x:c>
       <x:c r="C871" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D871" s="0" t="s">
-        <x:v>1841</x:v>
+        <x:v>1842</x:v>
       </x:c>
       <x:c r="G871" s="0" t="s">
-        <x:v>1841</x:v>
+        <x:v>1842</x:v>
       </x:c>
       <x:c r="I871" s="0" t="s">
-        <x:v>1842</x:v>
+        <x:v>1843</x:v>
       </x:c>
     </x:row>
     <x:row r="872" spans="1:17">
@@ -23767,16 +23773,16 @@
         <x:v>1404001064</x:v>
       </x:c>
       <x:c r="C872" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D872" s="0" t="s">
-        <x:v>1843</x:v>
+        <x:v>1844</x:v>
       </x:c>
       <x:c r="G872" s="0" t="s">
-        <x:v>1843</x:v>
+        <x:v>1844</x:v>
       </x:c>
       <x:c r="I872" s="0" t="s">
-        <x:v>1844</x:v>
+        <x:v>1845</x:v>
       </x:c>
     </x:row>
     <x:row r="873" spans="1:17">
@@ -23787,16 +23793,16 @@
         <x:v>1404001065</x:v>
       </x:c>
       <x:c r="C873" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D873" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="G873" s="0" t="s">
-        <x:v>1845</x:v>
+        <x:v>1846</x:v>
       </x:c>
       <x:c r="I873" s="0" t="s">
-        <x:v>1846</x:v>
+        <x:v>1847</x:v>
       </x:c>
     </x:row>
     <x:row r="874" spans="1:17">
@@ -23807,16 +23813,16 @@
         <x:v>1404001066</x:v>
       </x:c>
       <x:c r="C874" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D874" s="0" t="s">
-        <x:v>1847</x:v>
+        <x:v>1848</x:v>
       </x:c>
       <x:c r="G874" s="0" t="s">
-        <x:v>1847</x:v>
+        <x:v>1848</x:v>
       </x:c>
       <x:c r="I874" s="0" t="s">
-        <x:v>1848</x:v>
+        <x:v>1849</x:v>
       </x:c>
     </x:row>
     <x:row r="875" spans="1:17">
@@ -23827,16 +23833,16 @@
         <x:v>1404001067</x:v>
       </x:c>
       <x:c r="C875" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D875" s="0" t="s">
-        <x:v>1849</x:v>
+        <x:v>1850</x:v>
       </x:c>
       <x:c r="G875" s="0" t="s">
-        <x:v>1849</x:v>
+        <x:v>1850</x:v>
       </x:c>
       <x:c r="I875" s="0" t="s">
-        <x:v>1850</x:v>
+        <x:v>1851</x:v>
       </x:c>
     </x:row>
     <x:row r="876" spans="1:17">
@@ -23847,16 +23853,16 @@
         <x:v>1404001068</x:v>
       </x:c>
       <x:c r="C876" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D876" s="0" t="s">
-        <x:v>1851</x:v>
+        <x:v>1852</x:v>
       </x:c>
       <x:c r="G876" s="0" t="s">
-        <x:v>1851</x:v>
+        <x:v>1852</x:v>
       </x:c>
       <x:c r="I876" s="0" t="s">
-        <x:v>1852</x:v>
+        <x:v>1853</x:v>
       </x:c>
     </x:row>
     <x:row r="877" spans="1:17">
@@ -23867,16 +23873,16 @@
         <x:v>1404001069</x:v>
       </x:c>
       <x:c r="C877" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D877" s="0" t="s">
-        <x:v>1853</x:v>
+        <x:v>1854</x:v>
       </x:c>
       <x:c r="G877" s="0" t="s">
-        <x:v>1853</x:v>
+        <x:v>1854</x:v>
       </x:c>
       <x:c r="I877" s="0" t="s">
-        <x:v>1854</x:v>
+        <x:v>1855</x:v>
       </x:c>
     </x:row>
     <x:row r="878" spans="1:17">
@@ -23887,16 +23893,16 @@
         <x:v>1404001070</x:v>
       </x:c>
       <x:c r="C878" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D878" s="0" t="s">
-        <x:v>1855</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="G878" s="0" t="s">
-        <x:v>1855</x:v>
+        <x:v>1856</x:v>
       </x:c>
       <x:c r="I878" s="0" t="s">
-        <x:v>1856</x:v>
+        <x:v>1857</x:v>
       </x:c>
     </x:row>
     <x:row r="879" spans="1:17">
@@ -23907,16 +23913,16 @@
         <x:v>1404001071</x:v>
       </x:c>
       <x:c r="C879" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D879" s="0" t="s">
-        <x:v>1857</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="G879" s="0" t="s">
-        <x:v>1857</x:v>
+        <x:v>1858</x:v>
       </x:c>
       <x:c r="I879" s="0" t="s">
-        <x:v>1858</x:v>
+        <x:v>1859</x:v>
       </x:c>
     </x:row>
     <x:row r="880" spans="1:17">
@@ -23927,16 +23933,16 @@
         <x:v>1404001072</x:v>
       </x:c>
       <x:c r="C880" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D880" s="0" t="s">
-        <x:v>1859</x:v>
+        <x:v>1860</x:v>
       </x:c>
       <x:c r="G880" s="0" t="s">
-        <x:v>1859</x:v>
+        <x:v>1860</x:v>
       </x:c>
       <x:c r="I880" s="0" t="s">
-        <x:v>1860</x:v>
+        <x:v>1861</x:v>
       </x:c>
     </x:row>
     <x:row r="881" spans="1:17">
@@ -23947,16 +23953,16 @@
         <x:v>1404001073</x:v>
       </x:c>
       <x:c r="C881" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D881" s="0" t="s">
-        <x:v>1861</x:v>
+        <x:v>1862</x:v>
       </x:c>
       <x:c r="G881" s="0" t="s">
-        <x:v>1861</x:v>
+        <x:v>1862</x:v>
       </x:c>
       <x:c r="I881" s="0" t="s">
-        <x:v>1862</x:v>
+        <x:v>1863</x:v>
       </x:c>
     </x:row>
     <x:row r="882" spans="1:17">
@@ -23967,16 +23973,16 @@
         <x:v>1404001074</x:v>
       </x:c>
       <x:c r="C882" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D882" s="0" t="s">
-        <x:v>1863</x:v>
+        <x:v>1864</x:v>
       </x:c>
       <x:c r="G882" s="0" t="s">
-        <x:v>1863</x:v>
+        <x:v>1864</x:v>
       </x:c>
       <x:c r="I882" s="0" t="s">
-        <x:v>1864</x:v>
+        <x:v>1865</x:v>
       </x:c>
     </x:row>
     <x:row r="883" spans="1:17">
@@ -23987,16 +23993,16 @@
         <x:v>1404001075</x:v>
       </x:c>
       <x:c r="C883" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D883" s="0" t="s">
-        <x:v>1865</x:v>
+        <x:v>1866</x:v>
       </x:c>
       <x:c r="G883" s="0" t="s">
-        <x:v>1865</x:v>
+        <x:v>1866</x:v>
       </x:c>
       <x:c r="I883" s="0" t="s">
-        <x:v>1866</x:v>
+        <x:v>1867</x:v>
       </x:c>
     </x:row>
     <x:row r="884" spans="1:17">
@@ -24007,16 +24013,16 @@
         <x:v>1404001076</x:v>
       </x:c>
       <x:c r="C884" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D884" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1868</x:v>
       </x:c>
       <x:c r="G884" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1868</x:v>
       </x:c>
       <x:c r="I884" s="0" t="s">
-        <x:v>1868</x:v>
+        <x:v>1869</x:v>
       </x:c>
     </x:row>
     <x:row r="885" spans="1:17">
@@ -24027,16 +24033,16 @@
         <x:v>1404001077</x:v>
       </x:c>
       <x:c r="C885" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D885" s="0" t="s">
-        <x:v>1869</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="G885" s="0" t="s">
-        <x:v>1869</x:v>
+        <x:v>1870</x:v>
       </x:c>
       <x:c r="I885" s="0" t="s">
-        <x:v>1870</x:v>
+        <x:v>1871</x:v>
       </x:c>
     </x:row>
     <x:row r="886" spans="1:17">
@@ -24047,16 +24053,16 @@
         <x:v>1404001078</x:v>
       </x:c>
       <x:c r="C886" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D886" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1868</x:v>
       </x:c>
       <x:c r="G886" s="0" t="s">
-        <x:v>1867</x:v>
+        <x:v>1868</x:v>
       </x:c>
       <x:c r="I886" s="0" t="s">
-        <x:v>1871</x:v>
+        <x:v>1872</x:v>
       </x:c>
     </x:row>
     <x:row r="887" spans="1:17">
@@ -24067,16 +24073,16 @@
         <x:v>1404001079</x:v>
       </x:c>
       <x:c r="C887" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D887" s="0" t="s">
-        <x:v>1872</x:v>
+        <x:v>1873</x:v>
       </x:c>
       <x:c r="G887" s="0" t="s">
-        <x:v>1872</x:v>
+        <x:v>1873</x:v>
       </x:c>
       <x:c r="I887" s="0" t="s">
-        <x:v>1873</x:v>
+        <x:v>1874</x:v>
       </x:c>
     </x:row>
     <x:row r="888" spans="1:17">
@@ -24087,16 +24093,16 @@
         <x:v>1404001080</x:v>
       </x:c>
       <x:c r="C888" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D888" s="0" t="s">
-        <x:v>1874</x:v>
+        <x:v>1875</x:v>
       </x:c>
       <x:c r="G888" s="0" t="s">
-        <x:v>1874</x:v>
+        <x:v>1875</x:v>
       </x:c>
       <x:c r="I888" s="0" t="s">
-        <x:v>1875</x:v>
+        <x:v>1876</x:v>
       </x:c>
     </x:row>
     <x:row r="889" spans="1:17">
@@ -24107,16 +24113,16 @@
         <x:v>1404001081</x:v>
       </x:c>
       <x:c r="C889" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D889" s="0" t="s">
-        <x:v>1876</x:v>
+        <x:v>1877</x:v>
       </x:c>
       <x:c r="G889" s="0" t="s">
-        <x:v>1876</x:v>
+        <x:v>1877</x:v>
       </x:c>
       <x:c r="I889" s="0" t="s">
-        <x:v>1877</x:v>
+        <x:v>1878</x:v>
       </x:c>
     </x:row>
     <x:row r="890" spans="1:17">
@@ -24127,16 +24133,16 @@
         <x:v>1404001082</x:v>
       </x:c>
       <x:c r="C890" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D890" s="0" t="s">
-        <x:v>1878</x:v>
+        <x:v>1879</x:v>
       </x:c>
       <x:c r="G890" s="0" t="s">
-        <x:v>1878</x:v>
+        <x:v>1879</x:v>
       </x:c>
       <x:c r="I890" s="0" t="s">
-        <x:v>1879</x:v>
+        <x:v>1880</x:v>
       </x:c>
     </x:row>
     <x:row r="891" spans="1:17">
@@ -24147,16 +24153,16 @@
         <x:v>1404001083</x:v>
       </x:c>
       <x:c r="C891" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D891" s="0" t="s">
-        <x:v>1880</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="G891" s="0" t="s">
-        <x:v>1880</x:v>
+        <x:v>1881</x:v>
       </x:c>
       <x:c r="I891" s="0" t="s">
-        <x:v>1881</x:v>
+        <x:v>1882</x:v>
       </x:c>
     </x:row>
     <x:row r="892" spans="1:17">
@@ -24167,16 +24173,16 @@
         <x:v>1404001084</x:v>
       </x:c>
       <x:c r="C892" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D892" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="G892" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="I892" s="0" t="s">
-        <x:v>1883</x:v>
+        <x:v>1884</x:v>
       </x:c>
     </x:row>
     <x:row r="893" spans="1:17">
@@ -24187,16 +24193,16 @@
         <x:v>1404001085</x:v>
       </x:c>
       <x:c r="C893" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D893" s="0" t="s">
-        <x:v>1884</x:v>
+        <x:v>1885</x:v>
       </x:c>
       <x:c r="G893" s="0" t="s">
-        <x:v>1884</x:v>
+        <x:v>1885</x:v>
       </x:c>
       <x:c r="I893" s="0" t="s">
-        <x:v>1885</x:v>
+        <x:v>1886</x:v>
       </x:c>
     </x:row>
     <x:row r="894" spans="1:17">
@@ -24207,16 +24213,16 @@
         <x:v>1404001086</x:v>
       </x:c>
       <x:c r="C894" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D894" s="0" t="s">
-        <x:v>1886</x:v>
+        <x:v>1887</x:v>
       </x:c>
       <x:c r="G894" s="0" t="s">
-        <x:v>1886</x:v>
+        <x:v>1887</x:v>
       </x:c>
       <x:c r="I894" s="0" t="s">
-        <x:v>1887</x:v>
+        <x:v>1888</x:v>
       </x:c>
     </x:row>
     <x:row r="895" spans="1:17">
@@ -24227,16 +24233,16 @@
         <x:v>1404001087</x:v>
       </x:c>
       <x:c r="C895" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D895" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="G895" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="I895" s="0" t="s">
-        <x:v>1883</x:v>
+        <x:v>1884</x:v>
       </x:c>
     </x:row>
     <x:row r="896" spans="1:17">
@@ -24247,16 +24253,16 @@
         <x:v>1404001088</x:v>
       </x:c>
       <x:c r="C896" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D896" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1889</x:v>
       </x:c>
       <x:c r="G896" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1889</x:v>
       </x:c>
       <x:c r="I896" s="0" t="s">
-        <x:v>1889</x:v>
+        <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="897" spans="1:17">
@@ -24267,16 +24273,16 @@
         <x:v>1404001089</x:v>
       </x:c>
       <x:c r="C897" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D897" s="0" t="s">
-        <x:v>1890</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="G897" s="0" t="s">
-        <x:v>1890</x:v>
+        <x:v>1891</x:v>
       </x:c>
       <x:c r="I897" s="0" t="s">
-        <x:v>1891</x:v>
+        <x:v>1892</x:v>
       </x:c>
     </x:row>
     <x:row r="898" spans="1:17">
@@ -24287,16 +24293,16 @@
         <x:v>1404001090</x:v>
       </x:c>
       <x:c r="C898" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D898" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="G898" s="0" t="s">
-        <x:v>1882</x:v>
+        <x:v>1883</x:v>
       </x:c>
       <x:c r="I898" s="0" t="s">
-        <x:v>1883</x:v>
+        <x:v>1884</x:v>
       </x:c>
     </x:row>
     <x:row r="899" spans="1:17">
@@ -24307,16 +24313,16 @@
         <x:v>1404001091</x:v>
       </x:c>
       <x:c r="C899" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D899" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1889</x:v>
       </x:c>
       <x:c r="G899" s="0" t="s">
-        <x:v>1888</x:v>
+        <x:v>1889</x:v>
       </x:c>
       <x:c r="I899" s="0" t="s">
-        <x:v>1889</x:v>
+        <x:v>1890</x:v>
       </x:c>
     </x:row>
     <x:row r="900" spans="1:17">
@@ -24327,16 +24333,16 @@
         <x:v>1404001092</x:v>
       </x:c>
       <x:c r="C900" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D900" s="0" t="s">
-        <x:v>1892</x:v>
+        <x:v>1893</x:v>
       </x:c>
       <x:c r="G900" s="0" t="s">
-        <x:v>1892</x:v>
+        <x:v>1893</x:v>
       </x:c>
       <x:c r="I900" s="0" t="s">
-        <x:v>1893</x:v>
+        <x:v>1894</x:v>
       </x:c>
     </x:row>
     <x:row r="901" spans="1:17">
@@ -24347,16 +24353,16 @@
         <x:v>1404001093</x:v>
       </x:c>
       <x:c r="C901" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D901" s="0" t="s">
-        <x:v>1894</x:v>
+        <x:v>1895</x:v>
       </x:c>
       <x:c r="G901" s="0" t="s">
-        <x:v>1894</x:v>
+        <x:v>1895</x:v>
       </x:c>
       <x:c r="I901" s="0" t="s">
-        <x:v>1895</x:v>
+        <x:v>1896</x:v>
       </x:c>
     </x:row>
     <x:row r="902" spans="1:17">
@@ -24367,16 +24373,16 @@
         <x:v>1404001094</x:v>
       </x:c>
       <x:c r="C902" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D902" s="0" t="s">
-        <x:v>1896</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="G902" s="0" t="s">
-        <x:v>1896</x:v>
+        <x:v>1897</x:v>
       </x:c>
       <x:c r="I902" s="0" t="s">
-        <x:v>1897</x:v>
+        <x:v>1898</x:v>
       </x:c>
     </x:row>
     <x:row r="903" spans="1:17">
@@ -24387,16 +24393,16 @@
         <x:v>1404001095</x:v>
       </x:c>
       <x:c r="C903" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D903" s="0" t="s">
-        <x:v>1898</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="G903" s="0" t="s">
-        <x:v>1898</x:v>
+        <x:v>1899</x:v>
       </x:c>
       <x:c r="I903" s="0" t="s">
-        <x:v>1899</x:v>
+        <x:v>1900</x:v>
       </x:c>
     </x:row>
     <x:row r="904" spans="1:17">
@@ -24407,16 +24413,16 @@
         <x:v>1404001096</x:v>
       </x:c>
       <x:c r="C904" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D904" s="0" t="s">
-        <x:v>1900</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="G904" s="0" t="s">
-        <x:v>1900</x:v>
+        <x:v>1901</x:v>
       </x:c>
       <x:c r="I904" s="0" t="s">
-        <x:v>1901</x:v>
+        <x:v>1902</x:v>
       </x:c>
     </x:row>
     <x:row r="905" spans="1:17">
@@ -24427,16 +24433,16 @@
         <x:v>1404001097</x:v>
       </x:c>
       <x:c r="C905" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D905" s="0" t="s">
-        <x:v>1902</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="G905" s="0" t="s">
-        <x:v>1902</x:v>
+        <x:v>1903</x:v>
       </x:c>
       <x:c r="I905" s="0" t="s">
-        <x:v>1903</x:v>
+        <x:v>1904</x:v>
       </x:c>
     </x:row>
     <x:row r="906" spans="1:17">
@@ -24447,16 +24453,16 @@
         <x:v>1404001098</x:v>
       </x:c>
       <x:c r="C906" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D906" s="0" t="s">
-        <x:v>1904</x:v>
+        <x:v>1905</x:v>
       </x:c>
       <x:c r="G906" s="0" t="s">
-        <x:v>1904</x:v>
+        <x:v>1905</x:v>
       </x:c>
       <x:c r="I906" s="0" t="s">
-        <x:v>1905</x:v>
+        <x:v>1906</x:v>
       </x:c>
     </x:row>
     <x:row r="907" spans="1:17">
@@ -24467,16 +24473,16 @@
         <x:v>1404001099</x:v>
       </x:c>
       <x:c r="C907" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D907" s="0" t="s">
-        <x:v>1906</x:v>
+        <x:v>1907</x:v>
       </x:c>
       <x:c r="G907" s="0" t="s">
-        <x:v>1906</x:v>
+        <x:v>1907</x:v>
       </x:c>
       <x:c r="I907" s="0" t="s">
-        <x:v>1907</x:v>
+        <x:v>1908</x:v>
       </x:c>
     </x:row>
     <x:row r="908" spans="1:17">
@@ -24487,16 +24493,16 @@
         <x:v>1404001100</x:v>
       </x:c>
       <x:c r="C908" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D908" s="0" t="s">
-        <x:v>1908</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="G908" s="0" t="s">
-        <x:v>1908</x:v>
+        <x:v>1909</x:v>
       </x:c>
       <x:c r="I908" s="0" t="s">
-        <x:v>1909</x:v>
+        <x:v>1910</x:v>
       </x:c>
     </x:row>
     <x:row r="909" spans="1:17">
@@ -24507,16 +24513,16 @@
         <x:v>1404001101</x:v>
       </x:c>
       <x:c r="C909" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D909" s="0" t="s">
-        <x:v>1910</x:v>
+        <x:v>1911</x:v>
       </x:c>
       <x:c r="G909" s="0" t="s">
-        <x:v>1910</x:v>
+        <x:v>1911</x:v>
       </x:c>
       <x:c r="I909" s="0" t="s">
-        <x:v>1911</x:v>
+        <x:v>1912</x:v>
       </x:c>
     </x:row>
     <x:row r="910" spans="1:17">
@@ -24527,16 +24533,16 @@
         <x:v>1404001102</x:v>
       </x:c>
       <x:c r="C910" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D910" s="0" t="s">
-        <x:v>1912</x:v>
+        <x:v>1913</x:v>
       </x:c>
       <x:c r="G910" s="0" t="s">
-        <x:v>1912</x:v>
+        <x:v>1913</x:v>
       </x:c>
       <x:c r="I910" s="0" t="s">
-        <x:v>1913</x:v>
+        <x:v>1914</x:v>
       </x:c>
     </x:row>
     <x:row r="911" spans="1:17">
@@ -24547,16 +24553,16 @@
         <x:v>1404001103</x:v>
       </x:c>
       <x:c r="C911" s="0" t="s">
-        <x:v>1809</x:v>
+        <x:v>1810</x:v>
       </x:c>
       <x:c r="D911" s="0" t="s">
-        <x:v>1914</x:v>
+        <x:v>1915</x:v>
       </x:c>
       <x:c r="G911" s="0" t="s">
-        <x:v>1914</x:v>
+        <x:v>1915</x:v>
       </x:c>
       <x:c r="I911" s="0" t="s">
-        <x:v>1915</x:v>
+        <x:v>1916</x:v>
       </x:c>
     </x:row>
     <x:row r="912" spans="1:17">
@@ -24567,16 +24573,16 @@
         <x:v>1404001104</x:v>
       </x:c>
       <x:c r="C912" s="0" t="s">
-        <x:v>1812</x:v>
+        <x:v>1813</x:v>
       </x:c>
       <x:c r="D912" s="0" t="s">
-        <x:v>1916</x:v>
+        <x:v>1917</x:v>
       </x:c>
       <x:c r="G912" s="0" t="s">
-        <x:v>1916</x:v>
+        <x:v>1917</x:v>
       </x:c>
       <x:c r="I912" s="0" t="s">
-        <x:v>1917</x:v>
+        <x:v>1918</x:v>
       </x:c>
     </x:row>
     <x:row r="913" spans="1:17">
@@ -24601,10 +24607,10 @@
         <x:v>1404001110</x:v>
       </x:c>
       <x:c r="C914" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D914" s="0" t="s">
-        <x:v>1918</x:v>
+        <x:v>1919</x:v>
       </x:c>
     </x:row>
     <x:row r="915" spans="1:17">
@@ -24615,10 +24621,10 @@
         <x:v>1404001111</x:v>
       </x:c>
       <x:c r="C915" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D915" s="0" t="s">
-        <x:v>1919</x:v>
+        <x:v>1920</x:v>
       </x:c>
     </x:row>
     <x:row r="916" spans="1:17">
@@ -24629,10 +24635,10 @@
         <x:v>1404001112</x:v>
       </x:c>
       <x:c r="C916" s="0" t="s">
-        <x:v>1392</x:v>
+        <x:v>1393</x:v>
       </x:c>
       <x:c r="D916" s="0" t="s">
-        <x:v>1920</x:v>
+        <x:v>1921</x:v>
       </x:c>
     </x:row>
     <x:row r="917" spans="1:17">
@@ -24643,16 +24649,16 @@
         <x:v>1404001115</x:v>
       </x:c>
       <x:c r="C917" s="0" t="s">
-        <x:v>1921</x:v>
+        <x:v>1922</x:v>
       </x:c>
       <x:c r="D917" s="0" t="s">
-        <x:v>1922</x:v>
+        <x:v>1923</x:v>
       </x:c>
       <x:c r="G917" s="0" t="s">
-        <x:v>1922</x:v>
+        <x:v>1923</x:v>
       </x:c>
       <x:c r="I917" s="0" t="s">
-        <x:v>1923</x:v>
+        <x:v>1924</x:v>
       </x:c>
     </x:row>
     <x:row r="918" spans="1:17">
@@ -24666,13 +24672,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="D918" s="0" t="s">
-        <x:v>1921</x:v>
+        <x:v>1922</x:v>
       </x:c>
       <x:c r="G918" s="0" t="s">
-        <x:v>1922</x:v>
+        <x:v>1923</x:v>
       </x:c>
       <x:c r="I918" s="0" t="s">
-        <x:v>1923</x:v>
+        <x:v>1924</x:v>
       </x:c>
     </x:row>
     <x:row r="919" spans="1:17">
@@ -24683,16 +24689,16 @@
         <x:v>1404001117</x:v>
       </x:c>
       <x:c r="C919" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="D919" s="0" t="s">
-        <x:v>1925</x:v>
+        <x:v>1926</x:v>
       </x:c>
       <x:c r="G919" s="0" t="s">
-        <x:v>1925</x:v>
+        <x:v>1926</x:v>
       </x:c>
       <x:c r="I919" s="0" t="s">
-        <x:v>1926</x:v>
+        <x:v>1927</x:v>
       </x:c>
     </x:row>
     <x:row r="920" spans="1:17">
@@ -24706,13 +24712,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D920" s="0" t="s">
-        <x:v>1927</x:v>
+        <x:v>1928</x:v>
       </x:c>
       <x:c r="G920" s="0" t="s">
-        <x:v>1927</x:v>
+        <x:v>1928</x:v>
       </x:c>
       <x:c r="I920" s="0" t="s">
-        <x:v>1928</x:v>
+        <x:v>1929</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:17">
@@ -24723,16 +24729,16 @@
         <x:v>1404001120</x:v>
       </x:c>
       <x:c r="C921" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="D921" s="0" t="s">
-        <x:v>1929</x:v>
+        <x:v>1930</x:v>
       </x:c>
       <x:c r="G921" s="0" t="s">
-        <x:v>1929</x:v>
+        <x:v>1930</x:v>
       </x:c>
       <x:c r="I921" s="0" t="s">
-        <x:v>1930</x:v>
+        <x:v>1931</x:v>
       </x:c>
     </x:row>
     <x:row r="922" spans="1:17">
@@ -24746,13 +24752,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D922" s="0" t="s">
-        <x:v>1931</x:v>
+        <x:v>1932</x:v>
       </x:c>
       <x:c r="G922" s="0" t="s">
-        <x:v>1931</x:v>
+        <x:v>1932</x:v>
       </x:c>
       <x:c r="I922" s="0" t="s">
-        <x:v>1932</x:v>
+        <x:v>1933</x:v>
       </x:c>
     </x:row>
     <x:row r="923" spans="1:17">
@@ -24763,16 +24769,16 @@
         <x:v>1404001123</x:v>
       </x:c>
       <x:c r="C923" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="D923" s="0" t="s">
-        <x:v>1933</x:v>
+        <x:v>1934</x:v>
       </x:c>
       <x:c r="G923" s="0" t="s">
-        <x:v>1933</x:v>
+        <x:v>1934</x:v>
       </x:c>
       <x:c r="I923" s="0" t="s">
-        <x:v>1934</x:v>
+        <x:v>1935</x:v>
       </x:c>
     </x:row>
     <x:row r="924" spans="1:17">
@@ -24786,13 +24792,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D924" s="0" t="s">
-        <x:v>1935</x:v>
+        <x:v>1936</x:v>
       </x:c>
       <x:c r="G924" s="0" t="s">
-        <x:v>1935</x:v>
+        <x:v>1936</x:v>
       </x:c>
       <x:c r="I924" s="0" t="s">
-        <x:v>1936</x:v>
+        <x:v>1937</x:v>
       </x:c>
     </x:row>
     <x:row r="925" spans="1:17">
@@ -24803,16 +24809,16 @@
         <x:v>1404001126</x:v>
       </x:c>
       <x:c r="C925" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="D925" s="0" t="s">
-        <x:v>1937</x:v>
+        <x:v>1938</x:v>
       </x:c>
       <x:c r="G925" s="0" t="s">
-        <x:v>1937</x:v>
+        <x:v>1938</x:v>
       </x:c>
       <x:c r="I925" s="0" t="s">
-        <x:v>1938</x:v>
+        <x:v>1939</x:v>
       </x:c>
     </x:row>
     <x:row r="926" spans="1:17">
@@ -24826,13 +24832,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D926" s="0" t="s">
-        <x:v>1939</x:v>
+        <x:v>1940</x:v>
       </x:c>
       <x:c r="G926" s="0" t="s">
-        <x:v>1939</x:v>
+        <x:v>1940</x:v>
       </x:c>
       <x:c r="I926" s="0" t="s">
-        <x:v>1940</x:v>
+        <x:v>1941</x:v>
       </x:c>
     </x:row>
     <x:row r="927" spans="1:17">
@@ -24843,16 +24849,16 @@
         <x:v>1404001129</x:v>
       </x:c>
       <x:c r="C927" s="0" t="s">
-        <x:v>1924</x:v>
+        <x:v>1925</x:v>
       </x:c>
       <x:c r="D927" s="0" t="s">
-        <x:v>1941</x:v>
+        <x:v>1942</x:v>
       </x:c>
       <x:c r="G927" s="0" t="s">
-        <x:v>1941</x:v>
+        <x:v>1942</x:v>
       </x:c>
       <x:c r="I927" s="0" t="s">
-        <x:v>1942</x:v>
+        <x:v>1943</x:v>
       </x:c>
     </x:row>
     <x:row r="928" spans="1:17">
@@ -24866,13 +24872,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D928" s="0" t="s">
-        <x:v>1943</x:v>
+        <x:v>1944</x:v>
       </x:c>
       <x:c r="G928" s="0" t="s">
-        <x:v>1943</x:v>
+        <x:v>1944</x:v>
       </x:c>
       <x:c r="I928" s="0" t="s">
-        <x:v>1944</x:v>
+        <x:v>1945</x:v>
       </x:c>
     </x:row>
     <x:row r="929" spans="1:17">
@@ -24886,13 +24892,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D929" s="0" t="s">
-        <x:v>1945</x:v>
+        <x:v>1946</x:v>
       </x:c>
       <x:c r="G929" s="0" t="s">
-        <x:v>1945</x:v>
+        <x:v>1946</x:v>
       </x:c>
       <x:c r="I929" s="0" t="s">
-        <x:v>1946</x:v>
+        <x:v>1947</x:v>
       </x:c>
     </x:row>
     <x:row r="930" spans="1:17">
@@ -24906,13 +24912,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D930" s="0" t="s">
-        <x:v>1947</x:v>
+        <x:v>1948</x:v>
       </x:c>
       <x:c r="G930" s="0" t="s">
-        <x:v>1947</x:v>
+        <x:v>1948</x:v>
       </x:c>
       <x:c r="I930" s="0" t="s">
-        <x:v>1948</x:v>
+        <x:v>1949</x:v>
       </x:c>
     </x:row>
     <x:row r="931" spans="1:17">
@@ -24926,13 +24932,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D931" s="0" t="s">
-        <x:v>1949</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="G931" s="0" t="s">
-        <x:v>1949</x:v>
+        <x:v>1950</x:v>
       </x:c>
       <x:c r="I931" s="0" t="s">
-        <x:v>1950</x:v>
+        <x:v>1951</x:v>
       </x:c>
     </x:row>
     <x:row r="932" spans="1:17">
@@ -24946,13 +24952,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D932" s="0" t="s">
-        <x:v>1951</x:v>
+        <x:v>1952</x:v>
       </x:c>
       <x:c r="G932" s="0" t="s">
-        <x:v>1951</x:v>
+        <x:v>1952</x:v>
       </x:c>
       <x:c r="I932" s="0" t="s">
-        <x:v>1952</x:v>
+        <x:v>1953</x:v>
       </x:c>
     </x:row>
     <x:row r="933" spans="1:17">
@@ -24966,7 +24972,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="D933" s="0" t="s">
-        <x:v>1953</x:v>
+        <x:v>1954</x:v>
       </x:c>
     </x:row>
     <x:row r="934" spans="1:17">
@@ -24980,7 +24986,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D934" s="0" t="s">
-        <x:v>1954</x:v>
+        <x:v>1955</x:v>
       </x:c>
     </x:row>
     <x:row r="935" spans="1:17">
@@ -24994,7 +25000,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D935" s="0" t="s">
-        <x:v>1955</x:v>
+        <x:v>1956</x:v>
       </x:c>
     </x:row>
     <x:row r="936" spans="1:17">
@@ -25008,7 +25014,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D936" s="0" t="s">
-        <x:v>1956</x:v>
+        <x:v>1957</x:v>
       </x:c>
     </x:row>
     <x:row r="937" spans="1:17">
@@ -25022,7 +25028,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D937" s="0" t="s">
-        <x:v>1957</x:v>
+        <x:v>1958</x:v>
       </x:c>
     </x:row>
     <x:row r="938" spans="1:17">
@@ -25036,7 +25042,7 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="D938" s="0" t="s">
-        <x:v>1958</x:v>
+        <x:v>1959</x:v>
       </x:c>
     </x:row>
     <x:row r="939" spans="1:17">
@@ -25047,10 +25053,10 @@
         <x:v>1404001152</x:v>
       </x:c>
       <x:c r="C939" s="0" t="s">
-        <x:v>1436</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="D939" s="0" t="s">
-        <x:v>1959</x:v>
+        <x:v>1960</x:v>
       </x:c>
     </x:row>
     <x:row r="940" spans="1:17">
@@ -25061,10 +25067,10 @@
         <x:v>1404001153</x:v>
       </x:c>
       <x:c r="C940" s="0" t="s">
-        <x:v>1436</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="D940" s="0" t="s">
-        <x:v>1960</x:v>
+        <x:v>1961</x:v>
       </x:c>
     </x:row>
     <x:row r="941" spans="1:17">
@@ -25075,10 +25081,10 @@
         <x:v>1404001154</x:v>
       </x:c>
       <x:c r="C941" s="0" t="s">
-        <x:v>1436</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="D941" s="0" t="s">
-        <x:v>1961</x:v>
+        <x:v>1962</x:v>
       </x:c>
     </x:row>
     <x:row r="942" spans="1:17">
@@ -25089,10 +25095,10 @@
         <x:v>1404001155</x:v>
       </x:c>
       <x:c r="C942" s="0" t="s">
-        <x:v>1436</x:v>
+        <x:v>1437</x:v>
       </x:c>
       <x:c r="D942" s="0" t="s">
-        <x:v>1962</x:v>
+        <x:v>1963</x:v>
       </x:c>
     </x:row>
     <x:row r="943" spans="1:17">
@@ -25103,10 +25109,10 @@
         <x:v>1404001156</x:v>
       </x:c>
       <x:c r="C943" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D943" s="0" t="s">
-        <x:v>1963</x:v>
+        <x:v>1964</x:v>
       </x:c>
     </x:row>
     <x:row r="944" spans="1:17">
@@ -25117,10 +25123,10 @@
         <x:v>1404001157</x:v>
       </x:c>
       <x:c r="C944" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D944" s="0" t="s">
-        <x:v>1964</x:v>
+        <x:v>1965</x:v>
       </x:c>
     </x:row>
     <x:row r="945" spans="1:17">
@@ -25131,10 +25137,10 @@
         <x:v>1404001158</x:v>
       </x:c>
       <x:c r="C945" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D945" s="0" t="s">
-        <x:v>1965</x:v>
+        <x:v>1966</x:v>
       </x:c>
     </x:row>
     <x:row r="946" spans="1:17">
@@ -25145,10 +25151,10 @@
         <x:v>1404001159</x:v>
       </x:c>
       <x:c r="C946" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D946" s="0" t="s">
-        <x:v>1966</x:v>
+        <x:v>1967</x:v>
       </x:c>
     </x:row>
     <x:row r="947" spans="1:17">
@@ -25159,10 +25165,10 @@
         <x:v>1404001160</x:v>
       </x:c>
       <x:c r="C947" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D947" s="0" t="s">
-        <x:v>1967</x:v>
+        <x:v>1968</x:v>
       </x:c>
     </x:row>
     <x:row r="948" spans="1:17">
@@ -25173,10 +25179,10 @@
         <x:v>1404001161</x:v>
       </x:c>
       <x:c r="C948" s="0" t="s">
-        <x:v>1421</x:v>
+        <x:v>1422</x:v>
       </x:c>
       <x:c r="D948" s="0" t="s">
-        <x:v>1968</x:v>
+        <x:v>1969</x:v>
       </x:c>
     </x:row>
     <x:row r="949" spans="1:17">
@@ -25187,16 +25193,16 @@
         <x:v>1404001162</x:v>
       </x:c>
       <x:c r="C949" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D949" s="0" t="s">
-        <x:v>1969</x:v>
+        <x:v>1970</x:v>
       </x:c>
       <x:c r="G949" s="0" t="s">
-        <x:v>1969</x:v>
+        <x:v>1970</x:v>
       </x:c>
       <x:c r="I949" s="0" t="s">
-        <x:v>1970</x:v>
+        <x:v>1971</x:v>
       </x:c>
     </x:row>
     <x:row r="950" spans="1:17">
@@ -25210,13 +25216,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D950" s="0" t="s">
-        <x:v>1971</x:v>
+        <x:v>1972</x:v>
       </x:c>
       <x:c r="G950" s="0" t="s">
-        <x:v>1972</x:v>
+        <x:v>1973</x:v>
       </x:c>
       <x:c r="I950" s="0" t="s">
-        <x:v>1973</x:v>
+        <x:v>1974</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:17">
@@ -25227,16 +25233,16 @@
         <x:v>1404001164</x:v>
       </x:c>
       <x:c r="C951" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D951" s="0" t="s">
-        <x:v>1972</x:v>
+        <x:v>1973</x:v>
       </x:c>
       <x:c r="G951" s="0" t="s">
-        <x:v>1972</x:v>
+        <x:v>1973</x:v>
       </x:c>
       <x:c r="I951" s="0" t="s">
-        <x:v>1974</x:v>
+        <x:v>1975</x:v>
       </x:c>
     </x:row>
     <x:row r="952" spans="1:17">
@@ -25250,13 +25256,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D952" s="0" t="s">
-        <x:v>1975</x:v>
+        <x:v>1976</x:v>
       </x:c>
       <x:c r="G952" s="0" t="s">
-        <x:v>1976</x:v>
+        <x:v>1977</x:v>
       </x:c>
       <x:c r="I952" s="0" t="s">
-        <x:v>1977</x:v>
+        <x:v>1978</x:v>
       </x:c>
     </x:row>
     <x:row r="953" spans="1:17">
@@ -25267,16 +25273,16 @@
         <x:v>1404001166</x:v>
       </x:c>
       <x:c r="C953" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D953" s="0" t="s">
-        <x:v>1978</x:v>
+        <x:v>1979</x:v>
       </x:c>
       <x:c r="G953" s="0" t="s">
-        <x:v>1978</x:v>
+        <x:v>1979</x:v>
       </x:c>
       <x:c r="I953" s="0" t="s">
-        <x:v>1979</x:v>
+        <x:v>1980</x:v>
       </x:c>
     </x:row>
     <x:row r="954" spans="1:17">
@@ -25290,13 +25296,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D954" s="0" t="s">
-        <x:v>1980</x:v>
+        <x:v>1981</x:v>
       </x:c>
       <x:c r="G954" s="0" t="s">
-        <x:v>1981</x:v>
+        <x:v>1982</x:v>
       </x:c>
       <x:c r="I954" s="0" t="s">
-        <x:v>1982</x:v>
+        <x:v>1983</x:v>
       </x:c>
     </x:row>
     <x:row r="955" spans="1:17">
@@ -25307,16 +25313,16 @@
         <x:v>1404001168</x:v>
       </x:c>
       <x:c r="C955" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D955" s="0" t="s">
-        <x:v>1976</x:v>
+        <x:v>1977</x:v>
       </x:c>
       <x:c r="G955" s="0" t="s">
-        <x:v>1976</x:v>
+        <x:v>1977</x:v>
       </x:c>
       <x:c r="I955" s="0" t="s">
-        <x:v>1983</x:v>
+        <x:v>1984</x:v>
       </x:c>
     </x:row>
     <x:row r="956" spans="1:17">
@@ -25330,13 +25336,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D956" s="0" t="s">
-        <x:v>1984</x:v>
+        <x:v>1985</x:v>
       </x:c>
       <x:c r="G956" s="0" t="s">
-        <x:v>1985</x:v>
+        <x:v>1986</x:v>
       </x:c>
       <x:c r="I956" s="0" t="s">
-        <x:v>1986</x:v>
+        <x:v>1987</x:v>
       </x:c>
     </x:row>
     <x:row r="957" spans="1:17">
@@ -25347,16 +25353,16 @@
         <x:v>1404001170</x:v>
       </x:c>
       <x:c r="C957" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D957" s="0" t="s">
-        <x:v>1987</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="G957" s="0" t="s">
-        <x:v>1987</x:v>
+        <x:v>1988</x:v>
       </x:c>
       <x:c r="I957" s="0" t="s">
-        <x:v>1988</x:v>
+        <x:v>1989</x:v>
       </x:c>
     </x:row>
     <x:row r="958" spans="1:17">
@@ -25370,13 +25376,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D958" s="0" t="s">
-        <x:v>1989</x:v>
+        <x:v>1990</x:v>
       </x:c>
       <x:c r="G958" s="0" t="s">
-        <x:v>1990</x:v>
+        <x:v>1991</x:v>
       </x:c>
       <x:c r="I958" s="0" t="s">
-        <x:v>1991</x:v>
+        <x:v>1992</x:v>
       </x:c>
     </x:row>
     <x:row r="959" spans="1:17">
@@ -25387,16 +25393,16 @@
         <x:v>1404001172</x:v>
       </x:c>
       <x:c r="C959" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D959" s="0" t="s">
-        <x:v>1981</x:v>
+        <x:v>1982</x:v>
       </x:c>
       <x:c r="G959" s="0" t="s">
-        <x:v>1981</x:v>
+        <x:v>1982</x:v>
       </x:c>
       <x:c r="I959" s="0" t="s">
-        <x:v>1992</x:v>
+        <x:v>1993</x:v>
       </x:c>
     </x:row>
     <x:row r="960" spans="1:17">
@@ -25410,13 +25416,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D960" s="0" t="s">
-        <x:v>1993</x:v>
+        <x:v>1994</x:v>
       </x:c>
       <x:c r="G960" s="0" t="s">
-        <x:v>1994</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="I960" s="0" t="s">
-        <x:v>1995</x:v>
+        <x:v>1996</x:v>
       </x:c>
     </x:row>
     <x:row r="961" spans="1:17">
@@ -25427,16 +25433,16 @@
         <x:v>1404001174</x:v>
       </x:c>
       <x:c r="C961" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D961" s="0" t="s">
-        <x:v>1996</x:v>
+        <x:v>1997</x:v>
       </x:c>
       <x:c r="G961" s="0" t="s">
-        <x:v>1996</x:v>
+        <x:v>1997</x:v>
       </x:c>
       <x:c r="I961" s="0" t="s">
-        <x:v>1997</x:v>
+        <x:v>1998</x:v>
       </x:c>
     </x:row>
     <x:row r="962" spans="1:17">
@@ -25450,13 +25456,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D962" s="0" t="s">
-        <x:v>1998</x:v>
+        <x:v>1999</x:v>
       </x:c>
       <x:c r="G962" s="0" t="s">
-        <x:v>1999</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="I962" s="0" t="s">
-        <x:v>2000</x:v>
+        <x:v>2001</x:v>
       </x:c>
     </x:row>
     <x:row r="963" spans="1:17">
@@ -25467,16 +25473,16 @@
         <x:v>1404001176</x:v>
       </x:c>
       <x:c r="C963" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D963" s="0" t="s">
-        <x:v>1985</x:v>
+        <x:v>1986</x:v>
       </x:c>
       <x:c r="G963" s="0" t="s">
-        <x:v>1985</x:v>
+        <x:v>1986</x:v>
       </x:c>
       <x:c r="I963" s="0" t="s">
-        <x:v>2001</x:v>
+        <x:v>2002</x:v>
       </x:c>
     </x:row>
     <x:row r="964" spans="1:17">
@@ -25490,13 +25496,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D964" s="0" t="s">
-        <x:v>2002</x:v>
+        <x:v>2003</x:v>
       </x:c>
       <x:c r="G964" s="0" t="s">
-        <x:v>2002</x:v>
+        <x:v>2003</x:v>
       </x:c>
       <x:c r="I964" s="0" t="s">
-        <x:v>2003</x:v>
+        <x:v>2004</x:v>
       </x:c>
     </x:row>
     <x:row r="965" spans="1:17">
@@ -25507,16 +25513,16 @@
         <x:v>1404001178</x:v>
       </x:c>
       <x:c r="C965" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D965" s="0" t="s">
-        <x:v>2004</x:v>
+        <x:v>2005</x:v>
       </x:c>
       <x:c r="G965" s="0" t="s">
-        <x:v>2004</x:v>
+        <x:v>2005</x:v>
       </x:c>
       <x:c r="I965" s="0" t="s">
-        <x:v>2005</x:v>
+        <x:v>2006</x:v>
       </x:c>
     </x:row>
     <x:row r="966" spans="1:17">
@@ -25530,13 +25536,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D966" s="0" t="s">
-        <x:v>2006</x:v>
+        <x:v>2007</x:v>
       </x:c>
       <x:c r="G966" s="0" t="s">
-        <x:v>2006</x:v>
+        <x:v>2007</x:v>
       </x:c>
       <x:c r="I966" s="0" t="s">
-        <x:v>2007</x:v>
+        <x:v>2008</x:v>
       </x:c>
     </x:row>
     <x:row r="967" spans="1:17">
@@ -25547,16 +25553,16 @@
         <x:v>1404001180</x:v>
       </x:c>
       <x:c r="C967" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D967" s="0" t="s">
-        <x:v>1990</x:v>
+        <x:v>1991</x:v>
       </x:c>
       <x:c r="G967" s="0" t="s">
-        <x:v>1990</x:v>
+        <x:v>1991</x:v>
       </x:c>
       <x:c r="I967" s="0" t="s">
-        <x:v>2008</x:v>
+        <x:v>2009</x:v>
       </x:c>
     </x:row>
     <x:row r="968" spans="1:17">
@@ -25570,13 +25576,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D968" s="0" t="s">
-        <x:v>2009</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="G968" s="0" t="s">
-        <x:v>2009</x:v>
+        <x:v>2010</x:v>
       </x:c>
       <x:c r="I968" s="0" t="s">
-        <x:v>2010</x:v>
+        <x:v>2011</x:v>
       </x:c>
     </x:row>
     <x:row r="969" spans="1:17">
@@ -25587,16 +25593,16 @@
         <x:v>1404001182</x:v>
       </x:c>
       <x:c r="C969" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D969" s="0" t="s">
-        <x:v>2011</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="G969" s="0" t="s">
-        <x:v>2011</x:v>
+        <x:v>2012</x:v>
       </x:c>
       <x:c r="I969" s="0" t="s">
-        <x:v>2012</x:v>
+        <x:v>2013</x:v>
       </x:c>
     </x:row>
     <x:row r="970" spans="1:17">
@@ -25610,13 +25616,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D970" s="0" t="s">
-        <x:v>2013</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="G970" s="0" t="s">
-        <x:v>2013</x:v>
+        <x:v>2014</x:v>
       </x:c>
       <x:c r="I970" s="0" t="s">
-        <x:v>2014</x:v>
+        <x:v>2015</x:v>
       </x:c>
     </x:row>
     <x:row r="971" spans="1:17">
@@ -25627,16 +25633,16 @@
         <x:v>1404001184</x:v>
       </x:c>
       <x:c r="C971" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D971" s="0" t="s">
-        <x:v>1994</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="G971" s="0" t="s">
-        <x:v>1994</x:v>
+        <x:v>1995</x:v>
       </x:c>
       <x:c r="I971" s="0" t="s">
-        <x:v>2015</x:v>
+        <x:v>2016</x:v>
       </x:c>
     </x:row>
     <x:row r="972" spans="1:17">
@@ -25650,13 +25656,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D972" s="0" t="s">
-        <x:v>2016</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="G972" s="0" t="s">
-        <x:v>2016</x:v>
+        <x:v>2017</x:v>
       </x:c>
       <x:c r="I972" s="0" t="s">
-        <x:v>2017</x:v>
+        <x:v>2018</x:v>
       </x:c>
     </x:row>
     <x:row r="973" spans="1:17">
@@ -25667,16 +25673,16 @@
         <x:v>1404001186</x:v>
       </x:c>
       <x:c r="C973" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D973" s="0" t="s">
-        <x:v>2018</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="G973" s="0" t="s">
-        <x:v>2018</x:v>
+        <x:v>2019</x:v>
       </x:c>
       <x:c r="I973" s="0" t="s">
-        <x:v>2019</x:v>
+        <x:v>2020</x:v>
       </x:c>
     </x:row>
     <x:row r="974" spans="1:17">
@@ -25690,13 +25696,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D974" s="0" t="s">
-        <x:v>2020</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="G974" s="0" t="s">
-        <x:v>2020</x:v>
+        <x:v>2021</x:v>
       </x:c>
       <x:c r="I974" s="0" t="s">
-        <x:v>2021</x:v>
+        <x:v>2022</x:v>
       </x:c>
     </x:row>
     <x:row r="975" spans="1:17">
@@ -25707,16 +25713,16 @@
         <x:v>1404001188</x:v>
       </x:c>
       <x:c r="C975" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D975" s="0" t="s">
-        <x:v>1999</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G975" s="0" t="s">
-        <x:v>1999</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="I975" s="0" t="s">
-        <x:v>2022</x:v>
+        <x:v>2023</x:v>
       </x:c>
     </x:row>
     <x:row r="976" spans="1:17">
@@ -25730,13 +25736,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D976" s="0" t="s">
-        <x:v>2023</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="G976" s="0" t="s">
-        <x:v>2023</x:v>
+        <x:v>2024</x:v>
       </x:c>
       <x:c r="I976" s="0" t="s">
-        <x:v>2024</x:v>
+        <x:v>2025</x:v>
       </x:c>
     </x:row>
     <x:row r="977" spans="1:17">
@@ -25747,16 +25753,16 @@
         <x:v>1404001190</x:v>
       </x:c>
       <x:c r="C977" s="0" t="s">
-        <x:v>1525</x:v>
+        <x:v>1526</x:v>
       </x:c>
       <x:c r="D977" s="0" t="s">
-        <x:v>2025</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="G977" s="0" t="s">
-        <x:v>2025</x:v>
+        <x:v>2026</x:v>
       </x:c>
       <x:c r="I977" s="0" t="s">
-        <x:v>2026</x:v>
+        <x:v>2027</x:v>
       </x:c>
     </x:row>
     <x:row r="978" spans="1:17">
@@ -25770,13 +25776,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D978" s="0" t="s">
-        <x:v>2027</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="G978" s="0" t="s">
-        <x:v>2027</x:v>
+        <x:v>2028</x:v>
       </x:c>
       <x:c r="I978" s="0" t="s">
-        <x:v>2028</x:v>
+        <x:v>2029</x:v>
       </x:c>
     </x:row>
     <x:row r="979" spans="1:17">
@@ -25790,13 +25796,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D979" s="0" t="s">
-        <x:v>2029</x:v>
+        <x:v>2030</x:v>
       </x:c>
       <x:c r="G979" s="0" t="s">
-        <x:v>2029</x:v>
+        <x:v>2030</x:v>
       </x:c>
       <x:c r="I979" s="0" t="s">
-        <x:v>2030</x:v>
+        <x:v>2031</x:v>
       </x:c>
     </x:row>
     <x:row r="980" spans="1:17">
@@ -25810,13 +25816,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D980" s="0" t="s">
-        <x:v>2031</x:v>
+        <x:v>2032</x:v>
       </x:c>
       <x:c r="G980" s="0" t="s">
-        <x:v>2031</x:v>
+        <x:v>2032</x:v>
       </x:c>
       <x:c r="I980" s="0" t="s">
-        <x:v>2032</x:v>
+        <x:v>2033</x:v>
       </x:c>
     </x:row>
     <x:row r="981" spans="1:17">
@@ -25830,13 +25836,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D981" s="0" t="s">
-        <x:v>2033</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="G981" s="0" t="s">
-        <x:v>2033</x:v>
+        <x:v>2034</x:v>
       </x:c>
       <x:c r="I981" s="0" t="s">
-        <x:v>2034</x:v>
+        <x:v>2035</x:v>
       </x:c>
     </x:row>
     <x:row r="982" spans="1:17">
@@ -25850,13 +25856,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D982" s="0" t="s">
-        <x:v>2035</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="G982" s="0" t="s">
-        <x:v>2035</x:v>
+        <x:v>2036</x:v>
       </x:c>
       <x:c r="I982" s="0" t="s">
-        <x:v>2036</x:v>
+        <x:v>2037</x:v>
       </x:c>
     </x:row>
     <x:row r="983" spans="1:17">
@@ -25870,13 +25876,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D983" s="0" t="s">
-        <x:v>2037</x:v>
+        <x:v>2038</x:v>
       </x:c>
       <x:c r="G983" s="0" t="s">
-        <x:v>2037</x:v>
+        <x:v>2038</x:v>
       </x:c>
       <x:c r="I983" s="0" t="s">
-        <x:v>2038</x:v>
+        <x:v>2039</x:v>
       </x:c>
     </x:row>
     <x:row r="984" spans="1:17">
@@ -25890,13 +25896,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D984" s="0" t="s">
-        <x:v>2039</x:v>
+        <x:v>2040</x:v>
       </x:c>
       <x:c r="G984" s="0" t="s">
-        <x:v>2039</x:v>
+        <x:v>2040</x:v>
       </x:c>
       <x:c r="I984" s="0" t="s">
-        <x:v>2040</x:v>
+        <x:v>2041</x:v>
       </x:c>
     </x:row>
     <x:row r="985" spans="1:17">
@@ -25910,13 +25916,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D985" s="0" t="s">
-        <x:v>2041</x:v>
+        <x:v>2042</x:v>
       </x:c>
       <x:c r="G985" s="0" t="s">
-        <x:v>2041</x:v>
+        <x:v>2042</x:v>
       </x:c>
       <x:c r="I985" s="0" t="s">
-        <x:v>2042</x:v>
+        <x:v>2043</x:v>
       </x:c>
     </x:row>
     <x:row r="986" spans="1:17">
@@ -25930,13 +25936,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D986" s="0" t="s">
-        <x:v>2043</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="G986" s="0" t="s">
-        <x:v>2043</x:v>
+        <x:v>2044</x:v>
       </x:c>
       <x:c r="I986" s="0" t="s">
-        <x:v>2044</x:v>
+        <x:v>2045</x:v>
       </x:c>
     </x:row>
     <x:row r="987" spans="1:17">
@@ -25950,13 +25956,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D987" s="0" t="s">
-        <x:v>2045</x:v>
+        <x:v>2046</x:v>
       </x:c>
       <x:c r="G987" s="0" t="s">
-        <x:v>2045</x:v>
+        <x:v>2046</x:v>
       </x:c>
       <x:c r="I987" s="0" t="s">
-        <x:v>2046</x:v>
+        <x:v>2047</x:v>
       </x:c>
     </x:row>
     <x:row r="988" spans="1:17">
@@ -25970,13 +25976,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D988" s="0" t="s">
-        <x:v>2047</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="G988" s="0" t="s">
-        <x:v>2047</x:v>
+        <x:v>2048</x:v>
       </x:c>
       <x:c r="I988" s="0" t="s">
-        <x:v>2048</x:v>
+        <x:v>2049</x:v>
       </x:c>
     </x:row>
     <x:row r="989" spans="1:17">
@@ -25990,13 +25996,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D989" s="0" t="s">
-        <x:v>2049</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="G989" s="0" t="s">
-        <x:v>2049</x:v>
+        <x:v>2050</x:v>
       </x:c>
       <x:c r="I989" s="0" t="s">
-        <x:v>2050</x:v>
+        <x:v>2051</x:v>
       </x:c>
     </x:row>
     <x:row r="990" spans="1:17">
@@ -26010,13 +26016,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D990" s="0" t="s">
-        <x:v>2051</x:v>
+        <x:v>2052</x:v>
       </x:c>
       <x:c r="G990" s="0" t="s">
-        <x:v>2051</x:v>
+        <x:v>2052</x:v>
       </x:c>
       <x:c r="I990" s="0" t="s">
-        <x:v>2052</x:v>
+        <x:v>2053</x:v>
       </x:c>
     </x:row>
     <x:row r="991" spans="1:17">
@@ -26030,13 +26036,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D991" s="0" t="s">
-        <x:v>2053</x:v>
+        <x:v>2054</x:v>
       </x:c>
       <x:c r="G991" s="0" t="s">
-        <x:v>2053</x:v>
+        <x:v>2054</x:v>
       </x:c>
       <x:c r="I991" s="0" t="s">
-        <x:v>2054</x:v>
+        <x:v>2055</x:v>
       </x:c>
     </x:row>
     <x:row r="992" spans="1:17">
@@ -26050,13 +26056,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D992" s="0" t="s">
-        <x:v>2055</x:v>
+        <x:v>2056</x:v>
       </x:c>
       <x:c r="G992" s="0" t="s">
-        <x:v>2055</x:v>
+        <x:v>2056</x:v>
       </x:c>
       <x:c r="I992" s="0" t="s">
-        <x:v>2056</x:v>
+        <x:v>2057</x:v>
       </x:c>
     </x:row>
     <x:row r="993" spans="1:17">
@@ -26070,13 +26076,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D993" s="0" t="s">
-        <x:v>2057</x:v>
+        <x:v>2058</x:v>
       </x:c>
       <x:c r="G993" s="0" t="s">
-        <x:v>2057</x:v>
+        <x:v>2058</x:v>
       </x:c>
       <x:c r="I993" s="0" t="s">
-        <x:v>2058</x:v>
+        <x:v>2059</x:v>
       </x:c>
     </x:row>
     <x:row r="994" spans="1:17">
@@ -26090,13 +26096,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D994" s="0" t="s">
-        <x:v>2059</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="G994" s="0" t="s">
-        <x:v>2059</x:v>
+        <x:v>2060</x:v>
       </x:c>
       <x:c r="I994" s="0" t="s">
-        <x:v>2060</x:v>
+        <x:v>2061</x:v>
       </x:c>
     </x:row>
     <x:row r="995" spans="1:17">
@@ -26110,13 +26116,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D995" s="0" t="s">
-        <x:v>2061</x:v>
+        <x:v>2062</x:v>
       </x:c>
       <x:c r="G995" s="0" t="s">
-        <x:v>2062</x:v>
+        <x:v>2063</x:v>
       </x:c>
       <x:c r="I995" s="0" t="s">
-        <x:v>2063</x:v>
+        <x:v>2064</x:v>
       </x:c>
     </x:row>
     <x:row r="996" spans="1:17">
@@ -26130,13 +26136,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D996" s="0" t="s">
-        <x:v>2064</x:v>
+        <x:v>2065</x:v>
       </x:c>
       <x:c r="G996" s="0" t="s">
-        <x:v>2064</x:v>
+        <x:v>2065</x:v>
       </x:c>
       <x:c r="I996" s="0" t="s">
-        <x:v>2065</x:v>
+        <x:v>2066</x:v>
       </x:c>
     </x:row>
     <x:row r="997" spans="1:17">
@@ -26150,13 +26156,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D997" s="0" t="s">
-        <x:v>2066</x:v>
+        <x:v>2067</x:v>
       </x:c>
       <x:c r="G997" s="0" t="s">
-        <x:v>2067</x:v>
+        <x:v>2068</x:v>
       </x:c>
       <x:c r="I997" s="0" t="s">
-        <x:v>2068</x:v>
+        <x:v>2069</x:v>
       </x:c>
     </x:row>
     <x:row r="998" spans="1:17">
@@ -26170,13 +26176,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D998" s="0" t="s">
-        <x:v>2069</x:v>
+        <x:v>2070</x:v>
       </x:c>
       <x:c r="G998" s="0" t="s">
-        <x:v>2069</x:v>
+        <x:v>2070</x:v>
       </x:c>
       <x:c r="I998" s="0" t="s">
-        <x:v>2070</x:v>
+        <x:v>2071</x:v>
       </x:c>
     </x:row>
     <x:row r="999" spans="1:17">
@@ -26190,13 +26196,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D999" s="0" t="s">
-        <x:v>2071</x:v>
+        <x:v>2072</x:v>
       </x:c>
       <x:c r="G999" s="0" t="s">
-        <x:v>2071</x:v>
+        <x:v>2072</x:v>
       </x:c>
       <x:c r="I999" s="0" t="s">
-        <x:v>2072</x:v>
+        <x:v>2073</x:v>
       </x:c>
     </x:row>
     <x:row r="1000" spans="1:17">
@@ -26210,13 +26216,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1000" s="0" t="s">
-        <x:v>2073</x:v>
+        <x:v>2074</x:v>
       </x:c>
       <x:c r="G1000" s="0" t="s">
-        <x:v>2073</x:v>
+        <x:v>2074</x:v>
       </x:c>
       <x:c r="I1000" s="0" t="s">
-        <x:v>2074</x:v>
+        <x:v>2075</x:v>
       </x:c>
     </x:row>
     <x:row r="1001" spans="1:17">
@@ -26230,13 +26236,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1001" s="0" t="s">
-        <x:v>2075</x:v>
+        <x:v>2076</x:v>
       </x:c>
       <x:c r="G1001" s="0" t="s">
-        <x:v>2075</x:v>
+        <x:v>2076</x:v>
       </x:c>
       <x:c r="I1001" s="0" t="s">
-        <x:v>2076</x:v>
+        <x:v>2077</x:v>
       </x:c>
     </x:row>
     <x:row r="1002" spans="1:17">
@@ -26250,13 +26256,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1002" s="0" t="s">
-        <x:v>2077</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="G1002" s="0" t="s">
-        <x:v>2077</x:v>
+        <x:v>2078</x:v>
       </x:c>
       <x:c r="I1002" s="0" t="s">
-        <x:v>2078</x:v>
+        <x:v>2079</x:v>
       </x:c>
     </x:row>
     <x:row r="1003" spans="1:17">
@@ -26270,13 +26276,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1003" s="0" t="s">
-        <x:v>2079</x:v>
+        <x:v>2080</x:v>
       </x:c>
       <x:c r="G1003" s="0" t="s">
-        <x:v>2079</x:v>
+        <x:v>2080</x:v>
       </x:c>
       <x:c r="I1003" s="0" t="s">
-        <x:v>2080</x:v>
+        <x:v>2081</x:v>
       </x:c>
     </x:row>
     <x:row r="1004" spans="1:17">
@@ -26287,16 +26293,16 @@
         <x:v>1404001217</x:v>
       </x:c>
       <x:c r="C1004" s="0" t="s">
-        <x:v>1382</x:v>
+        <x:v>1383</x:v>
       </x:c>
       <x:c r="D1004" s="0" t="s">
-        <x:v>2081</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="G1004" s="0" t="s">
-        <x:v>2081</x:v>
+        <x:v>2082</x:v>
       </x:c>
       <x:c r="I1004" s="0" t="s">
-        <x:v>2082</x:v>
+        <x:v>2083</x:v>
       </x:c>
     </x:row>
     <x:row r="1005" spans="1:17">
@@ -26310,13 +26316,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1005" s="0" t="s">
-        <x:v>2083</x:v>
+        <x:v>2084</x:v>
       </x:c>
       <x:c r="G1005" s="0" t="s">
-        <x:v>2083</x:v>
+        <x:v>2084</x:v>
       </x:c>
       <x:c r="I1005" s="0" t="s">
-        <x:v>2084</x:v>
+        <x:v>2085</x:v>
       </x:c>
     </x:row>
     <x:row r="1006" spans="1:17">
@@ -26330,13 +26336,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1006" s="0" t="s">
-        <x:v>2085</x:v>
+        <x:v>2086</x:v>
       </x:c>
       <x:c r="G1006" s="0" t="s">
-        <x:v>2085</x:v>
+        <x:v>2086</x:v>
       </x:c>
       <x:c r="I1006" s="0" t="s">
-        <x:v>2086</x:v>
+        <x:v>2087</x:v>
       </x:c>
     </x:row>
     <x:row r="1007" spans="1:17">
@@ -26350,13 +26356,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1007" s="0" t="s">
-        <x:v>2087</x:v>
+        <x:v>2088</x:v>
       </x:c>
       <x:c r="G1007" s="0" t="s">
-        <x:v>2087</x:v>
+        <x:v>2088</x:v>
       </x:c>
       <x:c r="I1007" s="0" t="s">
-        <x:v>2088</x:v>
+        <x:v>2089</x:v>
       </x:c>
     </x:row>
     <x:row r="1008" spans="1:17">
@@ -26370,13 +26376,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1008" s="0" t="s">
-        <x:v>2089</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="G1008" s="0" t="s">
-        <x:v>2089</x:v>
+        <x:v>2090</x:v>
       </x:c>
       <x:c r="I1008" s="0" t="s">
-        <x:v>2090</x:v>
+        <x:v>2091</x:v>
       </x:c>
     </x:row>
     <x:row r="1009" spans="1:17">
@@ -26390,13 +26396,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1009" s="0" t="s">
-        <x:v>2091</x:v>
+        <x:v>2092</x:v>
       </x:c>
       <x:c r="G1009" s="0" t="s">
-        <x:v>2091</x:v>
+        <x:v>2092</x:v>
       </x:c>
       <x:c r="I1009" s="0" t="s">
-        <x:v>2092</x:v>
+        <x:v>2093</x:v>
       </x:c>
     </x:row>
     <x:row r="1010" spans="1:17">
@@ -26410,13 +26416,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1010" s="0" t="s">
-        <x:v>2093</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="G1010" s="0" t="s">
-        <x:v>2093</x:v>
+        <x:v>2094</x:v>
       </x:c>
       <x:c r="I1010" s="0" t="s">
-        <x:v>2094</x:v>
+        <x:v>2095</x:v>
       </x:c>
     </x:row>
     <x:row r="1011" spans="1:17">
@@ -26430,13 +26436,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1011" s="0" t="s">
-        <x:v>2095</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="G1011" s="0" t="s">
-        <x:v>2095</x:v>
+        <x:v>2096</x:v>
       </x:c>
       <x:c r="I1011" s="0" t="s">
-        <x:v>2096</x:v>
+        <x:v>2097</x:v>
       </x:c>
     </x:row>
     <x:row r="1012" spans="1:17">
@@ -26450,13 +26456,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1012" s="0" t="s">
-        <x:v>2097</x:v>
+        <x:v>2098</x:v>
       </x:c>
       <x:c r="G1012" s="0" t="s">
-        <x:v>2097</x:v>
+        <x:v>2098</x:v>
       </x:c>
       <x:c r="I1012" s="0" t="s">
-        <x:v>2098</x:v>
+        <x:v>2099</x:v>
       </x:c>
     </x:row>
     <x:row r="1013" spans="1:17">
@@ -26470,13 +26476,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1013" s="0" t="s">
-        <x:v>2099</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="G1013" s="0" t="s">
-        <x:v>2099</x:v>
+        <x:v>2100</x:v>
       </x:c>
       <x:c r="I1013" s="0" t="s">
-        <x:v>2100</x:v>
+        <x:v>2101</x:v>
       </x:c>
     </x:row>
     <x:row r="1014" spans="1:17">
@@ -26490,13 +26496,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D1014" s="0" t="s">
-        <x:v>2101</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="G1014" s="0" t="s">
-        <x:v>2101</x:v>
+        <x:v>2102</x:v>
       </x:c>
       <x:c r="I1014" s="0" t="s">
-        <x:v>2102</x:v>
+        <x:v>2103</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
